--- a/qc-corrections/PP_Batch_Release_QC_Register_CORRECTED.xlsx
+++ b/qc-corrections/PP_Batch_Release_QC_Register_CORRECTED.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch Release QC" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correction Log" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="THC by Strain" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Batch Release QC'!$A$4:$Z$289</definedName>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,13 +95,32 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="FF16232B"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <color rgb="FF5A6E75"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -135,16 +154,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FF16232B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3F9"/>
+        <fgColor rgb="FF0E6E6E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F6F5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -157,11 +181,16 @@
         <color rgb="00C6D0CD"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FFD8DEDC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -259,14 +288,37 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -341,48 +393,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>eCoA cross-check</author>
-  </authors>
-  <commentList>
-    <comment ref="H9" authorId="0" shapeId="0">
-      <text>
-        <t>CORRECTED 0.28 -&gt; 0.02
-Batch BG1024 / CBN (%)
-Basis: CoA BG1024 (PPK25050) and the full-panel bundle both state 'CBN 0.02%'. Transcription error.
-QC data-review 17.08.2026 (eCoA cross-check)</t>
-      </text>
-    </comment>
-    <comment ref="U31" authorId="0" shapeId="0">
-      <text>
-        <t>CORRECTED 0.001 -&gt; 0.011
-Batch OPM1024_01 / Hg (mg/kg)
-Basis: CoA P050042 (OPM1024_01): 'Mercury: &lt; 0.1 mg/kg | 0.011 mg/kg'. Decimal-place error (10x low).
-QC data-review 17.08.2026 (eCoA cross-check)</t>
-      </text>
-    </comment>
-    <comment ref="G36" authorId="0" shapeId="0">
-      <text>
-        <t>CORRECTED 24.70 -&gt; 0.10
-Batch HPA1024_01 / CBD (%)
-Basis: CoA P050052 (HPA1024_01): 'Vkupno CBD*** = 0.10'. The recorded 24.70 is the Delta9-THCA content from the same table (wrong-column entry). Confirmed in BOTH eCoA sources.
-QC data-review 17.08.2026 (eCoA cross-check)</t>
-      </text>
-    </comment>
-    <comment ref="H285" authorId="0" shapeId="0">
-      <text>
-        <t>CORRECTED 0.36 -&gt; N.D.
-Batch HPA1024 / CBN (%)
-Basis: CoA HPA1024 (bulk): 'Related substances** - Cannabinol | &lt; 1.0% | N.D.'. Recorded value not supported by the CoA.
-QC data-review 17.08.2026 (eCoA cross-check)</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1333,7 +1343,7 @@
           <t>&lt;LOQ</t>
         </is>
       </c>
-      <c r="H9" s="43" t="n">
+      <c r="H9" s="7" t="n">
         <v>0.02</v>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -4024,7 +4034,7 @@
           <t>0.01</t>
         </is>
       </c>
-      <c r="U31" s="43" t="n">
+      <c r="U31" s="7" t="n">
         <v>0.011</v>
       </c>
       <c r="V31" s="12" t="inlineStr">
@@ -4560,7 +4570,7 @@
           <t>/</t>
         </is>
       </c>
-      <c r="G36" s="43" t="n">
+      <c r="G36" s="33" t="n">
         <v>0.1</v>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -34107,7 +34117,7 @@
           <t>&lt;LOQ</t>
         </is>
       </c>
-      <c r="H285" s="43" t="inlineStr">
+      <c r="H285" s="7" t="inlineStr">
         <is>
           <t>N.D.</t>
         </is>
@@ -35008,7 +35018,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z289" r:id="rId267"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -35018,238 +35027,4343 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="86" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="8.300000000000001" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="44" t="inlineStr">
-        <is>
-          <t>Purely Plant GmbH - Batch Release QC Register - CORRECTION LOG</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="45" t="inlineStr">
-        <is>
-          <t>Corrections raised from an eCoA cross-check of all 80 batches x 17 parameters against source CoAs (RAGflow eCOA dataset, 260 CoAs + Letta ImB_QC_COAs, 120 files). Original values are preserved in this log and in a note on each corrected cell. PENDING QC REVIEW/APPROVAL before the record is re-issued.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="46" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="46" t="inlineStr">
-        <is>
-          <t>Cell</t>
-        </is>
-      </c>
-      <c r="C4" s="46" t="inlineStr">
-        <is>
-          <t>Batch</t>
-        </is>
-      </c>
-      <c r="D4" s="46" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="E4" s="46" t="inlineStr">
-        <is>
-          <t>Original</t>
-        </is>
-      </c>
-      <c r="F4" s="46" t="inlineStr">
-        <is>
-          <t>Corrected</t>
-        </is>
-      </c>
-      <c r="G4" s="46" t="inlineStr">
-        <is>
-          <t>Basis / source evidence</t>
-        </is>
-      </c>
-      <c r="H4" s="46" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="A1" s="43" t="inlineStr">
+        <is>
+          <t>Purely Plant GmbH — Total Δ⁹-THC by strain</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Every production batch grouped by strain, with every Total Δ⁹-THC result on file, referenced to its certificate. BLQ / &lt;LOQ values are shown but excluded from the numeric range. Strain names canonicalised; CoA codes resolved against source certificates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="45" t="inlineStr">
+        <is>
+          <t>Seq</t>
+        </is>
+      </c>
+      <c r="B4" s="45" t="inlineStr">
+        <is>
+          <t>Batch number</t>
+        </is>
+      </c>
+      <c r="C4" s="45" t="inlineStr">
+        <is>
+          <t>P-number</t>
+        </is>
+      </c>
+      <c r="D4" s="45" t="inlineStr">
+        <is>
+          <t>Total Δ⁹-THC</t>
+        </is>
+      </c>
+      <c r="E4" s="45" t="inlineStr">
+        <is>
+          <t>Batch THC spec</t>
+        </is>
+      </c>
+      <c r="F4" s="45" t="inlineStr">
+        <is>
+          <t>CoA code</t>
+        </is>
+      </c>
+      <c r="G4" s="45" t="inlineStr">
+        <is>
+          <t>Date of issue</t>
+        </is>
+      </c>
+      <c r="H4" s="45" t="inlineStr">
+        <is>
+          <t>Issuing institution</t>
+        </is>
+      </c>
+      <c r="I4" s="45" t="inlineStr">
+        <is>
+          <t>Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="19.5" customHeight="1">
+      <c r="A5" s="46" t="inlineStr">
+        <is>
+          <t>Apple and Banana      1 batch(es)      Total Δ⁹-THC across batches: 16.93 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>G36</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" s="48" t="inlineStr">
+        <is>
+          <t>AB092501</t>
+        </is>
+      </c>
+      <c r="C6" s="49" t="inlineStr">
+        <is>
+          <t>P060052</t>
+        </is>
+      </c>
+      <c r="D6" s="49" t="inlineStr">
+        <is>
+          <t>16.93%</t>
+        </is>
+      </c>
+      <c r="E6" s="49" t="inlineStr">
+        <is>
+          <t>15.23 – 18.62 %</t>
+        </is>
+      </c>
+      <c r="F6" s="49" t="inlineStr">
+        <is>
+          <t>PP CoA #037 / ППК26005</t>
+        </is>
+      </c>
+      <c r="G6" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H6" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I6" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="19.5" customHeight="1">
+      <c r="A7" s="46" t="inlineStr">
+        <is>
+          <t>Blue Gelato      1 batch(es)      Total Δ⁹-THC across batches: 21.80 – 26.14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="51" t="inlineStr">
+        <is>
+          <t>BG1024</t>
+        </is>
+      </c>
+      <c r="C8" s="52" t="n"/>
+      <c r="D8" s="52" t="inlineStr">
+        <is>
+          <t>21.80%</t>
+        </is>
+      </c>
+      <c r="E8" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F8" s="52" t="inlineStr">
+        <is>
+          <t>ППК25050</t>
+        </is>
+      </c>
+      <c r="G8" s="52" t="inlineStr">
+        <is>
+          <t>26.02.2025</t>
+        </is>
+      </c>
+      <c r="H8" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I8" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="53" t="n"/>
+      <c r="B9" s="53" t="n"/>
+      <c r="C9" s="53" t="n"/>
+      <c r="D9" s="49" t="inlineStr">
+        <is>
+          <t>26.14 %w/w (U 1.61)</t>
+        </is>
+      </c>
+      <c r="E9" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F9" s="49" t="inlineStr">
+        <is>
+          <t>197-1-К/26</t>
+        </is>
+      </c>
+      <c r="G9" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H9" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I9" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="19.5" customHeight="1">
+      <c r="A10" s="46" t="inlineStr">
+        <is>
+          <t>Blue Sunset Sherbet      3 batch(es)      Total Δ⁹-THC across batches: 20.39 – 25.01 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="51" t="inlineStr">
+        <is>
+          <t>BSS1024</t>
+        </is>
+      </c>
+      <c r="C11" s="52" t="n"/>
+      <c r="D11" s="52" t="inlineStr">
+        <is>
+          <t>21.03%</t>
+        </is>
+      </c>
+      <c r="E11" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F11" s="52" t="inlineStr">
+        <is>
+          <t>ППК25051</t>
+        </is>
+      </c>
+      <c r="G11" s="52" t="inlineStr">
+        <is>
+          <t>26.02.2025</t>
+        </is>
+      </c>
+      <c r="H11" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I11" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="53" t="n"/>
+      <c r="B12" s="53" t="n"/>
+      <c r="C12" s="53" t="n"/>
+      <c r="D12" s="49" t="inlineStr">
+        <is>
+          <t>25.01 %w/w (U 1.54)</t>
+        </is>
+      </c>
+      <c r="E12" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F12" s="49" t="inlineStr">
+        <is>
+          <t>197-2-К/26</t>
+        </is>
+      </c>
+      <c r="G12" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H12" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I12" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="47" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="48" t="inlineStr">
+        <is>
+          <t>BSS1024_01</t>
+        </is>
+      </c>
+      <c r="C13" s="49" t="inlineStr">
+        <is>
+          <t>P050122</t>
+        </is>
+      </c>
+      <c r="D13" s="49" t="inlineStr">
+        <is>
+          <t>23.42%</t>
+        </is>
+      </c>
+      <c r="E13" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F13" s="49" t="inlineStr">
+        <is>
+          <t>ППК25176</t>
+        </is>
+      </c>
+      <c r="G13" s="49" t="inlineStr">
+        <is>
+          <t>10.07.2025</t>
+        </is>
+      </c>
+      <c r="H13" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I13" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="48" t="inlineStr">
+        <is>
+          <t>BSS052501</t>
+        </is>
+      </c>
+      <c r="C14" s="49" t="inlineStr">
+        <is>
+          <t>P050192</t>
+        </is>
+      </c>
+      <c r="D14" s="49" t="inlineStr">
+        <is>
+          <t>20.39%</t>
+        </is>
+      </c>
+      <c r="E14" s="49" t="inlineStr">
+        <is>
+          <t>19.8 – 24.2 %</t>
+        </is>
+      </c>
+      <c r="F14" s="49" t="inlineStr">
+        <is>
+          <t>In-house GC cross-check NGP/QCG/SOP-024</t>
+        </is>
+      </c>
+      <c r="G14" s="49" t="inlineStr">
+        <is>
+          <t>28.11.2025</t>
+        </is>
+      </c>
+      <c r="H14" s="49" t="inlineStr">
+        <is>
+          <t>Purely Plant (in-house)</t>
+        </is>
+      </c>
+      <c r="I14" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="46" t="inlineStr">
+        <is>
+          <t>Cap Junkie      2 batch(es)      Total Δ⁹-THC across batches: 16.56 – 21.51 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="50" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" s="51" t="inlineStr">
+        <is>
+          <t>CJ062501-2</t>
+        </is>
+      </c>
+      <c r="C16" s="52" t="inlineStr">
+        <is>
+          <t>P050212</t>
+        </is>
+      </c>
+      <c r="D16" s="52" t="inlineStr">
+        <is>
+          <t>16.56%</t>
+        </is>
+      </c>
+      <c r="E16" s="52" t="inlineStr">
+        <is>
+          <t>14.9 – 18.2 %</t>
+        </is>
+      </c>
+      <c r="F16" s="52" t="inlineStr">
+        <is>
+          <t>ППК25322</t>
+        </is>
+      </c>
+      <c r="G16" s="52" t="inlineStr">
+        <is>
+          <t>23.10.2025</t>
+        </is>
+      </c>
+      <c r="H16" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I16" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="53" t="n"/>
+      <c r="B17" s="53" t="n"/>
+      <c r="C17" s="53" t="n"/>
+      <c r="D17" s="49" t="inlineStr">
+        <is>
+          <t>18.91% w/w (U 1.16% w/w)</t>
+        </is>
+      </c>
+      <c r="E17" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F17" s="49" t="inlineStr">
+        <is>
+          <t>197-4-К/26</t>
+        </is>
+      </c>
+      <c r="G17" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H17" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I17" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" s="48" t="inlineStr">
+        <is>
+          <t>CJ062501-1</t>
+        </is>
+      </c>
+      <c r="C18" s="49" t="inlineStr">
+        <is>
+          <t>P050222</t>
+        </is>
+      </c>
+      <c r="D18" s="49" t="inlineStr">
+        <is>
+          <t>21.51%</t>
+        </is>
+      </c>
+      <c r="E18" s="49" t="inlineStr">
+        <is>
+          <t>n/a (informational)</t>
+        </is>
+      </c>
+      <c r="F18" s="49" t="inlineStr">
+        <is>
+          <t>ППК25321</t>
+        </is>
+      </c>
+      <c r="G18" s="49" t="inlineStr">
+        <is>
+          <t>23.10.2025</t>
+        </is>
+      </c>
+      <c r="H18" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I18" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="46" t="inlineStr">
+        <is>
+          <t>Cap Junky      3 batch(es)      Total Δ⁹-THC across batches: 18.29 – 24.96 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="47" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>CJ082501-1</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="inlineStr">
+        <is>
+          <t>P060022</t>
+        </is>
+      </c>
+      <c r="D20" s="49" t="inlineStr">
+        <is>
+          <t>24.96%</t>
+        </is>
+      </c>
+      <c r="E20" s="49" t="inlineStr">
+        <is>
+          <t>22.46 – 27.45 %</t>
+        </is>
+      </c>
+      <c r="F20" s="49" t="inlineStr">
+        <is>
+          <t>ППК26002</t>
+        </is>
+      </c>
+      <c r="G20" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H20" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I20" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="50" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" s="51" t="inlineStr">
+        <is>
+          <t>CJ082501-2</t>
+        </is>
+      </c>
+      <c r="C21" s="52" t="inlineStr">
+        <is>
+          <t>P060032</t>
+        </is>
+      </c>
+      <c r="D21" s="52" t="inlineStr">
+        <is>
+          <t>20.84%</t>
+        </is>
+      </c>
+      <c r="E21" s="52" t="inlineStr">
+        <is>
+          <t>18.75 – 22.92 %</t>
+        </is>
+      </c>
+      <c r="F21" s="52" t="inlineStr">
+        <is>
+          <t>ППК26003</t>
+        </is>
+      </c>
+      <c r="G21" s="52" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H21" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I21" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="53" t="n"/>
+      <c r="B22" s="53" t="n"/>
+      <c r="C22" s="53" t="n"/>
+      <c r="D22" s="49" t="inlineStr">
+        <is>
+          <t>18.29% w/w (U 1.12% w/w)</t>
+        </is>
+      </c>
+      <c r="E22" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F22" s="49" t="inlineStr">
+        <is>
+          <t>197-5-К/26</t>
+        </is>
+      </c>
+      <c r="G22" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H22" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I22" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>CJ092501</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="inlineStr">
+        <is>
+          <t>P060072</t>
+        </is>
+      </c>
+      <c r="D23" s="49" t="inlineStr">
+        <is>
+          <t>22.30%</t>
+        </is>
+      </c>
+      <c r="E23" s="49" t="inlineStr">
+        <is>
+          <t>20.07 – 24.53 %</t>
+        </is>
+      </c>
+      <c r="F23" s="49" t="inlineStr">
+        <is>
+          <t>ППК26007</t>
+        </is>
+      </c>
+      <c r="G23" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H23" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I23" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19.5" customHeight="1">
+      <c r="A24" s="46" t="inlineStr">
+        <is>
+          <t>Cash Cow      2 batch(es)      Total Δ⁹-THC across batches: 13.35 – 17.67 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>CC112501</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="inlineStr">
+        <is>
+          <t>13.35%</t>
+        </is>
+      </c>
+      <c r="E25" s="49" t="n"/>
+      <c r="F25" s="49" t="inlineStr">
+        <is>
+          <t>ППК26068</t>
+        </is>
+      </c>
+      <c r="G25" s="49" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H25" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I25" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="47" t="n">
+        <v>12</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>P060332</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="inlineStr">
+        <is>
+          <t>P060332</t>
+        </is>
+      </c>
+      <c r="D26" s="49" t="inlineStr">
+        <is>
+          <t>17.67 %w/w (U 1.09 %w/w, k=2)</t>
+        </is>
+      </c>
+      <c r="E26" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F26" s="49" t="inlineStr">
+        <is>
+          <t>197-6-К/26</t>
+        </is>
+      </c>
+      <c r="G26" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H26" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I26" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19.5" customHeight="1">
+      <c r="A27" s="46" t="inlineStr">
+        <is>
+          <t>Clemosa a bud      1 batch(es)      Total Δ⁹-THC across batches: 8.02 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="47" t="n">
+        <v>13</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>CLE072501</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="inlineStr">
+        <is>
+          <t>P050282</t>
+        </is>
+      </c>
+      <c r="D28" s="49" t="inlineStr">
+        <is>
+          <t>8.02%</t>
+        </is>
+      </c>
+      <c r="E28" s="49" t="inlineStr">
+        <is>
+          <t>7.2 – 8.82 %</t>
+        </is>
+      </c>
+      <c r="F28" s="49" t="inlineStr">
+        <is>
+          <t>PP CoA #027 / ППК25370</t>
+        </is>
+      </c>
+      <c r="G28" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H28" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I28" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="A29" s="46" t="inlineStr">
+        <is>
+          <t>Cup Junky      4 batch(es)      Total Δ⁹-THC across batches: 14.93 – 24.05 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="47" t="n">
+        <v>14</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>CJ1024</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="inlineStr">
+        <is>
+          <t>23.00%</t>
+        </is>
+      </c>
+      <c r="E30" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F30" s="49" t="inlineStr">
+        <is>
+          <t>ППК25052</t>
+        </is>
+      </c>
+      <c r="G30" s="49" t="inlineStr">
+        <is>
+          <t>26.02.2025</t>
+        </is>
+      </c>
+      <c r="H30" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I30" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" s="51" t="inlineStr">
+        <is>
+          <t>CJ052501-1</t>
+        </is>
+      </c>
+      <c r="C31" s="52" t="inlineStr">
+        <is>
+          <t>P050162</t>
+        </is>
+      </c>
+      <c r="D31" s="52" t="inlineStr">
+        <is>
+          <t>20.29%</t>
+        </is>
+      </c>
+      <c r="E31" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F31" s="52" t="inlineStr">
+        <is>
+          <t>ППК25280</t>
+        </is>
+      </c>
+      <c r="G31" s="52" t="inlineStr">
+        <is>
+          <t>17.09.2025</t>
+        </is>
+      </c>
+      <c r="H31" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I31" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="53" t="n"/>
+      <c r="B32" s="53" t="n"/>
+      <c r="C32" s="53" t="n"/>
+      <c r="D32" s="49" t="inlineStr">
+        <is>
+          <t>24.05 %w/w (U 1.48)</t>
+        </is>
+      </c>
+      <c r="E32" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F32" s="49" t="inlineStr">
+        <is>
+          <t>197-3-К/26</t>
+        </is>
+      </c>
+      <c r="G32" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H32" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I32" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="47" t="n">
+        <v>16</v>
+      </c>
+      <c r="B33" s="48" t="inlineStr">
+        <is>
+          <t>CJ052501-2</t>
+        </is>
+      </c>
+      <c r="C33" s="49" t="inlineStr">
+        <is>
+          <t>P050172</t>
+        </is>
+      </c>
+      <c r="D33" s="49" t="inlineStr">
+        <is>
+          <t>14.93%</t>
+        </is>
+      </c>
+      <c r="E33" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F33" s="49" t="inlineStr">
+        <is>
+          <t>ППК25281</t>
+        </is>
+      </c>
+      <c r="G33" s="49" t="inlineStr">
+        <is>
+          <t>17.09.2025</t>
+        </is>
+      </c>
+      <c r="H33" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I33" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="47" t="n">
+        <v>17</v>
+      </c>
+      <c r="B34" s="48" t="inlineStr">
+        <is>
+          <t>CJ072501</t>
+        </is>
+      </c>
+      <c r="C34" s="49" t="inlineStr">
+        <is>
+          <t>P050252</t>
+        </is>
+      </c>
+      <c r="D34" s="49" t="inlineStr">
+        <is>
+          <t>23.70%</t>
+        </is>
+      </c>
+      <c r="E34" s="49" t="inlineStr">
+        <is>
+          <t>n/a (informational)</t>
+        </is>
+      </c>
+      <c r="F34" s="49" t="inlineStr">
+        <is>
+          <t>ППК25367</t>
+        </is>
+      </c>
+      <c r="G34" s="49" t="inlineStr">
+        <is>
+          <t>28.11.2025</t>
+        </is>
+      </c>
+      <c r="H34" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I34" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="A35" s="46" t="inlineStr">
+        <is>
+          <t>Fat Bastard      6 batch(es)      Total Δ⁹-THC across batches: 12.39 – 20.83 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="47" t="n">
+        <v>18</v>
+      </c>
+      <c r="B36" s="48" t="inlineStr">
+        <is>
+          <t>FB012601</t>
+        </is>
+      </c>
+      <c r="C36" s="49" t="n"/>
+      <c r="D36" s="49" t="inlineStr">
+        <is>
+          <t>14.68%</t>
+        </is>
+      </c>
+      <c r="E36" s="49" t="n"/>
+      <c r="F36" s="49" t="inlineStr">
+        <is>
+          <t>ППК26067</t>
+        </is>
+      </c>
+      <c r="G36" s="49" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H36" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I36" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="47" t="n">
+        <v>19</v>
+      </c>
+      <c r="B37" s="48" t="inlineStr">
+        <is>
+          <t>FB112501</t>
+        </is>
+      </c>
+      <c r="C37" s="49" t="n"/>
+      <c r="D37" s="49" t="inlineStr">
+        <is>
+          <t>16.69%</t>
+        </is>
+      </c>
+      <c r="E37" s="49" t="n"/>
+      <c r="F37" s="49" t="inlineStr">
+        <is>
+          <t>ППК26066</t>
+        </is>
+      </c>
+      <c r="G37" s="49" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H37" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I37" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="47" t="n">
+        <v>20</v>
+      </c>
+      <c r="B38" s="48" t="inlineStr">
+        <is>
+          <t>FB012603</t>
+        </is>
+      </c>
+      <c r="C38" s="49" t="n"/>
+      <c r="D38" s="49" t="inlineStr">
+        <is>
+          <t>20.83%</t>
+        </is>
+      </c>
+      <c r="E38" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F38" s="49" t="inlineStr">
+        <is>
+          <t>ППК26112</t>
+        </is>
+      </c>
+      <c r="G38" s="49" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="H38" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I38" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="47" t="n">
+        <v>21</v>
+      </c>
+      <c r="B39" s="48" t="inlineStr">
+        <is>
+          <t>FB012603V</t>
+        </is>
+      </c>
+      <c r="C39" s="49" t="n"/>
+      <c r="D39" s="49" t="inlineStr">
+        <is>
+          <t>18.29%</t>
+        </is>
+      </c>
+      <c r="E39" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F39" s="49" t="inlineStr">
+        <is>
+          <t>ППК26110</t>
+        </is>
+      </c>
+      <c r="G39" s="49" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="H39" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I39" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="47" t="n">
+        <v>22</v>
+      </c>
+      <c r="B40" s="48" t="inlineStr">
+        <is>
+          <t>FB032601</t>
+        </is>
+      </c>
+      <c r="C40" s="49" t="n"/>
+      <c r="D40" s="49" t="inlineStr">
+        <is>
+          <t>12.39%</t>
+        </is>
+      </c>
+      <c r="E40" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F40" s="49" t="inlineStr">
+        <is>
+          <t>ППК26127</t>
+        </is>
+      </c>
+      <c r="G40" s="49" t="inlineStr">
+        <is>
+          <t>21.07.2026</t>
+        </is>
+      </c>
+      <c r="H40" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I40" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="47" t="n">
+        <v>23</v>
+      </c>
+      <c r="B41" s="48" t="inlineStr">
+        <is>
+          <t>P060352</t>
+        </is>
+      </c>
+      <c r="C41" s="49" t="inlineStr">
+        <is>
+          <t>P060352</t>
+        </is>
+      </c>
+      <c r="D41" s="49" t="inlineStr">
+        <is>
+          <t>18.86 %w/w (U 1.16 %w/w, k=2)</t>
+        </is>
+      </c>
+      <c r="E41" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F41" s="49" t="inlineStr">
+        <is>
+          <t>197-7-К/26</t>
+        </is>
+      </c>
+      <c r="G41" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H41" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I41" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="19.5" customHeight="1">
+      <c r="A42" s="46" t="inlineStr">
+        <is>
+          <t>Gorilla Glue      7 batch(es)      Total Δ⁹-THC across batches: 15.35 – 18.98 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="50" t="n">
+        <v>24</v>
+      </c>
+      <c r="B43" s="51" t="inlineStr">
+        <is>
+          <t>GG1024_01</t>
+        </is>
+      </c>
+      <c r="C43" s="52" t="inlineStr">
+        <is>
+          <t>P050092</t>
+        </is>
+      </c>
+      <c r="D43" s="52" t="inlineStr">
+        <is>
+          <t>17.22%</t>
+        </is>
+      </c>
+      <c r="E43" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F43" s="52" t="inlineStr">
+        <is>
+          <t>ППК25104</t>
+        </is>
+      </c>
+      <c r="G43" s="52" t="inlineStr">
+        <is>
+          <t>17.04.2025</t>
+        </is>
+      </c>
+      <c r="H43" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I43" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="53" t="n"/>
+      <c r="B44" s="53" t="n"/>
+      <c r="C44" s="53" t="n"/>
+      <c r="D44" s="49" t="inlineStr">
+        <is>
+          <t>18.67 %w/w (U 1.15)</t>
+        </is>
+      </c>
+      <c r="E44" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F44" s="49" t="inlineStr">
+        <is>
+          <t>197-9-К/26</t>
+        </is>
+      </c>
+      <c r="G44" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H44" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I44" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="47" t="n">
+        <v>25</v>
+      </c>
+      <c r="B45" s="48" t="inlineStr">
+        <is>
+          <t>GG1024_02</t>
+        </is>
+      </c>
+      <c r="C45" s="49" t="inlineStr">
+        <is>
+          <t>P050012</t>
+        </is>
+      </c>
+      <c r="D45" s="49" t="inlineStr">
+        <is>
+          <t>15.95%</t>
+        </is>
+      </c>
+      <c r="E45" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F45" s="49" t="inlineStr">
+        <is>
+          <t>ППК25140</t>
+        </is>
+      </c>
+      <c r="G45" s="49" t="inlineStr">
+        <is>
+          <t>22.05.2025</t>
+        </is>
+      </c>
+      <c r="H45" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I45" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="47" t="n">
+        <v>26</v>
+      </c>
+      <c r="B46" s="48" t="inlineStr">
+        <is>
+          <t>GG012601</t>
+        </is>
+      </c>
+      <c r="C46" s="49" t="n"/>
+      <c r="D46" s="49" t="inlineStr">
+        <is>
+          <t>15.35%</t>
+        </is>
+      </c>
+      <c r="E46" s="49" t="n"/>
+      <c r="F46" s="49" t="inlineStr">
+        <is>
+          <t>ППК26062</t>
+        </is>
+      </c>
+      <c r="G46" s="49" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H46" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I46" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="47" t="n">
+        <v>27</v>
+      </c>
+      <c r="B47" s="48" t="inlineStr">
+        <is>
+          <t>GG112501</t>
+        </is>
+      </c>
+      <c r="C47" s="49" t="n"/>
+      <c r="D47" s="49" t="inlineStr">
+        <is>
+          <t>17.94%</t>
+        </is>
+      </c>
+      <c r="E47" s="49" t="n"/>
+      <c r="F47" s="49" t="inlineStr">
+        <is>
+          <t>ППК26061</t>
+        </is>
+      </c>
+      <c r="G47" s="49" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H47" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I47" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="47" t="n">
+        <v>28</v>
+      </c>
+      <c r="B48" s="48" t="inlineStr">
+        <is>
+          <t>GG012603</t>
+        </is>
+      </c>
+      <c r="C48" s="49" t="n"/>
+      <c r="D48" s="49" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="E48" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F48" s="49" t="inlineStr">
+        <is>
+          <t>ППК26114</t>
+        </is>
+      </c>
+      <c r="G48" s="49" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="H48" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I48" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="47" t="n">
+        <v>29</v>
+      </c>
+      <c r="B49" s="48" t="inlineStr">
+        <is>
+          <t>GG032601</t>
+        </is>
+      </c>
+      <c r="C49" s="49" t="n"/>
+      <c r="D49" s="49" t="inlineStr">
+        <is>
+          <t>18.98%</t>
+        </is>
+      </c>
+      <c r="E49" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F49" s="49" t="inlineStr">
+        <is>
+          <t>ППК26128</t>
+        </is>
+      </c>
+      <c r="G49" s="49" t="inlineStr">
+        <is>
+          <t>21.07.2026</t>
+        </is>
+      </c>
+      <c r="H49" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I49" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="B50" s="48" t="inlineStr">
+        <is>
+          <t>P060402</t>
+        </is>
+      </c>
+      <c r="C50" s="49" t="inlineStr">
+        <is>
+          <t>P060402</t>
+        </is>
+      </c>
+      <c r="D50" s="49" t="inlineStr">
+        <is>
+          <t>16.70 %w/w (U 1.03 %w/w, k=2)</t>
+        </is>
+      </c>
+      <c r="E50" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F50" s="49" t="inlineStr">
+        <is>
+          <t>197-8-К/26</t>
+        </is>
+      </c>
+      <c r="G50" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H50" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I50" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="19.5" customHeight="1">
+      <c r="A51" s="46" t="inlineStr">
+        <is>
+          <t>Grape Pie      13 batch(es)      Total Δ⁹-THC across batches: 14.83 – 26.32 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="47" t="n">
+        <v>31</v>
+      </c>
+      <c r="B52" s="48" t="inlineStr">
+        <is>
+          <t>GP0824_01</t>
+        </is>
+      </c>
+      <c r="C52" s="49" t="inlineStr">
+        <is>
+          <t>P050102</t>
+        </is>
+      </c>
+      <c r="D52" s="49" t="inlineStr">
+        <is>
+          <t>20.79%</t>
+        </is>
+      </c>
+      <c r="E52" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F52" s="49" t="inlineStr">
+        <is>
+          <t>ППК25105</t>
+        </is>
+      </c>
+      <c r="G52" s="49" t="inlineStr">
+        <is>
+          <t>17.04.2025</t>
+        </is>
+      </c>
+      <c r="H52" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I52" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="50" t="n">
+        <v>32</v>
+      </c>
+      <c r="B53" s="51" t="inlineStr">
+        <is>
+          <t>GP0824_02</t>
+        </is>
+      </c>
+      <c r="C53" s="52" t="inlineStr">
+        <is>
+          <t>P050022</t>
+        </is>
+      </c>
+      <c r="D53" s="52" t="inlineStr">
+        <is>
+          <t>23.19%</t>
+        </is>
+      </c>
+      <c r="E53" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F53" s="52" t="inlineStr">
+        <is>
+          <t>ППК25174</t>
+        </is>
+      </c>
+      <c r="G53" s="52" t="inlineStr">
+        <is>
+          <t>10.07.2025</t>
+        </is>
+      </c>
+      <c r="H53" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I53" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="53" t="n"/>
+      <c r="B54" s="53" t="n"/>
+      <c r="C54" s="53" t="n"/>
+      <c r="D54" s="49" t="inlineStr">
+        <is>
+          <t>22.61 %w/w (U 1.39)</t>
+        </is>
+      </c>
+      <c r="E54" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F54" s="49" t="inlineStr">
+        <is>
+          <t>197-11-К/26</t>
+        </is>
+      </c>
+      <c r="G54" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H54" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I54" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="47" t="n">
+        <v>33</v>
+      </c>
+      <c r="B55" s="48" t="inlineStr">
+        <is>
+          <t>GP0824_03</t>
+        </is>
+      </c>
+      <c r="C55" s="49" t="inlineStr">
+        <is>
+          <t>P050072</t>
+        </is>
+      </c>
+      <c r="D55" s="49" t="inlineStr">
+        <is>
+          <t>25.45%</t>
+        </is>
+      </c>
+      <c r="E55" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F55" s="49" t="inlineStr">
+        <is>
+          <t>ППК25175</t>
+        </is>
+      </c>
+      <c r="G55" s="49" t="inlineStr">
+        <is>
+          <t>10.07.2025</t>
+        </is>
+      </c>
+      <c r="H55" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I55" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="50" t="n">
+        <v>34</v>
+      </c>
+      <c r="B56" s="51" t="inlineStr">
+        <is>
+          <t>GP052501</t>
+        </is>
+      </c>
+      <c r="C56" s="52" t="inlineStr">
+        <is>
+          <t>P050152</t>
+        </is>
+      </c>
+      <c r="D56" s="52" t="inlineStr">
+        <is>
+          <t>18.98%</t>
+        </is>
+      </c>
+      <c r="E56" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F56" s="52" t="inlineStr">
+        <is>
+          <t>ППК25279</t>
+        </is>
+      </c>
+      <c r="G56" s="52" t="inlineStr">
+        <is>
+          <t>19.09.2025</t>
+        </is>
+      </c>
+      <c r="H56" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I56" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="53" t="n"/>
+      <c r="B57" s="53" t="n"/>
+      <c r="C57" s="53" t="n"/>
+      <c r="D57" s="49" t="inlineStr">
+        <is>
+          <t>18.52 %w/w (U 1.14)</t>
+        </is>
+      </c>
+      <c r="E57" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F57" s="49" t="inlineStr">
+        <is>
+          <t>197-10-К/26</t>
+        </is>
+      </c>
+      <c r="G57" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H57" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I57" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="47" t="n">
+        <v>35</v>
+      </c>
+      <c r="B58" s="48" t="inlineStr">
+        <is>
+          <t>GP062501</t>
+        </is>
+      </c>
+      <c r="C58" s="49" t="inlineStr">
+        <is>
+          <t>P050202</t>
+        </is>
+      </c>
+      <c r="D58" s="49" t="inlineStr">
+        <is>
+          <t>24.89%</t>
+        </is>
+      </c>
+      <c r="E58" s="49" t="inlineStr">
+        <is>
+          <t>19.8 – 24.2 %</t>
+        </is>
+      </c>
+      <c r="F58" s="49" t="inlineStr">
+        <is>
+          <t>In-house HPLC cross-check NPCCC/SCP-02, NGP/QCG/SOP-024</t>
+        </is>
+      </c>
+      <c r="G58" s="49" t="inlineStr">
+        <is>
+          <t>28.11.2025</t>
+        </is>
+      </c>
+      <c r="H58" s="49" t="inlineStr">
+        <is>
+          <t>Purely Plant (in-house)</t>
+        </is>
+      </c>
+      <c r="I58" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="47" t="n">
+        <v>36</v>
+      </c>
+      <c r="B59" s="48" t="inlineStr">
+        <is>
+          <t>GP072501-1</t>
+        </is>
+      </c>
+      <c r="C59" s="49" t="inlineStr">
+        <is>
+          <t>P050292</t>
+        </is>
+      </c>
+      <c r="D59" s="49" t="inlineStr">
+        <is>
+          <t>21.36%</t>
+        </is>
+      </c>
+      <c r="E59" s="49" t="inlineStr">
+        <is>
+          <t>19.2 – 23.4 %</t>
+        </is>
+      </c>
+      <c r="F59" s="49" t="inlineStr">
+        <is>
+          <t>PP CoA #018 / ППК25378</t>
+        </is>
+      </c>
+      <c r="G59" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H59" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I59" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="47" t="n">
+        <v>37</v>
+      </c>
+      <c r="B60" s="48" t="inlineStr">
+        <is>
+          <t>GP072501-2</t>
+        </is>
+      </c>
+      <c r="C60" s="49" t="inlineStr">
+        <is>
+          <t>P050302</t>
+        </is>
+      </c>
+      <c r="D60" s="49" t="inlineStr">
+        <is>
+          <t>19.81%</t>
+        </is>
+      </c>
+      <c r="E60" s="49" t="inlineStr">
+        <is>
+          <t>17.8 – 21.7 %</t>
+        </is>
+      </c>
+      <c r="F60" s="49" t="inlineStr">
+        <is>
+          <t>PP CoA #019 / ППК25379</t>
+        </is>
+      </c>
+      <c r="G60" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H60" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I60" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="47" t="n">
+        <v>38</v>
+      </c>
+      <c r="B61" s="48" t="inlineStr">
+        <is>
+          <t>GP082501-1</t>
+        </is>
+      </c>
+      <c r="C61" s="49" t="inlineStr">
+        <is>
+          <t>P050312</t>
+        </is>
+      </c>
+      <c r="D61" s="49" t="inlineStr">
+        <is>
+          <t>21.29%</t>
+        </is>
+      </c>
+      <c r="E61" s="49" t="inlineStr">
+        <is>
+          <t>19.1 – 23.4 %</t>
+        </is>
+      </c>
+      <c r="F61" s="49" t="inlineStr">
+        <is>
+          <t>PP CoA #020 / ППК25380</t>
+        </is>
+      </c>
+      <c r="G61" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H61" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I61" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="50" t="n">
+        <v>39</v>
+      </c>
+      <c r="B62" s="51" t="inlineStr">
+        <is>
+          <t>GP082501-2</t>
+        </is>
+      </c>
+      <c r="C62" s="52" t="inlineStr">
+        <is>
+          <t>P050322</t>
+        </is>
+      </c>
+      <c r="D62" s="52" t="inlineStr">
+        <is>
+          <t>14.83%</t>
+        </is>
+      </c>
+      <c r="E62" s="52" t="inlineStr">
+        <is>
+          <t>13.3 – 16.3 %</t>
+        </is>
+      </c>
+      <c r="F62" s="52" t="inlineStr">
+        <is>
+          <t>PP CoA #021 / ППК25381</t>
+        </is>
+      </c>
+      <c r="G62" s="52" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H62" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I62" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="53" t="n"/>
+      <c r="B63" s="53" t="n"/>
+      <c r="C63" s="53" t="n"/>
+      <c r="D63" s="49" t="inlineStr">
+        <is>
+          <t>15.70% w/w (U 0.96% w/w)</t>
+        </is>
+      </c>
+      <c r="E63" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F63" s="49" t="inlineStr">
+        <is>
+          <t>197-12-К/26</t>
+        </is>
+      </c>
+      <c r="G63" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H63" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I63" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="47" t="n">
+        <v>40</v>
+      </c>
+      <c r="B64" s="48" t="inlineStr">
+        <is>
+          <t>GP092501</t>
+        </is>
+      </c>
+      <c r="C64" s="49" t="inlineStr">
+        <is>
+          <t>P060092</t>
+        </is>
+      </c>
+      <c r="D64" s="49" t="inlineStr">
+        <is>
+          <t>25.73%</t>
+        </is>
+      </c>
+      <c r="E64" s="49" t="inlineStr">
+        <is>
+          <t>23.15 – 28.3 %</t>
+        </is>
+      </c>
+      <c r="F64" s="49" t="inlineStr">
+        <is>
+          <t>ППК26009</t>
+        </is>
+      </c>
+      <c r="G64" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H64" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I64" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="47" t="n">
+        <v>41</v>
+      </c>
+      <c r="B65" s="48" t="inlineStr">
+        <is>
+          <t>P160012</t>
+        </is>
+      </c>
+      <c r="C65" s="49" t="inlineStr">
+        <is>
+          <t>P160012</t>
+        </is>
+      </c>
+      <c r="D65" s="49" t="inlineStr">
+        <is>
+          <t>26.32%</t>
+        </is>
+      </c>
+      <c r="E65" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F65" s="49" t="inlineStr">
+        <is>
+          <t>ППК26117</t>
+        </is>
+      </c>
+      <c r="G65" s="49" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="H65" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I65" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="47" t="n">
+        <v>42</v>
+      </c>
+      <c r="B66" s="48" t="inlineStr">
+        <is>
+          <t>P160022</t>
+        </is>
+      </c>
+      <c r="C66" s="49" t="inlineStr">
+        <is>
+          <t>P160022</t>
+        </is>
+      </c>
+      <c r="D66" s="49" t="inlineStr">
+        <is>
+          <t>25.72%</t>
+        </is>
+      </c>
+      <c r="E66" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F66" s="49" t="inlineStr">
+        <is>
+          <t>ППК26118</t>
+        </is>
+      </c>
+      <c r="G66" s="49" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="H66" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I66" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="47" t="n">
+        <v>43</v>
+      </c>
+      <c r="B67" s="48" t="inlineStr">
+        <is>
+          <t>P160032</t>
+        </is>
+      </c>
+      <c r="C67" s="49" t="inlineStr">
+        <is>
+          <t>P160032</t>
+        </is>
+      </c>
+      <c r="D67" s="49" t="inlineStr">
+        <is>
+          <t>24.78%</t>
+        </is>
+      </c>
+      <c r="E67" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F67" s="49" t="inlineStr">
+        <is>
+          <t>ППК26119</t>
+        </is>
+      </c>
+      <c r="G67" s="49" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="H67" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I67" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="19.5" customHeight="1">
+      <c r="A68" s="46" t="inlineStr">
+        <is>
+          <t>Graps &amp; Creme      1 batch(es)      Total Δ⁹-THC across batches: 11.53 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="47" t="n">
+        <v>44</v>
+      </c>
+      <c r="B69" s="48" t="inlineStr">
+        <is>
+          <t>GRC102501-2</t>
+        </is>
+      </c>
+      <c r="C69" s="49" t="n"/>
+      <c r="D69" s="49" t="inlineStr">
+        <is>
+          <t>11.53 %w/w (U ±0.71)</t>
+        </is>
+      </c>
+      <c r="E69" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F69" s="49" t="inlineStr">
+        <is>
+          <t>051-6-K/26</t>
+        </is>
+      </c>
+      <c r="G69" s="49" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="H69" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I69" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="19.5" customHeight="1">
+      <c r="A70" s="46" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia      3 batch(es)      Total Δ⁹-THC across batches: 14.97 – 22.43 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="50" t="n">
+        <v>45</v>
+      </c>
+      <c r="B71" s="51" t="inlineStr">
         <is>
           <t>HPA1024_01</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CBD (%)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>24.70</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="G5" s="45" t="inlineStr">
-        <is>
-          <t>CoA P050052 (HPA1024_01): 'Vkupno CBD*** = 0.10'. The recorded 24.70 is the Delta9-THCA content from the same table (wrong-column entry). Confirmed in BOTH eCoA sources.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Pending QC approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>H9</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>BG1024</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CBN (%)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="G6" s="45" t="inlineStr">
-        <is>
-          <t>CoA BG1024 (PPK25050) and the full-panel bundle both state 'CBN 0.02%'. Transcription error.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Pending QC approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>U31</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="C71" s="52" t="inlineStr">
+        <is>
+          <t>P050052</t>
+        </is>
+      </c>
+      <c r="D71" s="52" t="inlineStr">
+        <is>
+          <t>22.43%</t>
+        </is>
+      </c>
+      <c r="E71" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F71" s="52" t="inlineStr">
+        <is>
+          <t>НИК22155 (likely OCR misread of ППК25xxx)</t>
+        </is>
+      </c>
+      <c r="G71" s="52" t="inlineStr">
+        <is>
+          <t>24.06.2025</t>
+        </is>
+      </c>
+      <c r="H71" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I71" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="53" t="n"/>
+      <c r="B72" s="53" t="n"/>
+      <c r="C72" s="53" t="n"/>
+      <c r="D72" s="49" t="inlineStr">
+        <is>
+          <t>21.61 %w/w (U 1.33)</t>
+        </is>
+      </c>
+      <c r="E72" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F72" s="49" t="inlineStr">
+        <is>
+          <t>197-14-К/26</t>
+        </is>
+      </c>
+      <c r="G72" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H72" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I72" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B73" s="48" t="inlineStr">
+        <is>
+          <t>HPA052501</t>
+        </is>
+      </c>
+      <c r="C73" s="49" t="inlineStr">
+        <is>
+          <t>P050182</t>
+        </is>
+      </c>
+      <c r="D73" s="49" t="inlineStr">
+        <is>
+          <t>20.39%</t>
+        </is>
+      </c>
+      <c r="E73" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F73" s="49" t="inlineStr">
+        <is>
+          <t>ППК25278</t>
+        </is>
+      </c>
+      <c r="G73" s="49" t="inlineStr">
+        <is>
+          <t>19.09.2025</t>
+        </is>
+      </c>
+      <c r="H73" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I73" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="50" t="n">
+        <v>47</v>
+      </c>
+      <c r="B74" s="51" t="inlineStr">
+        <is>
+          <t>HPA1024</t>
+        </is>
+      </c>
+      <c r="C74" s="52" t="n"/>
+      <c r="D74" s="52" t="inlineStr">
+        <is>
+          <t>14.97%</t>
+        </is>
+      </c>
+      <c r="E74" s="52" t="inlineStr">
+        <is>
+          <t>12.6 – 15.4 %</t>
+        </is>
+      </c>
+      <c r="F74" s="52" t="inlineStr">
+        <is>
+          <t>n/a — Purely Plant in-house CoA (Batch HPA1024, no certificate/report number printed)</t>
+        </is>
+      </c>
+      <c r="G74" s="52" t="inlineStr">
+        <is>
+          <t>23.01.2025</t>
+        </is>
+      </c>
+      <c r="H74" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I74" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="53" t="n"/>
+      <c r="B75" s="53" t="n"/>
+      <c r="C75" s="53" t="n"/>
+      <c r="D75" s="49" t="inlineStr">
+        <is>
+          <t>17.31 %w/w (U 1.06 %w/w, k=2)</t>
+        </is>
+      </c>
+      <c r="E75" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F75" s="49" t="inlineStr">
+        <is>
+          <t>197-13-К/26</t>
+        </is>
+      </c>
+      <c r="G75" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H75" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I75" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="19.5" customHeight="1">
+      <c r="A76" s="46" t="inlineStr">
+        <is>
+          <t>Jelly Donutz      6 batch(es)      Total Δ⁹-THC across batches: 13.93 – 20.54 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="47" t="n">
+        <v>48</v>
+      </c>
+      <c r="B77" s="48" t="inlineStr">
+        <is>
+          <t>JD012601</t>
+        </is>
+      </c>
+      <c r="C77" s="49" t="n"/>
+      <c r="D77" s="49" t="inlineStr">
+        <is>
+          <t>18.16%</t>
+        </is>
+      </c>
+      <c r="E77" s="49" t="n"/>
+      <c r="F77" s="49" t="inlineStr">
+        <is>
+          <t>ППК26064</t>
+        </is>
+      </c>
+      <c r="G77" s="49" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H77" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I77" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B78" s="51" t="inlineStr">
+        <is>
+          <t>JD112501</t>
+        </is>
+      </c>
+      <c r="C78" s="52" t="n"/>
+      <c r="D78" s="52" t="inlineStr">
+        <is>
+          <t>19.64%</t>
+        </is>
+      </c>
+      <c r="E78" s="52" t="n"/>
+      <c r="F78" s="52" t="inlineStr">
+        <is>
+          <t>ППК26063</t>
+        </is>
+      </c>
+      <c r="G78" s="52" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H78" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I78" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="53" t="n"/>
+      <c r="B79" s="53" t="n"/>
+      <c r="C79" s="53" t="n"/>
+      <c r="D79" s="49" t="inlineStr">
+        <is>
+          <t>13.93%</t>
+        </is>
+      </c>
+      <c r="E79" s="49" t="n"/>
+      <c r="F79" s="49" t="inlineStr">
+        <is>
+          <t>ППК26065</t>
+        </is>
+      </c>
+      <c r="G79" s="49" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H79" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I79" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="47" t="n">
+        <v>50</v>
+      </c>
+      <c r="B80" s="48" t="inlineStr">
+        <is>
+          <t>JD012603-02</t>
+        </is>
+      </c>
+      <c r="C80" s="49" t="n"/>
+      <c r="D80" s="49" t="inlineStr">
+        <is>
+          <t>20.54%</t>
+        </is>
+      </c>
+      <c r="E80" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F80" s="49" t="inlineStr">
+        <is>
+          <t>ППК26113</t>
+        </is>
+      </c>
+      <c r="G80" s="49" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="H80" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I80" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="47" t="n">
+        <v>51</v>
+      </c>
+      <c r="B81" s="48" t="inlineStr">
+        <is>
+          <t>JD012603-02V</t>
+        </is>
+      </c>
+      <c r="C81" s="49" t="n"/>
+      <c r="D81" s="49" t="inlineStr">
+        <is>
+          <t>15.16%</t>
+        </is>
+      </c>
+      <c r="E81" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F81" s="49" t="inlineStr">
+        <is>
+          <t>ППК26111</t>
+        </is>
+      </c>
+      <c r="G81" s="49" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="H81" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I81" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="47" t="n">
+        <v>52</v>
+      </c>
+      <c r="B82" s="48" t="inlineStr">
+        <is>
+          <t>JD022601</t>
+        </is>
+      </c>
+      <c r="C82" s="49" t="n"/>
+      <c r="D82" s="49" t="inlineStr">
+        <is>
+          <t>18.58%</t>
+        </is>
+      </c>
+      <c r="E82" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F82" s="49" t="inlineStr">
+        <is>
+          <t>ППК26115</t>
+        </is>
+      </c>
+      <c r="G82" s="49" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="H82" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I82" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="47" t="n">
+        <v>53</v>
+      </c>
+      <c r="B83" s="48" t="inlineStr">
+        <is>
+          <t>P060212</t>
+        </is>
+      </c>
+      <c r="C83" s="49" t="inlineStr">
+        <is>
+          <t>P060212</t>
+        </is>
+      </c>
+      <c r="D83" s="49" t="inlineStr">
+        <is>
+          <t>20.32 %w/w (U 1.25 %w/w, k=2)</t>
+        </is>
+      </c>
+      <c r="E83" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F83" s="49" t="inlineStr">
+        <is>
+          <t>197-15-К/26</t>
+        </is>
+      </c>
+      <c r="G83" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H83" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I83" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="19.5" customHeight="1">
+      <c r="A84" s="46" t="inlineStr">
+        <is>
+          <t>Jokerz 31      4 batch(es)      Total Δ⁹-THC across batches: 17.32 – 25.27 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="47" t="n">
+        <v>54</v>
+      </c>
+      <c r="B85" s="48" t="inlineStr">
+        <is>
+          <t>J31102501</t>
+        </is>
+      </c>
+      <c r="C85" s="49" t="n"/>
+      <c r="D85" s="49" t="inlineStr">
+        <is>
+          <t>19.14 %w/w (U ±1.18)</t>
+        </is>
+      </c>
+      <c r="E85" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F85" s="49" t="inlineStr">
+        <is>
+          <t>051-1-K/26</t>
+        </is>
+      </c>
+      <c r="G85" s="49" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="H85" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I85" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="50" t="n">
+        <v>55</v>
+      </c>
+      <c r="B86" s="51" t="inlineStr">
+        <is>
+          <t>J31112501</t>
+        </is>
+      </c>
+      <c r="C86" s="52" t="n"/>
+      <c r="D86" s="52" t="inlineStr">
+        <is>
+          <t>25.27 %w/w (U ±1.55)</t>
+        </is>
+      </c>
+      <c r="E86" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F86" s="52" t="inlineStr">
+        <is>
+          <t>051-5-K/26</t>
+        </is>
+      </c>
+      <c r="G86" s="52" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="H86" s="52" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I86" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="53" t="n"/>
+      <c r="B87" s="53" t="n"/>
+      <c r="C87" s="53" t="n"/>
+      <c r="D87" s="49" t="inlineStr">
+        <is>
+          <t>20.21 %w/w (U ±1.24)</t>
+        </is>
+      </c>
+      <c r="E87" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F87" s="49" t="inlineStr">
+        <is>
+          <t>100-1-K/26</t>
+        </is>
+      </c>
+      <c r="G87" s="49" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="H87" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I87" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="50" t="n">
+        <v>56</v>
+      </c>
+      <c r="B88" s="51" t="inlineStr">
+        <is>
+          <t>J31122501</t>
+        </is>
+      </c>
+      <c r="C88" s="52" t="n"/>
+      <c r="D88" s="52" t="inlineStr">
+        <is>
+          <t>19.84 %w/w (U ±1.22)</t>
+        </is>
+      </c>
+      <c r="E88" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F88" s="52" t="inlineStr">
+        <is>
+          <t>100-2-К/26</t>
+        </is>
+      </c>
+      <c r="G88" s="52" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="H88" s="52" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I88" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="53" t="n"/>
+      <c r="B89" s="53" t="n"/>
+      <c r="C89" s="53" t="n"/>
+      <c r="D89" s="49" t="inlineStr">
+        <is>
+          <t>21.84 %w/w (U ±1.34)</t>
+        </is>
+      </c>
+      <c r="E89" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F89" s="49" t="inlineStr">
+        <is>
+          <t>100-3-К/26</t>
+        </is>
+      </c>
+      <c r="G89" s="49" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="H89" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I89" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="47" t="n">
+        <v>57</v>
+      </c>
+      <c r="B90" s="48" t="inlineStr">
+        <is>
+          <t>P060152</t>
+        </is>
+      </c>
+      <c r="C90" s="49" t="inlineStr">
+        <is>
+          <t>P060152</t>
+        </is>
+      </c>
+      <c r="D90" s="49" t="inlineStr">
+        <is>
+          <t>17.32 %w/w (U 1.06 %w/w, k=2)</t>
+        </is>
+      </c>
+      <c r="E90" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F90" s="49" t="inlineStr">
+        <is>
+          <t>197-16-К/26</t>
+        </is>
+      </c>
+      <c r="G90" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H90" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I90" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="19.5" customHeight="1">
+      <c r="A91" s="46" t="inlineStr">
+        <is>
+          <t>Kush Crasher      1 batch(es)      Total Δ⁹-THC across batches: 17.04 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="47" t="n">
+        <v>58</v>
+      </c>
+      <c r="B92" s="48" t="inlineStr">
+        <is>
+          <t>KC102501</t>
+        </is>
+      </c>
+      <c r="C92" s="49" t="n"/>
+      <c r="D92" s="49" t="inlineStr">
+        <is>
+          <t>17.04 %w/w (U ±1.05)</t>
+        </is>
+      </c>
+      <c r="E92" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F92" s="49" t="inlineStr">
+        <is>
+          <t>051-4-K/26</t>
+        </is>
+      </c>
+      <c r="G92" s="49" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="H92" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I92" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="19.5" customHeight="1">
+      <c r="A93" s="46" t="inlineStr">
+        <is>
+          <t>Motor Breath      2 batch(es)      Total Δ⁹-THC across batches: 16.82 – 18.67 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="47" t="n">
+        <v>59</v>
+      </c>
+      <c r="B94" s="48" t="inlineStr">
+        <is>
+          <t>MB0824_04</t>
+        </is>
+      </c>
+      <c r="C94" s="49" t="inlineStr">
+        <is>
+          <t>P050032</t>
+        </is>
+      </c>
+      <c r="D94" s="49" t="inlineStr">
+        <is>
+          <t>18.67%</t>
+        </is>
+      </c>
+      <c r="E94" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F94" s="49" t="inlineStr">
+        <is>
+          <t>ППК25118</t>
+        </is>
+      </c>
+      <c r="G94" s="49" t="inlineStr">
+        <is>
+          <t>06.05.2025</t>
+        </is>
+      </c>
+      <c r="H94" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I94" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="47" t="n">
+        <v>60</v>
+      </c>
+      <c r="B95" s="48" t="inlineStr">
+        <is>
+          <t>MB0824_05</t>
+        </is>
+      </c>
+      <c r="C95" s="49" t="inlineStr">
+        <is>
+          <t>P050112</t>
+        </is>
+      </c>
+      <c r="D95" s="49" t="inlineStr">
+        <is>
+          <t>16.82%</t>
+        </is>
+      </c>
+      <c r="E95" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F95" s="49" t="inlineStr">
+        <is>
+          <t>ППК25211</t>
+        </is>
+      </c>
+      <c r="G95" s="49" t="inlineStr">
+        <is>
+          <t>28.07.2025</t>
+        </is>
+      </c>
+      <c r="H95" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I95" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="19.5" customHeight="1">
+      <c r="A96" s="46" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa      9 batch(es)      Total Δ⁹-THC across batches: 7.91 – 20.03 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="47" t="n">
+        <v>61</v>
+      </c>
+      <c r="B97" s="48" t="inlineStr">
         <is>
           <t>OPM1024_01</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Hg (mg/kg)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.011</t>
-        </is>
-      </c>
-      <c r="G7" s="45" t="inlineStr">
-        <is>
-          <t>CoA P050042 (OPM1024_01): 'Mercury: &lt; 0.1 mg/kg | 0.011 mg/kg'. Decimal-place error (10x low).</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Pending QC approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>H285</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>HPA1024</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CBN (%)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>N.D.</t>
-        </is>
-      </c>
-      <c r="G8" s="45" t="inlineStr">
-        <is>
-          <t>CoA HPA1024 (bulk): 'Related substances** - Cannabinol | &lt; 1.0% | N.D.'. Recorded value not supported by the CoA.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Pending QC approval</t>
+      <c r="C97" s="49" t="inlineStr">
+        <is>
+          <t>P050042</t>
+        </is>
+      </c>
+      <c r="D97" s="49" t="inlineStr">
+        <is>
+          <t>15.38%</t>
+        </is>
+      </c>
+      <c r="E97" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F97" s="49" t="inlineStr">
+        <is>
+          <t>ППК25117</t>
+        </is>
+      </c>
+      <c r="G97" s="49" t="inlineStr">
+        <is>
+          <t>06.05.2025</t>
+        </is>
+      </c>
+      <c r="H97" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I97" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="50" t="n">
+        <v>62</v>
+      </c>
+      <c r="B98" s="51" t="inlineStr">
+        <is>
+          <t>OPM1024_02</t>
+        </is>
+      </c>
+      <c r="C98" s="52" t="inlineStr">
+        <is>
+          <t>P050062</t>
+        </is>
+      </c>
+      <c r="D98" s="52" t="inlineStr">
+        <is>
+          <t>18.27%</t>
+        </is>
+      </c>
+      <c r="E98" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F98" s="52" t="inlineStr">
+        <is>
+          <t>ППК25154</t>
+        </is>
+      </c>
+      <c r="G98" s="52" t="inlineStr">
+        <is>
+          <t>24.06.2025</t>
+        </is>
+      </c>
+      <c r="H98" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I98" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="53" t="n"/>
+      <c r="B99" s="53" t="n"/>
+      <c r="C99" s="53" t="n"/>
+      <c r="D99" s="49" t="inlineStr">
+        <is>
+          <t>18.04 %w/w (U 1.11)</t>
+        </is>
+      </c>
+      <c r="E99" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F99" s="49" t="inlineStr">
+        <is>
+          <t>197-18-К/26</t>
+        </is>
+      </c>
+      <c r="G99" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H99" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I99" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="47" t="n">
+        <v>63</v>
+      </c>
+      <c r="B100" s="48" t="inlineStr">
+        <is>
+          <t>OPM1024_03</t>
+        </is>
+      </c>
+      <c r="C100" s="49" t="inlineStr">
+        <is>
+          <t>P050082</t>
+        </is>
+      </c>
+      <c r="D100" s="49" t="inlineStr">
+        <is>
+          <t>16.55%</t>
+        </is>
+      </c>
+      <c r="E100" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F100" s="49" t="inlineStr">
+        <is>
+          <t>ППК25210</t>
+        </is>
+      </c>
+      <c r="G100" s="49" t="inlineStr">
+        <is>
+          <t>28.07.2025</t>
+        </is>
+      </c>
+      <c r="H100" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I100" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="47" t="n">
+        <v>64</v>
+      </c>
+      <c r="B101" s="48" t="inlineStr">
+        <is>
+          <t>OPM052501</t>
+        </is>
+      </c>
+      <c r="C101" s="49" t="inlineStr">
+        <is>
+          <t>P050132</t>
+        </is>
+      </c>
+      <c r="D101" s="49" t="inlineStr">
+        <is>
+          <t>14.16%</t>
+        </is>
+      </c>
+      <c r="E101" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F101" s="49" t="inlineStr">
+        <is>
+          <t>ППК25257</t>
+        </is>
+      </c>
+      <c r="G101" s="49" t="inlineStr">
+        <is>
+          <t>05.09.2025</t>
+        </is>
+      </c>
+      <c r="H101" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I101" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="47" t="n">
+        <v>65</v>
+      </c>
+      <c r="B102" s="48" t="inlineStr">
+        <is>
+          <t>OPM092501</t>
+        </is>
+      </c>
+      <c r="C102" s="49" t="inlineStr">
+        <is>
+          <t>P060042</t>
+        </is>
+      </c>
+      <c r="D102" s="49" t="inlineStr">
+        <is>
+          <t>9.43%</t>
+        </is>
+      </c>
+      <c r="E102" s="49" t="inlineStr">
+        <is>
+          <t>8.48 – 10.37 %</t>
+        </is>
+      </c>
+      <c r="F102" s="49" t="inlineStr">
+        <is>
+          <t>ППК26008</t>
+        </is>
+      </c>
+      <c r="G102" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H102" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I102" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="47" t="n">
+        <v>66</v>
+      </c>
+      <c r="B103" s="48" t="inlineStr">
+        <is>
+          <t>OPM112501</t>
+        </is>
+      </c>
+      <c r="C103" s="49" t="n"/>
+      <c r="D103" s="49" t="inlineStr">
+        <is>
+          <t>8.00%</t>
+        </is>
+      </c>
+      <c r="E103" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F103" s="49" t="inlineStr">
+        <is>
+          <t>ППК26031</t>
+        </is>
+      </c>
+      <c r="G103" s="49" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="H103" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I103" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="47" t="n">
+        <v>67</v>
+      </c>
+      <c r="B104" s="48" t="inlineStr">
+        <is>
+          <t>OPM122501</t>
+        </is>
+      </c>
+      <c r="C104" s="49" t="n"/>
+      <c r="D104" s="49" t="inlineStr">
+        <is>
+          <t>8.09 %w/w (U ±0.50)</t>
+        </is>
+      </c>
+      <c r="E104" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F104" s="49" t="inlineStr">
+        <is>
+          <t>100-4-К/26</t>
+        </is>
+      </c>
+      <c r="G104" s="49" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="H104" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I104" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="47" t="n">
+        <v>68</v>
+      </c>
+      <c r="B105" s="48" t="inlineStr">
+        <is>
+          <t>P060242</t>
+        </is>
+      </c>
+      <c r="C105" s="49" t="inlineStr">
+        <is>
+          <t>P060242</t>
+        </is>
+      </c>
+      <c r="D105" s="49" t="inlineStr">
+        <is>
+          <t>7.91 %w/w (U 0.49 %w/w, k=2)</t>
+        </is>
+      </c>
+      <c r="E105" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F105" s="49" t="inlineStr">
+        <is>
+          <t>197-19-К/26</t>
+        </is>
+      </c>
+      <c r="G105" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H105" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I105" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="50" t="n">
+        <v>69</v>
+      </c>
+      <c r="B106" s="51" t="inlineStr">
+        <is>
+          <t>OPM1024</t>
+        </is>
+      </c>
+      <c r="C106" s="52" t="n"/>
+      <c r="D106" s="52" t="inlineStr">
+        <is>
+          <t>19.96%</t>
+        </is>
+      </c>
+      <c r="E106" s="52" t="inlineStr">
+        <is>
+          <t>18.0 – 22.0 %</t>
+        </is>
+      </c>
+      <c r="F106" s="52" t="inlineStr">
+        <is>
+          <t>n/a — Purely Plant in-house CoA (Batch OPM1024, no certificate/report number printed)</t>
+        </is>
+      </c>
+      <c r="G106" s="52" t="inlineStr">
+        <is>
+          <t>23.04.2025</t>
+        </is>
+      </c>
+      <c r="H106" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I106" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="53" t="n"/>
+      <c r="B107" s="53" t="n"/>
+      <c r="C107" s="53" t="n"/>
+      <c r="D107" s="49" t="inlineStr">
+        <is>
+          <t>20.03 %w/w (U 1.23 %w/w, k=2)</t>
+        </is>
+      </c>
+      <c r="E107" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F107" s="49" t="inlineStr">
+        <is>
+          <t>197-17-К/26</t>
+        </is>
+      </c>
+      <c r="G107" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H107" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I107" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="19.5" customHeight="1">
+      <c r="A108" s="46" t="inlineStr">
+        <is>
+          <t>Permanent Market      3 batch(es)      Total Δ⁹-THC across batches: 10.01 – 14.06 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="47" t="n">
+        <v>70</v>
+      </c>
+      <c r="B109" s="48" t="inlineStr">
+        <is>
+          <t>PM072501</t>
+        </is>
+      </c>
+      <c r="C109" s="49" t="inlineStr">
+        <is>
+          <t>P050272</t>
+        </is>
+      </c>
+      <c r="D109" s="49" t="inlineStr">
+        <is>
+          <t>10.01%</t>
+        </is>
+      </c>
+      <c r="E109" s="49" t="inlineStr">
+        <is>
+          <t>9 – 11.01 %</t>
+        </is>
+      </c>
+      <c r="F109" s="49" t="inlineStr">
+        <is>
+          <t>ППК25368</t>
+        </is>
+      </c>
+      <c r="G109" s="49" t="inlineStr">
+        <is>
+          <t>28.11.2025</t>
+        </is>
+      </c>
+      <c r="H109" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I109" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="50" t="n">
+        <v>71</v>
+      </c>
+      <c r="B110" s="51" t="inlineStr">
+        <is>
+          <t>PM092501</t>
+        </is>
+      </c>
+      <c r="C110" s="52" t="inlineStr">
+        <is>
+          <t>P060062</t>
+        </is>
+      </c>
+      <c r="D110" s="52" t="inlineStr">
+        <is>
+          <t>14.06%</t>
+        </is>
+      </c>
+      <c r="E110" s="52" t="inlineStr">
+        <is>
+          <t>12.65 – 15.46 %</t>
+        </is>
+      </c>
+      <c r="F110" s="52" t="inlineStr">
+        <is>
+          <t>ППК26004</t>
+        </is>
+      </c>
+      <c r="G110" s="52" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H110" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I110" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="53" t="n"/>
+      <c r="B111" s="53" t="n"/>
+      <c r="C111" s="53" t="n"/>
+      <c r="D111" s="49" t="inlineStr">
+        <is>
+          <t>12.25% w/w (U 0.75% w/w)</t>
+        </is>
+      </c>
+      <c r="E111" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F111" s="49" t="inlineStr">
+        <is>
+          <t>197-20-К/26</t>
+        </is>
+      </c>
+      <c r="G111" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H111" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I111" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="47" t="n">
+        <v>72</v>
+      </c>
+      <c r="B112" s="48" t="inlineStr">
+        <is>
+          <t>PM112501</t>
+        </is>
+      </c>
+      <c r="C112" s="49" t="n"/>
+      <c r="D112" s="49" t="inlineStr">
+        <is>
+          <t>13.33%</t>
+        </is>
+      </c>
+      <c r="E112" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F112" s="49" t="inlineStr">
+        <is>
+          <t>ППК26030</t>
+        </is>
+      </c>
+      <c r="G112" s="49" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="H112" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I112" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="19.5" customHeight="1">
+      <c r="A113" s="46" t="inlineStr">
+        <is>
+          <t>Scrambler      3 batch(es)      Total Δ⁹-THC across batches: 17.13 – 21.92 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="47" t="n">
+        <v>73</v>
+      </c>
+      <c r="B114" s="48" t="inlineStr">
+        <is>
+          <t>SCR112501</t>
+        </is>
+      </c>
+      <c r="C114" s="49" t="n"/>
+      <c r="D114" s="49" t="inlineStr">
+        <is>
+          <t>17.13%</t>
+        </is>
+      </c>
+      <c r="E114" s="49" t="n"/>
+      <c r="F114" s="49" t="inlineStr">
+        <is>
+          <t>ППК26069</t>
+        </is>
+      </c>
+      <c r="G114" s="49" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H114" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I114" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="47" t="n">
+        <v>74</v>
+      </c>
+      <c r="B115" s="48" t="inlineStr">
+        <is>
+          <t>SCR022601</t>
+        </is>
+      </c>
+      <c r="C115" s="49" t="n"/>
+      <c r="D115" s="49" t="inlineStr">
+        <is>
+          <t>21.92%</t>
+        </is>
+      </c>
+      <c r="E115" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F115" s="49" t="inlineStr">
+        <is>
+          <t>ППК26116</t>
+        </is>
+      </c>
+      <c r="G115" s="49" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="H115" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I115" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="47" t="n">
+        <v>75</v>
+      </c>
+      <c r="B116" s="48" t="inlineStr">
+        <is>
+          <t>P060382</t>
+        </is>
+      </c>
+      <c r="C116" s="49" t="inlineStr">
+        <is>
+          <t>P060382</t>
+        </is>
+      </c>
+      <c r="D116" s="49" t="inlineStr">
+        <is>
+          <t>17.84 %w/w (U 1.10 %w/w, k=2)</t>
+        </is>
+      </c>
+      <c r="E116" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F116" s="49" t="inlineStr">
+        <is>
+          <t>197-21-К/26</t>
+        </is>
+      </c>
+      <c r="G116" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H116" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I116" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="19.5" customHeight="1">
+      <c r="A117" s="46" t="inlineStr">
+        <is>
+          <t>Sleepy Joy      3 batch(es)      Total Δ⁹-THC across batches: 9.20 – 11.20 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="47" t="n">
+        <v>76</v>
+      </c>
+      <c r="B118" s="48" t="inlineStr">
+        <is>
+          <t>SJ092501</t>
+        </is>
+      </c>
+      <c r="C118" s="49" t="inlineStr">
+        <is>
+          <t>P060082</t>
+        </is>
+      </c>
+      <c r="D118" s="49" t="inlineStr">
+        <is>
+          <t>10.96%</t>
+        </is>
+      </c>
+      <c r="E118" s="49" t="inlineStr">
+        <is>
+          <t>9.86 – 12.05 %</t>
+        </is>
+      </c>
+      <c r="F118" s="49" t="inlineStr">
+        <is>
+          <t>ППК26006</t>
+        </is>
+      </c>
+      <c r="G118" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H118" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I118" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="47" t="n">
+        <v>77</v>
+      </c>
+      <c r="B119" s="48" t="inlineStr">
+        <is>
+          <t>SJ102501</t>
+        </is>
+      </c>
+      <c r="C119" s="49" t="n"/>
+      <c r="D119" s="49" t="inlineStr">
+        <is>
+          <t>11.20 %w/w (U ±0.69)</t>
+        </is>
+      </c>
+      <c r="E119" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F119" s="49" t="inlineStr">
+        <is>
+          <t>051-3-K/26</t>
+        </is>
+      </c>
+      <c r="G119" s="49" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="H119" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I119" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="47" t="n">
+        <v>78</v>
+      </c>
+      <c r="B120" s="48" t="inlineStr">
+        <is>
+          <t>SJ112501</t>
+        </is>
+      </c>
+      <c r="C120" s="49" t="n"/>
+      <c r="D120" s="49" t="inlineStr">
+        <is>
+          <t>9.20 %w/w (U ±0.57)</t>
+        </is>
+      </c>
+      <c r="E120" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F120" s="49" t="inlineStr">
+        <is>
+          <t>051-2-K/26</t>
+        </is>
+      </c>
+      <c r="G120" s="49" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="H120" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I120" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="19.5" customHeight="1">
+      <c r="A121" s="46" t="inlineStr">
+        <is>
+          <t>Wedding Crasher      2 batch(es)      Total Δ⁹-THC across batches: 21.67 – 22.11 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="47" t="n">
+        <v>79</v>
+      </c>
+      <c r="B122" s="48" t="inlineStr">
+        <is>
+          <t>WC072501</t>
+        </is>
+      </c>
+      <c r="C122" s="49" t="inlineStr">
+        <is>
+          <t>P050262</t>
+        </is>
+      </c>
+      <c r="D122" s="49" t="inlineStr">
+        <is>
+          <t>22.11%</t>
+        </is>
+      </c>
+      <c r="E122" s="49" t="inlineStr">
+        <is>
+          <t>n/a (informational)</t>
+        </is>
+      </c>
+      <c r="F122" s="49" t="inlineStr">
+        <is>
+          <t>ППК25369</t>
+        </is>
+      </c>
+      <c r="G122" s="49" t="inlineStr">
+        <is>
+          <t>28.11.2025</t>
+        </is>
+      </c>
+      <c r="H122" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I122" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="47" t="n">
+        <v>80</v>
+      </c>
+      <c r="B123" s="48" t="inlineStr">
+        <is>
+          <t>WC082501</t>
+        </is>
+      </c>
+      <c r="C123" s="49" t="inlineStr">
+        <is>
+          <t>P060012</t>
+        </is>
+      </c>
+      <c r="D123" s="49" t="inlineStr">
+        <is>
+          <t>21.67%</t>
+        </is>
+      </c>
+      <c r="E123" s="49" t="inlineStr">
+        <is>
+          <t>19.5 – 23.83 %</t>
+        </is>
+      </c>
+      <c r="F123" s="49" t="inlineStr">
+        <is>
+          <t>ППК26001</t>
+        </is>
+      </c>
+      <c r="G123" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H123" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I123" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:H2"/>
+  <mergeCells count="75">
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A84:I84"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A108:I108"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="A113:I113"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="A91:I91"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A96:I96"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="C110:C111"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A117:I117"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="A93:I93"/>
+    <mergeCell ref="A121:I121"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B31:B32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/qc-corrections/PP_Batch_Release_QC_Register_CORRECTED.xlsx
+++ b/qc-corrections/PP_Batch_Release_QC_Register_CORRECTED.xlsx
@@ -35027,7 +35027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I123"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.300000000000001" customWidth="1" min="1" max="1"/>
@@ -35413,658 +35413,688 @@
     <row r="15" ht="19.5" customHeight="1">
       <c r="A15" s="46" t="inlineStr">
         <is>
-          <t>Cap Junkie      2 batch(es)      Total Δ⁹-THC across batches: 16.56 – 21.51 %</t>
+          <t>Cash Cow      2 batch(es)      Total Δ⁹-THC across batches: 13.35 – 17.67 %</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="50" t="n">
+      <c r="A16" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="B16" s="51" t="inlineStr">
+      <c r="B16" s="48" t="inlineStr">
+        <is>
+          <t>CC112501</t>
+        </is>
+      </c>
+      <c r="C16" s="49" t="n"/>
+      <c r="D16" s="49" t="inlineStr">
+        <is>
+          <t>13.35%</t>
+        </is>
+      </c>
+      <c r="E16" s="49" t="n"/>
+      <c r="F16" s="49" t="inlineStr">
+        <is>
+          <t>ППК26068</t>
+        </is>
+      </c>
+      <c r="G16" s="49" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H16" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I16" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B17" s="48" t="inlineStr">
+        <is>
+          <t>P060332</t>
+        </is>
+      </c>
+      <c r="C17" s="49" t="inlineStr">
+        <is>
+          <t>P060332</t>
+        </is>
+      </c>
+      <c r="D17" s="49" t="inlineStr">
+        <is>
+          <t>17.67 %w/w (U 1.09 %w/w, k=2)</t>
+        </is>
+      </c>
+      <c r="E17" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F17" s="49" t="inlineStr">
+        <is>
+          <t>197-6-К/26</t>
+        </is>
+      </c>
+      <c r="G17" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H17" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I17" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="19.5" customHeight="1">
+      <c r="A18" s="46" t="inlineStr">
+        <is>
+          <t>Clemosa a bud      1 batch(es)      Total Δ⁹-THC across batches: 8.02 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="47" t="n">
+        <v>8</v>
+      </c>
+      <c r="B19" s="48" t="inlineStr">
+        <is>
+          <t>CLE072501</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="inlineStr">
+        <is>
+          <t>P050282</t>
+        </is>
+      </c>
+      <c r="D19" s="49" t="inlineStr">
+        <is>
+          <t>8.02%</t>
+        </is>
+      </c>
+      <c r="E19" s="49" t="inlineStr">
+        <is>
+          <t>7.2 – 8.82 %</t>
+        </is>
+      </c>
+      <c r="F19" s="49" t="inlineStr">
+        <is>
+          <t>PP CoA #027 / ППК25370</t>
+        </is>
+      </c>
+      <c r="G19" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H19" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I19" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="46" t="inlineStr">
+        <is>
+          <t>Cup Junky      9 batch(es)      Total Δ⁹-THC across batches: 14.93 – 24.96 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>CJ1024</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="inlineStr">
+        <is>
+          <t>23.00%</t>
+        </is>
+      </c>
+      <c r="E21" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F21" s="49" t="inlineStr">
+        <is>
+          <t>ППК25052</t>
+        </is>
+      </c>
+      <c r="G21" s="49" t="inlineStr">
+        <is>
+          <t>26.02.2025</t>
+        </is>
+      </c>
+      <c r="H21" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I21" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" s="51" t="inlineStr">
+        <is>
+          <t>CJ052501-1</t>
+        </is>
+      </c>
+      <c r="C22" s="52" t="inlineStr">
+        <is>
+          <t>P050162</t>
+        </is>
+      </c>
+      <c r="D22" s="52" t="inlineStr">
+        <is>
+          <t>20.29%</t>
+        </is>
+      </c>
+      <c r="E22" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F22" s="52" t="inlineStr">
+        <is>
+          <t>ППК25280</t>
+        </is>
+      </c>
+      <c r="G22" s="52" t="inlineStr">
+        <is>
+          <t>17.09.2025</t>
+        </is>
+      </c>
+      <c r="H22" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I22" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="53" t="n"/>
+      <c r="B23" s="53" t="n"/>
+      <c r="C23" s="53" t="n"/>
+      <c r="D23" s="49" t="inlineStr">
+        <is>
+          <t>24.05 %w/w (U 1.48)</t>
+        </is>
+      </c>
+      <c r="E23" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F23" s="49" t="inlineStr">
+        <is>
+          <t>197-3-К/26</t>
+        </is>
+      </c>
+      <c r="G23" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H23" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I23" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>CJ052501-2</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="inlineStr">
+        <is>
+          <t>P050172</t>
+        </is>
+      </c>
+      <c r="D24" s="49" t="inlineStr">
+        <is>
+          <t>14.93%</t>
+        </is>
+      </c>
+      <c r="E24" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F24" s="49" t="inlineStr">
+        <is>
+          <t>ППК25281</t>
+        </is>
+      </c>
+      <c r="G24" s="49" t="inlineStr">
+        <is>
+          <t>17.09.2025</t>
+        </is>
+      </c>
+      <c r="H24" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I24" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="50" t="n">
+        <v>12</v>
+      </c>
+      <c r="B25" s="51" t="inlineStr">
         <is>
           <t>CJ062501-2</t>
         </is>
       </c>
-      <c r="C16" s="52" t="inlineStr">
+      <c r="C25" s="52" t="inlineStr">
         <is>
           <t>P050212</t>
         </is>
       </c>
-      <c r="D16" s="52" t="inlineStr">
+      <c r="D25" s="52" t="inlineStr">
         <is>
           <t>16.56%</t>
         </is>
       </c>
-      <c r="E16" s="52" t="inlineStr">
+      <c r="E25" s="52" t="inlineStr">
         <is>
           <t>14.9 – 18.2 %</t>
         </is>
       </c>
-      <c r="F16" s="52" t="inlineStr">
+      <c r="F25" s="52" t="inlineStr">
         <is>
           <t>ППК25322</t>
         </is>
       </c>
-      <c r="G16" s="52" t="inlineStr">
+      <c r="G25" s="52" t="inlineStr">
         <is>
           <t>23.10.2025</t>
         </is>
       </c>
-      <c r="H16" s="52" t="inlineStr">
+      <c r="H25" s="52" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I16" s="52" t="inlineStr">
+      <c r="I25" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="53" t="n"/>
-      <c r="B17" s="53" t="n"/>
-      <c r="C17" s="53" t="n"/>
-      <c r="D17" s="49" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="53" t="n"/>
+      <c r="B26" s="53" t="n"/>
+      <c r="C26" s="53" t="n"/>
+      <c r="D26" s="49" t="inlineStr">
         <is>
           <t>18.91% w/w (U 1.16% w/w)</t>
         </is>
       </c>
-      <c r="E17" s="49" t="inlineStr">
+      <c r="E26" s="49" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F17" s="49" t="inlineStr">
+      <c r="F26" s="49" t="inlineStr">
         <is>
           <t>197-4-К/26</t>
         </is>
       </c>
-      <c r="G17" s="49" t="inlineStr">
+      <c r="G26" s="49" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H17" s="49" t="inlineStr">
+      <c r="H26" s="49" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I17" s="49" t="inlineStr">
+      <c r="I26" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="47" t="n">
-        <v>7</v>
-      </c>
-      <c r="B18" s="48" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="47" t="n">
+        <v>13</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
         <is>
           <t>CJ062501-1</t>
         </is>
       </c>
-      <c r="C18" s="49" t="inlineStr">
+      <c r="C27" s="49" t="inlineStr">
         <is>
           <t>P050222</t>
         </is>
       </c>
-      <c r="D18" s="49" t="inlineStr">
+      <c r="D27" s="49" t="inlineStr">
         <is>
           <t>21.51%</t>
         </is>
       </c>
-      <c r="E18" s="49" t="inlineStr">
+      <c r="E27" s="49" t="inlineStr">
         <is>
           <t>n/a (informational)</t>
         </is>
       </c>
-      <c r="F18" s="49" t="inlineStr">
+      <c r="F27" s="49" t="inlineStr">
         <is>
           <t>ППК25321</t>
         </is>
       </c>
-      <c r="G18" s="49" t="inlineStr">
+      <c r="G27" s="49" t="inlineStr">
         <is>
           <t>23.10.2025</t>
         </is>
       </c>
-      <c r="H18" s="49" t="inlineStr">
+      <c r="H27" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I18" s="49" t="inlineStr">
+      <c r="I27" s="49" t="inlineStr">
         <is>
           <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="46" t="inlineStr">
-        <is>
-          <t>Cap Junky      3 batch(es)      Total Δ⁹-THC across batches: 18.29 – 24.96 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="47" t="n">
-        <v>8</v>
-      </c>
-      <c r="B20" s="48" t="inlineStr">
-        <is>
-          <t>CJ082501-1</t>
-        </is>
-      </c>
-      <c r="C20" s="49" t="inlineStr">
-        <is>
-          <t>P060022</t>
-        </is>
-      </c>
-      <c r="D20" s="49" t="inlineStr">
-        <is>
-          <t>24.96%</t>
-        </is>
-      </c>
-      <c r="E20" s="49" t="inlineStr">
-        <is>
-          <t>22.46 – 27.45 %</t>
-        </is>
-      </c>
-      <c r="F20" s="49" t="inlineStr">
-        <is>
-          <t>ППК26002</t>
-        </is>
-      </c>
-      <c r="G20" s="49" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H20" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I20" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="50" t="n">
-        <v>9</v>
-      </c>
-      <c r="B21" s="51" t="inlineStr">
-        <is>
-          <t>CJ082501-2</t>
-        </is>
-      </c>
-      <c r="C21" s="52" t="inlineStr">
-        <is>
-          <t>P060032</t>
-        </is>
-      </c>
-      <c r="D21" s="52" t="inlineStr">
-        <is>
-          <t>20.84%</t>
-        </is>
-      </c>
-      <c r="E21" s="52" t="inlineStr">
-        <is>
-          <t>18.75 – 22.92 %</t>
-        </is>
-      </c>
-      <c r="F21" s="52" t="inlineStr">
-        <is>
-          <t>ППК26003</t>
-        </is>
-      </c>
-      <c r="G21" s="52" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H21" s="52" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I21" s="52" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="53" t="n"/>
-      <c r="B22" s="53" t="n"/>
-      <c r="C22" s="53" t="n"/>
-      <c r="D22" s="49" t="inlineStr">
-        <is>
-          <t>18.29% w/w (U 1.12% w/w)</t>
-        </is>
-      </c>
-      <c r="E22" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F22" s="49" t="inlineStr">
-        <is>
-          <t>197-5-К/26</t>
-        </is>
-      </c>
-      <c r="G22" s="49" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H22" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I22" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="47" t="n">
-        <v>10</v>
-      </c>
-      <c r="B23" s="48" t="inlineStr">
-        <is>
-          <t>CJ092501</t>
-        </is>
-      </c>
-      <c r="C23" s="49" t="inlineStr">
-        <is>
-          <t>P060072</t>
-        </is>
-      </c>
-      <c r="D23" s="49" t="inlineStr">
-        <is>
-          <t>22.30%</t>
-        </is>
-      </c>
-      <c r="E23" s="49" t="inlineStr">
-        <is>
-          <t>20.07 – 24.53 %</t>
-        </is>
-      </c>
-      <c r="F23" s="49" t="inlineStr">
-        <is>
-          <t>ППК26007</t>
-        </is>
-      </c>
-      <c r="G23" s="49" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H23" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I23" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="46" t="inlineStr">
-        <is>
-          <t>Cash Cow      2 batch(es)      Total Δ⁹-THC across batches: 13.35 – 17.67 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="47" t="n">
-        <v>11</v>
-      </c>
-      <c r="B25" s="48" t="inlineStr">
-        <is>
-          <t>CC112501</t>
-        </is>
-      </c>
-      <c r="C25" s="49" t="n"/>
-      <c r="D25" s="49" t="inlineStr">
-        <is>
-          <t>13.35%</t>
-        </is>
-      </c>
-      <c r="E25" s="49" t="n"/>
-      <c r="F25" s="49" t="inlineStr">
-        <is>
-          <t>ППК26068</t>
-        </is>
-      </c>
-      <c r="G25" s="49" t="inlineStr">
-        <is>
-          <t>11.05.2026</t>
-        </is>
-      </c>
-      <c r="H25" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I25" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="47" t="n">
-        <v>12</v>
-      </c>
-      <c r="B26" s="48" t="inlineStr">
-        <is>
-          <t>P060332</t>
-        </is>
-      </c>
-      <c r="C26" s="49" t="inlineStr">
-        <is>
-          <t>P060332</t>
-        </is>
-      </c>
-      <c r="D26" s="49" t="inlineStr">
-        <is>
-          <t>17.67 %w/w (U 1.09 %w/w, k=2)</t>
-        </is>
-      </c>
-      <c r="E26" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F26" s="49" t="inlineStr">
-        <is>
-          <t>197-6-К/26</t>
-        </is>
-      </c>
-      <c r="G26" s="49" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H26" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I26" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="46" t="inlineStr">
-        <is>
-          <t>Clemosa a bud      1 batch(es)      Total Δ⁹-THC across batches: 8.02 %</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="47" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B28" s="48" t="inlineStr">
         <is>
-          <t>CLE072501</t>
+          <t>CJ072501</t>
         </is>
       </c>
       <c r="C28" s="49" t="inlineStr">
         <is>
-          <t>P050282</t>
+          <t>P050252</t>
         </is>
       </c>
       <c r="D28" s="49" t="inlineStr">
         <is>
-          <t>8.02%</t>
+          <t>23.70%</t>
         </is>
       </c>
       <c r="E28" s="49" t="inlineStr">
         <is>
-          <t>7.2 – 8.82 %</t>
+          <t>n/a (informational)</t>
         </is>
       </c>
       <c r="F28" s="49" t="inlineStr">
         <is>
-          <t>PP CoA #027 / ППК25370</t>
+          <t>ППК25367</t>
         </is>
       </c>
       <c r="G28" s="49" t="inlineStr">
         <is>
+          <t>28.11.2025</t>
+        </is>
+      </c>
+      <c r="H28" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I28" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="47" t="n">
+        <v>15</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>CJ082501-1</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="inlineStr">
+        <is>
+          <t>P060022</t>
+        </is>
+      </c>
+      <c r="D29" s="49" t="inlineStr">
+        <is>
+          <t>24.96%</t>
+        </is>
+      </c>
+      <c r="E29" s="49" t="inlineStr">
+        <is>
+          <t>22.46 – 27.45 %</t>
+        </is>
+      </c>
+      <c r="F29" s="49" t="inlineStr">
+        <is>
+          <t>ППК26002</t>
+        </is>
+      </c>
+      <c r="G29" s="49" t="inlineStr">
+        <is>
           <t>21.01.2026</t>
         </is>
       </c>
-      <c r="H28" s="49" t="inlineStr">
+      <c r="H29" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I28" s="49" t="inlineStr">
+      <c r="I29" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="46" t="inlineStr">
-        <is>
-          <t>Cup Junky      4 batch(es)      Total Δ⁹-THC across batches: 14.93 – 24.05 %</t>
-        </is>
-      </c>
-    </row>
     <row r="30">
-      <c r="A30" s="47" t="n">
-        <v>14</v>
-      </c>
-      <c r="B30" s="48" t="inlineStr">
-        <is>
-          <t>CJ1024</t>
-        </is>
-      </c>
-      <c r="C30" s="49" t="n"/>
-      <c r="D30" s="49" t="inlineStr">
-        <is>
-          <t>23.00%</t>
-        </is>
-      </c>
-      <c r="E30" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F30" s="49" t="inlineStr">
-        <is>
-          <t>ППК25052</t>
-        </is>
-      </c>
-      <c r="G30" s="49" t="inlineStr">
-        <is>
-          <t>26.02.2025</t>
-        </is>
-      </c>
-      <c r="H30" s="49" t="inlineStr">
+      <c r="A30" s="50" t="n">
+        <v>16</v>
+      </c>
+      <c r="B30" s="51" t="inlineStr">
+        <is>
+          <t>CJ082501-2</t>
+        </is>
+      </c>
+      <c r="C30" s="52" t="inlineStr">
+        <is>
+          <t>P060032</t>
+        </is>
+      </c>
+      <c r="D30" s="52" t="inlineStr">
+        <is>
+          <t>20.84%</t>
+        </is>
+      </c>
+      <c r="E30" s="52" t="inlineStr">
+        <is>
+          <t>18.75 – 22.92 %</t>
+        </is>
+      </c>
+      <c r="F30" s="52" t="inlineStr">
+        <is>
+          <t>ППК26003</t>
+        </is>
+      </c>
+      <c r="G30" s="52" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H30" s="52" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I30" s="49" t="inlineStr">
+      <c r="I30" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="50" t="n">
-        <v>15</v>
-      </c>
-      <c r="B31" s="51" t="inlineStr">
-        <is>
-          <t>CJ052501-1</t>
-        </is>
-      </c>
-      <c r="C31" s="52" t="inlineStr">
-        <is>
-          <t>P050162</t>
-        </is>
-      </c>
-      <c r="D31" s="52" t="inlineStr">
-        <is>
-          <t>20.29%</t>
-        </is>
-      </c>
-      <c r="E31" s="52" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F31" s="52" t="inlineStr">
-        <is>
-          <t>ППК25280</t>
-        </is>
-      </c>
-      <c r="G31" s="52" t="inlineStr">
-        <is>
-          <t>17.09.2025</t>
-        </is>
-      </c>
-      <c r="H31" s="52" t="inlineStr">
+      <c r="A31" s="53" t="n"/>
+      <c r="B31" s="53" t="n"/>
+      <c r="C31" s="53" t="n"/>
+      <c r="D31" s="49" t="inlineStr">
+        <is>
+          <t>18.29% w/w (U 1.12% w/w)</t>
+        </is>
+      </c>
+      <c r="E31" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F31" s="49" t="inlineStr">
+        <is>
+          <t>197-5-К/26</t>
+        </is>
+      </c>
+      <c r="G31" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H31" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I31" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="47" t="n">
+        <v>17</v>
+      </c>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>CJ092501</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="inlineStr">
+        <is>
+          <t>P060072</t>
+        </is>
+      </c>
+      <c r="D32" s="49" t="inlineStr">
+        <is>
+          <t>22.30%</t>
+        </is>
+      </c>
+      <c r="E32" s="49" t="inlineStr">
+        <is>
+          <t>20.07 – 24.53 %</t>
+        </is>
+      </c>
+      <c r="F32" s="49" t="inlineStr">
+        <is>
+          <t>ППК26007</t>
+        </is>
+      </c>
+      <c r="G32" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H32" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I31" s="52" t="inlineStr">
+      <c r="I32" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="53" t="n"/>
-      <c r="B32" s="53" t="n"/>
-      <c r="C32" s="53" t="n"/>
-      <c r="D32" s="49" t="inlineStr">
-        <is>
-          <t>24.05 %w/w (U 1.48)</t>
-        </is>
-      </c>
-      <c r="E32" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F32" s="49" t="inlineStr">
-        <is>
-          <t>197-3-К/26</t>
-        </is>
-      </c>
-      <c r="G32" s="49" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H32" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I32" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="47" t="n">
-        <v>16</v>
-      </c>
-      <c r="B33" s="48" t="inlineStr">
-        <is>
-          <t>CJ052501-2</t>
-        </is>
-      </c>
-      <c r="C33" s="49" t="inlineStr">
-        <is>
-          <t>P050172</t>
-        </is>
-      </c>
-      <c r="D33" s="49" t="inlineStr">
-        <is>
-          <t>14.93%</t>
-        </is>
-      </c>
-      <c r="E33" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F33" s="49" t="inlineStr">
-        <is>
-          <t>ППК25281</t>
-        </is>
-      </c>
-      <c r="G33" s="49" t="inlineStr">
-        <is>
-          <t>17.09.2025</t>
-        </is>
-      </c>
-      <c r="H33" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I33" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="A33" s="46" t="inlineStr">
+        <is>
+          <t>Fat Bastard      6 batch(es)      Total Δ⁹-THC across batches: 12.39 – 20.83 %</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="47" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B34" s="48" t="inlineStr">
         <is>
-          <t>CJ072501</t>
-        </is>
-      </c>
-      <c r="C34" s="49" t="inlineStr">
-        <is>
-          <t>P050252</t>
-        </is>
-      </c>
+          <t>FB012601</t>
+        </is>
+      </c>
+      <c r="C34" s="49" t="n"/>
       <c r="D34" s="49" t="inlineStr">
         <is>
-          <t>23.70%</t>
-        </is>
-      </c>
-      <c r="E34" s="49" t="inlineStr">
-        <is>
-          <t>n/a (informational)</t>
-        </is>
-      </c>
+          <t>14.68%</t>
+        </is>
+      </c>
+      <c r="E34" s="49" t="n"/>
       <c r="F34" s="49" t="inlineStr">
         <is>
-          <t>ППК25367</t>
+          <t>ППК26067</t>
         </is>
       </c>
       <c r="G34" s="49" t="inlineStr">
         <is>
-          <t>28.11.2025</t>
+          <t>11.05.2026</t>
         </is>
       </c>
       <c r="H34" s="49" t="inlineStr">
@@ -36078,37 +36108,71 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="46" t="inlineStr">
-        <is>
-          <t>Fat Bastard      6 batch(es)      Total Δ⁹-THC across batches: 12.39 – 20.83 %</t>
+    <row r="35">
+      <c r="A35" s="47" t="n">
+        <v>19</v>
+      </c>
+      <c r="B35" s="48" t="inlineStr">
+        <is>
+          <t>FB112501</t>
+        </is>
+      </c>
+      <c r="C35" s="49" t="n"/>
+      <c r="D35" s="49" t="inlineStr">
+        <is>
+          <t>16.69%</t>
+        </is>
+      </c>
+      <c r="E35" s="49" t="n"/>
+      <c r="F35" s="49" t="inlineStr">
+        <is>
+          <t>ППК26066</t>
+        </is>
+      </c>
+      <c r="G35" s="49" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H35" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I35" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B36" s="48" t="inlineStr">
         <is>
-          <t>FB012601</t>
+          <t>FB012603</t>
         </is>
       </c>
       <c r="C36" s="49" t="n"/>
       <c r="D36" s="49" t="inlineStr">
         <is>
-          <t>14.68%</t>
-        </is>
-      </c>
-      <c r="E36" s="49" t="n"/>
+          <t>20.83%</t>
+        </is>
+      </c>
+      <c r="E36" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
       <c r="F36" s="49" t="inlineStr">
         <is>
-          <t>ППК26067</t>
+          <t>ППК26112</t>
         </is>
       </c>
       <c r="G36" s="49" t="inlineStr">
         <is>
-          <t>11.05.2026</t>
+          <t>30.06.2026</t>
         </is>
       </c>
       <c r="H36" s="49" t="inlineStr">
@@ -36124,28 +36188,32 @@
     </row>
     <row r="37">
       <c r="A37" s="47" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B37" s="48" t="inlineStr">
         <is>
-          <t>FB112501</t>
+          <t>FB012603V</t>
         </is>
       </c>
       <c r="C37" s="49" t="n"/>
       <c r="D37" s="49" t="inlineStr">
         <is>
-          <t>16.69%</t>
-        </is>
-      </c>
-      <c r="E37" s="49" t="n"/>
+          <t>18.29%</t>
+        </is>
+      </c>
+      <c r="E37" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
       <c r="F37" s="49" t="inlineStr">
         <is>
-          <t>ППК26066</t>
+          <t>ППК26110</t>
         </is>
       </c>
       <c r="G37" s="49" t="inlineStr">
         <is>
-          <t>11.05.2026</t>
+          <t>30.06.2026</t>
         </is>
       </c>
       <c r="H37" s="49" t="inlineStr">
@@ -36161,17 +36229,17 @@
     </row>
     <row r="38">
       <c r="A38" s="47" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B38" s="48" t="inlineStr">
         <is>
-          <t>FB012603</t>
+          <t>FB032601</t>
         </is>
       </c>
       <c r="C38" s="49" t="n"/>
       <c r="D38" s="49" t="inlineStr">
         <is>
-          <t>20.83%</t>
+          <t>12.39%</t>
         </is>
       </c>
       <c r="E38" s="49" t="inlineStr">
@@ -36181,12 +36249,12 @@
       </c>
       <c r="F38" s="49" t="inlineStr">
         <is>
-          <t>ППК26112</t>
+          <t>ППК26127</t>
         </is>
       </c>
       <c r="G38" s="49" t="inlineStr">
         <is>
-          <t>30.06.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="H38" s="49" t="inlineStr">
@@ -36202,17 +36270,21 @@
     </row>
     <row r="39">
       <c r="A39" s="47" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B39" s="48" t="inlineStr">
         <is>
-          <t>FB012603V</t>
-        </is>
-      </c>
-      <c r="C39" s="49" t="n"/>
+          <t>P060352</t>
+        </is>
+      </c>
+      <c r="C39" s="49" t="inlineStr">
+        <is>
+          <t>P060352</t>
+        </is>
+      </c>
       <c r="D39" s="49" t="inlineStr">
         <is>
-          <t>18.29%</t>
+          <t>18.86 %w/w (U 1.16 %w/w, k=2)</t>
         </is>
       </c>
       <c r="E39" s="49" t="inlineStr">
@@ -36222,190 +36294,186 @@
       </c>
       <c r="F39" s="49" t="inlineStr">
         <is>
-          <t>ППК26110</t>
+          <t>197-7-К/26</t>
         </is>
       </c>
       <c r="G39" s="49" t="inlineStr">
         <is>
-          <t>30.06.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="H39" s="49" t="inlineStr">
         <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I39" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="19.5" customHeight="1">
+      <c r="A40" s="46" t="inlineStr">
+        <is>
+          <t>Gorilla Glue      7 batch(es)      Total Δ⁹-THC across batches: 15.35 – 18.98 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="50" t="n">
+        <v>24</v>
+      </c>
+      <c r="B41" s="51" t="inlineStr">
+        <is>
+          <t>GG1024_01</t>
+        </is>
+      </c>
+      <c r="C41" s="52" t="inlineStr">
+        <is>
+          <t>P050092</t>
+        </is>
+      </c>
+      <c r="D41" s="52" t="inlineStr">
+        <is>
+          <t>17.22%</t>
+        </is>
+      </c>
+      <c r="E41" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F41" s="52" t="inlineStr">
+        <is>
+          <t>ППК25104</t>
+        </is>
+      </c>
+      <c r="G41" s="52" t="inlineStr">
+        <is>
+          <t>17.04.2025</t>
+        </is>
+      </c>
+      <c r="H41" s="52" t="inlineStr">
+        <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I39" s="49" t="inlineStr">
+      <c r="I41" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="47" t="n">
-        <v>22</v>
-      </c>
-      <c r="B40" s="48" t="inlineStr">
-        <is>
-          <t>FB032601</t>
-        </is>
-      </c>
-      <c r="C40" s="49" t="n"/>
-      <c r="D40" s="49" t="inlineStr">
-        <is>
-          <t>12.39%</t>
-        </is>
-      </c>
-      <c r="E40" s="49" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="53" t="n"/>
+      <c r="B42" s="53" t="n"/>
+      <c r="C42" s="53" t="n"/>
+      <c r="D42" s="49" t="inlineStr">
+        <is>
+          <t>18.67 %w/w (U 1.15)</t>
+        </is>
+      </c>
+      <c r="E42" s="49" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F40" s="49" t="inlineStr">
-        <is>
-          <t>ППК26127</t>
-        </is>
-      </c>
-      <c r="G40" s="49" t="inlineStr">
-        <is>
-          <t>21.07.2026</t>
-        </is>
-      </c>
-      <c r="H40" s="49" t="inlineStr">
+      <c r="F42" s="49" t="inlineStr">
+        <is>
+          <t>197-9-К/26</t>
+        </is>
+      </c>
+      <c r="G42" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H42" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I42" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="47" t="n">
+        <v>25</v>
+      </c>
+      <c r="B43" s="48" t="inlineStr">
+        <is>
+          <t>GG1024_02</t>
+        </is>
+      </c>
+      <c r="C43" s="49" t="inlineStr">
+        <is>
+          <t>P050012</t>
+        </is>
+      </c>
+      <c r="D43" s="49" t="inlineStr">
+        <is>
+          <t>15.95%</t>
+        </is>
+      </c>
+      <c r="E43" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F43" s="49" t="inlineStr">
+        <is>
+          <t>ППК25140</t>
+        </is>
+      </c>
+      <c r="G43" s="49" t="inlineStr">
+        <is>
+          <t>22.05.2025</t>
+        </is>
+      </c>
+      <c r="H43" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I40" s="49" t="inlineStr">
+      <c r="I43" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="47" t="n">
-        <v>23</v>
-      </c>
-      <c r="B41" s="48" t="inlineStr">
-        <is>
-          <t>P060352</t>
-        </is>
-      </c>
-      <c r="C41" s="49" t="inlineStr">
-        <is>
-          <t>P060352</t>
-        </is>
-      </c>
-      <c r="D41" s="49" t="inlineStr">
-        <is>
-          <t>18.86 %w/w (U 1.16 %w/w, k=2)</t>
-        </is>
-      </c>
-      <c r="E41" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F41" s="49" t="inlineStr">
-        <is>
-          <t>197-7-К/26</t>
-        </is>
-      </c>
-      <c r="G41" s="49" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H41" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I41" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="19.5" customHeight="1">
-      <c r="A42" s="46" t="inlineStr">
-        <is>
-          <t>Gorilla Glue      7 batch(es)      Total Δ⁹-THC across batches: 15.35 – 18.98 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="50" t="n">
-        <v>24</v>
-      </c>
-      <c r="B43" s="51" t="inlineStr">
-        <is>
-          <t>GG1024_01</t>
-        </is>
-      </c>
-      <c r="C43" s="52" t="inlineStr">
-        <is>
-          <t>P050092</t>
-        </is>
-      </c>
-      <c r="D43" s="52" t="inlineStr">
-        <is>
-          <t>17.22%</t>
-        </is>
-      </c>
-      <c r="E43" s="52" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F43" s="52" t="inlineStr">
-        <is>
-          <t>ППК25104</t>
-        </is>
-      </c>
-      <c r="G43" s="52" t="inlineStr">
-        <is>
-          <t>17.04.2025</t>
-        </is>
-      </c>
-      <c r="H43" s="52" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="47" t="n">
+        <v>26</v>
+      </c>
+      <c r="B44" s="48" t="inlineStr">
+        <is>
+          <t>GG012601</t>
+        </is>
+      </c>
+      <c r="C44" s="49" t="n"/>
+      <c r="D44" s="49" t="inlineStr">
+        <is>
+          <t>15.35%</t>
+        </is>
+      </c>
+      <c r="E44" s="49" t="n"/>
+      <c r="F44" s="49" t="inlineStr">
+        <is>
+          <t>ППК26062</t>
+        </is>
+      </c>
+      <c r="G44" s="49" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H44" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I43" s="52" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="53" t="n"/>
-      <c r="B44" s="53" t="n"/>
-      <c r="C44" s="53" t="n"/>
-      <c r="D44" s="49" t="inlineStr">
-        <is>
-          <t>18.67 %w/w (U 1.15)</t>
-        </is>
-      </c>
-      <c r="E44" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F44" s="49" t="inlineStr">
-        <is>
-          <t>197-9-К/26</t>
-        </is>
-      </c>
-      <c r="G44" s="49" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H44" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
         </is>
       </c>
       <c r="I44" s="49" t="inlineStr">
@@ -36416,36 +36484,28 @@
     </row>
     <row r="45">
       <c r="A45" s="47" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B45" s="48" t="inlineStr">
         <is>
-          <t>GG1024_02</t>
-        </is>
-      </c>
-      <c r="C45" s="49" t="inlineStr">
-        <is>
-          <t>P050012</t>
-        </is>
-      </c>
+          <t>GG112501</t>
+        </is>
+      </c>
+      <c r="C45" s="49" t="n"/>
       <c r="D45" s="49" t="inlineStr">
         <is>
-          <t>15.95%</t>
-        </is>
-      </c>
-      <c r="E45" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>17.94%</t>
+        </is>
+      </c>
+      <c r="E45" s="49" t="n"/>
       <c r="F45" s="49" t="inlineStr">
         <is>
-          <t>ППК25140</t>
+          <t>ППК26061</t>
         </is>
       </c>
       <c r="G45" s="49" t="inlineStr">
         <is>
-          <t>22.05.2025</t>
+          <t>11.05.2026</t>
         </is>
       </c>
       <c r="H45" s="49" t="inlineStr">
@@ -36461,28 +36521,32 @@
     </row>
     <row r="46">
       <c r="A46" s="47" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B46" s="48" t="inlineStr">
         <is>
-          <t>GG012601</t>
+          <t>GG012603</t>
         </is>
       </c>
       <c r="C46" s="49" t="n"/>
       <c r="D46" s="49" t="inlineStr">
         <is>
-          <t>15.35%</t>
-        </is>
-      </c>
-      <c r="E46" s="49" t="n"/>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="E46" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
       <c r="F46" s="49" t="inlineStr">
         <is>
-          <t>ППК26062</t>
+          <t>ППК26114</t>
         </is>
       </c>
       <c r="G46" s="49" t="inlineStr">
         <is>
-          <t>11.05.2026</t>
+          <t>30.06.2026</t>
         </is>
       </c>
       <c r="H46" s="49" t="inlineStr">
@@ -36498,28 +36562,32 @@
     </row>
     <row r="47">
       <c r="A47" s="47" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B47" s="48" t="inlineStr">
         <is>
-          <t>GG112501</t>
+          <t>GG032601</t>
         </is>
       </c>
       <c r="C47" s="49" t="n"/>
       <c r="D47" s="49" t="inlineStr">
         <is>
-          <t>17.94%</t>
-        </is>
-      </c>
-      <c r="E47" s="49" t="n"/>
+          <t>18.98%</t>
+        </is>
+      </c>
+      <c r="E47" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
       <c r="F47" s="49" t="inlineStr">
         <is>
-          <t>ППК26061</t>
+          <t>ППК26128</t>
         </is>
       </c>
       <c r="G47" s="49" t="inlineStr">
         <is>
-          <t>11.05.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="H47" s="49" t="inlineStr">
@@ -36535,17 +36603,21 @@
     </row>
     <row r="48">
       <c r="A48" s="47" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B48" s="48" t="inlineStr">
         <is>
-          <t>GG012603</t>
-        </is>
-      </c>
-      <c r="C48" s="49" t="n"/>
+          <t>P060402</t>
+        </is>
+      </c>
+      <c r="C48" s="49" t="inlineStr">
+        <is>
+          <t>P060402</t>
+        </is>
+      </c>
       <c r="D48" s="49" t="inlineStr">
         <is>
-          <t>17.59%</t>
+          <t>16.70 %w/w (U 1.03 %w/w, k=2)</t>
         </is>
       </c>
       <c r="E48" s="49" t="inlineStr">
@@ -36555,17 +36627,17 @@
       </c>
       <c r="F48" s="49" t="inlineStr">
         <is>
-          <t>ППК26114</t>
+          <t>197-8-К/26</t>
         </is>
       </c>
       <c r="G48" s="49" t="inlineStr">
         <is>
-          <t>30.06.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="H48" s="49" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="I48" s="49" t="inlineStr">
@@ -36574,341 +36646,345 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="47" t="n">
-        <v>29</v>
-      </c>
-      <c r="B49" s="48" t="inlineStr">
-        <is>
-          <t>GG032601</t>
-        </is>
-      </c>
-      <c r="C49" s="49" t="n"/>
-      <c r="D49" s="49" t="inlineStr">
-        <is>
-          <t>18.98%</t>
-        </is>
-      </c>
-      <c r="E49" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F49" s="49" t="inlineStr">
-        <is>
-          <t>ППК26128</t>
-        </is>
-      </c>
-      <c r="G49" s="49" t="inlineStr">
-        <is>
-          <t>21.07.2026</t>
-        </is>
-      </c>
-      <c r="H49" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I49" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
+    <row r="49" ht="19.5" customHeight="1">
+      <c r="A49" s="46" t="inlineStr">
+        <is>
+          <t>Grape Pie      13 batch(es)      Total Δ⁹-THC across batches: 14.83 – 26.32 %</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="47" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B50" s="48" t="inlineStr">
         <is>
-          <t>P060402</t>
+          <t>GP0824_01</t>
         </is>
       </c>
       <c r="C50" s="49" t="inlineStr">
         <is>
-          <t>P060402</t>
+          <t>P050102</t>
         </is>
       </c>
       <c r="D50" s="49" t="inlineStr">
         <is>
-          <t>16.70 %w/w (U 1.03 %w/w, k=2)</t>
+          <t>20.79%</t>
         </is>
       </c>
       <c r="E50" s="49" t="inlineStr">
         <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F50" s="49" t="inlineStr">
+        <is>
+          <t>ППК25105</t>
+        </is>
+      </c>
+      <c r="G50" s="49" t="inlineStr">
+        <is>
+          <t>17.04.2025</t>
+        </is>
+      </c>
+      <c r="H50" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I50" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="50" t="n">
+        <v>32</v>
+      </c>
+      <c r="B51" s="51" t="inlineStr">
+        <is>
+          <t>GP0824_02</t>
+        </is>
+      </c>
+      <c r="C51" s="52" t="inlineStr">
+        <is>
+          <t>P050022</t>
+        </is>
+      </c>
+      <c r="D51" s="52" t="inlineStr">
+        <is>
+          <t>23.19%</t>
+        </is>
+      </c>
+      <c r="E51" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F51" s="52" t="inlineStr">
+        <is>
+          <t>ППК25174</t>
+        </is>
+      </c>
+      <c r="G51" s="52" t="inlineStr">
+        <is>
+          <t>10.07.2025</t>
+        </is>
+      </c>
+      <c r="H51" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I51" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="53" t="n"/>
+      <c r="B52" s="53" t="n"/>
+      <c r="C52" s="53" t="n"/>
+      <c r="D52" s="49" t="inlineStr">
+        <is>
+          <t>22.61 %w/w (U 1.39)</t>
+        </is>
+      </c>
+      <c r="E52" s="49" t="inlineStr">
+        <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F50" s="49" t="inlineStr">
-        <is>
-          <t>197-8-К/26</t>
-        </is>
-      </c>
-      <c r="G50" s="49" t="inlineStr">
+      <c r="F52" s="49" t="inlineStr">
+        <is>
+          <t>197-11-К/26</t>
+        </is>
+      </c>
+      <c r="G52" s="49" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H50" s="49" t="inlineStr">
+      <c r="H52" s="49" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I50" s="49" t="inlineStr">
+      <c r="I52" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="19.5" customHeight="1">
-      <c r="A51" s="46" t="inlineStr">
-        <is>
-          <t>Grape Pie      13 batch(es)      Total Δ⁹-THC across batches: 14.83 – 26.32 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="47" t="n">
-        <v>31</v>
-      </c>
-      <c r="B52" s="48" t="inlineStr">
-        <is>
-          <t>GP0824_01</t>
-        </is>
-      </c>
-      <c r="C52" s="49" t="inlineStr">
-        <is>
-          <t>P050102</t>
-        </is>
-      </c>
-      <c r="D52" s="49" t="inlineStr">
-        <is>
-          <t>20.79%</t>
-        </is>
-      </c>
-      <c r="E52" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F52" s="49" t="inlineStr">
-        <is>
-          <t>ППК25105</t>
-        </is>
-      </c>
-      <c r="G52" s="49" t="inlineStr">
-        <is>
-          <t>17.04.2025</t>
-        </is>
-      </c>
-      <c r="H52" s="49" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="47" t="n">
+        <v>33</v>
+      </c>
+      <c r="B53" s="48" t="inlineStr">
+        <is>
+          <t>GP0824_03</t>
+        </is>
+      </c>
+      <c r="C53" s="49" t="inlineStr">
+        <is>
+          <t>P050072</t>
+        </is>
+      </c>
+      <c r="D53" s="49" t="inlineStr">
+        <is>
+          <t>25.45%</t>
+        </is>
+      </c>
+      <c r="E53" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F53" s="49" t="inlineStr">
+        <is>
+          <t>ППК25175</t>
+        </is>
+      </c>
+      <c r="G53" s="49" t="inlineStr">
+        <is>
+          <t>10.07.2025</t>
+        </is>
+      </c>
+      <c r="H53" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I52" s="49" t="inlineStr">
+      <c r="I53" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="50" t="n">
-        <v>32</v>
-      </c>
-      <c r="B53" s="51" t="inlineStr">
-        <is>
-          <t>GP0824_02</t>
-        </is>
-      </c>
-      <c r="C53" s="52" t="inlineStr">
-        <is>
-          <t>P050022</t>
-        </is>
-      </c>
-      <c r="D53" s="52" t="inlineStr">
-        <is>
-          <t>23.19%</t>
-        </is>
-      </c>
-      <c r="E53" s="52" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F53" s="52" t="inlineStr">
-        <is>
-          <t>ППК25174</t>
-        </is>
-      </c>
-      <c r="G53" s="52" t="inlineStr">
-        <is>
-          <t>10.07.2025</t>
-        </is>
-      </c>
-      <c r="H53" s="52" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="50" t="n">
+        <v>34</v>
+      </c>
+      <c r="B54" s="51" t="inlineStr">
+        <is>
+          <t>GP052501</t>
+        </is>
+      </c>
+      <c r="C54" s="52" t="inlineStr">
+        <is>
+          <t>P050152</t>
+        </is>
+      </c>
+      <c r="D54" s="52" t="inlineStr">
+        <is>
+          <t>18.98%</t>
+        </is>
+      </c>
+      <c r="E54" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F54" s="52" t="inlineStr">
+        <is>
+          <t>ППК25279</t>
+        </is>
+      </c>
+      <c r="G54" s="52" t="inlineStr">
+        <is>
+          <t>19.09.2025</t>
+        </is>
+      </c>
+      <c r="H54" s="52" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I53" s="52" t="inlineStr">
+      <c r="I54" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="53" t="n"/>
-      <c r="B54" s="53" t="n"/>
-      <c r="C54" s="53" t="n"/>
-      <c r="D54" s="49" t="inlineStr">
-        <is>
-          <t>22.61 %w/w (U 1.39)</t>
-        </is>
-      </c>
-      <c r="E54" s="49" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="53" t="n"/>
+      <c r="B55" s="53" t="n"/>
+      <c r="C55" s="53" t="n"/>
+      <c r="D55" s="49" t="inlineStr">
+        <is>
+          <t>18.52 %w/w (U 1.14)</t>
+        </is>
+      </c>
+      <c r="E55" s="49" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F54" s="49" t="inlineStr">
-        <is>
-          <t>197-11-К/26</t>
-        </is>
-      </c>
-      <c r="G54" s="49" t="inlineStr">
+      <c r="F55" s="49" t="inlineStr">
+        <is>
+          <t>197-10-К/26</t>
+        </is>
+      </c>
+      <c r="G55" s="49" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H54" s="49" t="inlineStr">
+      <c r="H55" s="49" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I54" s="49" t="inlineStr">
+      <c r="I55" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="47" t="n">
-        <v>33</v>
-      </c>
-      <c r="B55" s="48" t="inlineStr">
-        <is>
-          <t>GP0824_03</t>
-        </is>
-      </c>
-      <c r="C55" s="49" t="inlineStr">
-        <is>
-          <t>P050072</t>
-        </is>
-      </c>
-      <c r="D55" s="49" t="inlineStr">
-        <is>
-          <t>25.45%</t>
-        </is>
-      </c>
-      <c r="E55" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F55" s="49" t="inlineStr">
-        <is>
-          <t>ППК25175</t>
-        </is>
-      </c>
-      <c r="G55" s="49" t="inlineStr">
-        <is>
-          <t>10.07.2025</t>
-        </is>
-      </c>
-      <c r="H55" s="49" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="47" t="n">
+        <v>35</v>
+      </c>
+      <c r="B56" s="48" t="inlineStr">
+        <is>
+          <t>GP062501</t>
+        </is>
+      </c>
+      <c r="C56" s="49" t="inlineStr">
+        <is>
+          <t>P050202</t>
+        </is>
+      </c>
+      <c r="D56" s="49" t="inlineStr">
+        <is>
+          <t>24.89%</t>
+        </is>
+      </c>
+      <c r="E56" s="49" t="inlineStr">
+        <is>
+          <t>19.8 – 24.2 %</t>
+        </is>
+      </c>
+      <c r="F56" s="49" t="inlineStr">
+        <is>
+          <t>In-house HPLC cross-check NPCCC/SCP-02, NGP/QCG/SOP-024</t>
+        </is>
+      </c>
+      <c r="G56" s="49" t="inlineStr">
+        <is>
+          <t>28.11.2025</t>
+        </is>
+      </c>
+      <c r="H56" s="49" t="inlineStr">
+        <is>
+          <t>Purely Plant (in-house)</t>
+        </is>
+      </c>
+      <c r="I56" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="47" t="n">
+        <v>36</v>
+      </c>
+      <c r="B57" s="48" t="inlineStr">
+        <is>
+          <t>GP072501-1</t>
+        </is>
+      </c>
+      <c r="C57" s="49" t="inlineStr">
+        <is>
+          <t>P050292</t>
+        </is>
+      </c>
+      <c r="D57" s="49" t="inlineStr">
+        <is>
+          <t>21.36%</t>
+        </is>
+      </c>
+      <c r="E57" s="49" t="inlineStr">
+        <is>
+          <t>19.2 – 23.4 %</t>
+        </is>
+      </c>
+      <c r="F57" s="49" t="inlineStr">
+        <is>
+          <t>PP CoA #018 / ППК25378</t>
+        </is>
+      </c>
+      <c r="G57" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H57" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I55" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="50" t="n">
-        <v>34</v>
-      </c>
-      <c r="B56" s="51" t="inlineStr">
-        <is>
-          <t>GP052501</t>
-        </is>
-      </c>
-      <c r="C56" s="52" t="inlineStr">
-        <is>
-          <t>P050152</t>
-        </is>
-      </c>
-      <c r="D56" s="52" t="inlineStr">
-        <is>
-          <t>18.98%</t>
-        </is>
-      </c>
-      <c r="E56" s="52" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F56" s="52" t="inlineStr">
-        <is>
-          <t>ППК25279</t>
-        </is>
-      </c>
-      <c r="G56" s="52" t="inlineStr">
-        <is>
-          <t>19.09.2025</t>
-        </is>
-      </c>
-      <c r="H56" s="52" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I56" s="52" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="53" t="n"/>
-      <c r="B57" s="53" t="n"/>
-      <c r="C57" s="53" t="n"/>
-      <c r="D57" s="49" t="inlineStr">
-        <is>
-          <t>18.52 %w/w (U 1.14)</t>
-        </is>
-      </c>
-      <c r="E57" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F57" s="49" t="inlineStr">
-        <is>
-          <t>197-10-К/26</t>
-        </is>
-      </c>
-      <c r="G57" s="49" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H57" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
         </is>
       </c>
       <c r="I57" s="49" t="inlineStr">
@@ -36919,41 +36995,41 @@
     </row>
     <row r="58">
       <c r="A58" s="47" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B58" s="48" t="inlineStr">
         <is>
-          <t>GP062501</t>
+          <t>GP072501-2</t>
         </is>
       </c>
       <c r="C58" s="49" t="inlineStr">
         <is>
-          <t>P050202</t>
+          <t>P050302</t>
         </is>
       </c>
       <c r="D58" s="49" t="inlineStr">
         <is>
-          <t>24.89%</t>
+          <t>19.81%</t>
         </is>
       </c>
       <c r="E58" s="49" t="inlineStr">
         <is>
-          <t>19.8 – 24.2 %</t>
+          <t>17.8 – 21.7 %</t>
         </is>
       </c>
       <c r="F58" s="49" t="inlineStr">
         <is>
-          <t>In-house HPLC cross-check NPCCC/SCP-02, NGP/QCG/SOP-024</t>
+          <t>PP CoA #019 / ППК25379</t>
         </is>
       </c>
       <c r="G58" s="49" t="inlineStr">
         <is>
-          <t>28.11.2025</t>
+          <t>21.01.2026</t>
         </is>
       </c>
       <c r="H58" s="49" t="inlineStr">
         <is>
-          <t>Purely Plant (in-house)</t>
+          <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
       <c r="I58" s="49" t="inlineStr">
@@ -36964,31 +37040,31 @@
     </row>
     <row r="59">
       <c r="A59" s="47" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B59" s="48" t="inlineStr">
         <is>
-          <t>GP072501-1</t>
+          <t>GP082501-1</t>
         </is>
       </c>
       <c r="C59" s="49" t="inlineStr">
         <is>
-          <t>P050292</t>
+          <t>P050312</t>
         </is>
       </c>
       <c r="D59" s="49" t="inlineStr">
         <is>
-          <t>21.36%</t>
+          <t>21.29%</t>
         </is>
       </c>
       <c r="E59" s="49" t="inlineStr">
         <is>
-          <t>19.2 – 23.4 %</t>
+          <t>19.1 – 23.4 %</t>
         </is>
       </c>
       <c r="F59" s="49" t="inlineStr">
         <is>
-          <t>PP CoA #018 / ППК25378</t>
+          <t>PP CoA #020 / ППК25380</t>
         </is>
       </c>
       <c r="G59" s="49" t="inlineStr">
@@ -37008,167 +37084,167 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="47" t="n">
-        <v>37</v>
-      </c>
-      <c r="B60" s="48" t="inlineStr">
-        <is>
-          <t>GP072501-2</t>
-        </is>
-      </c>
-      <c r="C60" s="49" t="inlineStr">
-        <is>
-          <t>P050302</t>
-        </is>
-      </c>
-      <c r="D60" s="49" t="inlineStr">
-        <is>
-          <t>19.81%</t>
-        </is>
-      </c>
-      <c r="E60" s="49" t="inlineStr">
-        <is>
-          <t>17.8 – 21.7 %</t>
-        </is>
-      </c>
-      <c r="F60" s="49" t="inlineStr">
-        <is>
-          <t>PP CoA #019 / ППК25379</t>
-        </is>
-      </c>
-      <c r="G60" s="49" t="inlineStr">
+      <c r="A60" s="50" t="n">
+        <v>39</v>
+      </c>
+      <c r="B60" s="51" t="inlineStr">
+        <is>
+          <t>GP082501-2</t>
+        </is>
+      </c>
+      <c r="C60" s="52" t="inlineStr">
+        <is>
+          <t>P050322</t>
+        </is>
+      </c>
+      <c r="D60" s="52" t="inlineStr">
+        <is>
+          <t>14.83%</t>
+        </is>
+      </c>
+      <c r="E60" s="52" t="inlineStr">
+        <is>
+          <t>13.3 – 16.3 %</t>
+        </is>
+      </c>
+      <c r="F60" s="52" t="inlineStr">
+        <is>
+          <t>PP CoA #021 / ППК25381</t>
+        </is>
+      </c>
+      <c r="G60" s="52" t="inlineStr">
         <is>
           <t>21.01.2026</t>
         </is>
       </c>
-      <c r="H60" s="49" t="inlineStr">
+      <c r="H60" s="52" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I60" s="49" t="inlineStr">
+      <c r="I60" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="47" t="n">
-        <v>38</v>
-      </c>
-      <c r="B61" s="48" t="inlineStr">
-        <is>
-          <t>GP082501-1</t>
-        </is>
-      </c>
-      <c r="C61" s="49" t="inlineStr">
-        <is>
-          <t>P050312</t>
-        </is>
-      </c>
+      <c r="A61" s="53" t="n"/>
+      <c r="B61" s="53" t="n"/>
+      <c r="C61" s="53" t="n"/>
       <c r="D61" s="49" t="inlineStr">
         <is>
-          <t>21.29%</t>
+          <t>15.70% w/w (U 0.96% w/w)</t>
         </is>
       </c>
       <c r="E61" s="49" t="inlineStr">
         <is>
-          <t>19.1 – 23.4 %</t>
+          <t>≥ 5.00 %</t>
         </is>
       </c>
       <c r="F61" s="49" t="inlineStr">
         <is>
-          <t>PP CoA #020 / ППК25380</t>
+          <t>197-12-К/26</t>
         </is>
       </c>
       <c r="G61" s="49" t="inlineStr">
         <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H61" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I61" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="47" t="n">
+        <v>40</v>
+      </c>
+      <c r="B62" s="48" t="inlineStr">
+        <is>
+          <t>GP092501</t>
+        </is>
+      </c>
+      <c r="C62" s="49" t="inlineStr">
+        <is>
+          <t>P060092</t>
+        </is>
+      </c>
+      <c r="D62" s="49" t="inlineStr">
+        <is>
+          <t>25.73%</t>
+        </is>
+      </c>
+      <c r="E62" s="49" t="inlineStr">
+        <is>
+          <t>23.15 – 28.3 %</t>
+        </is>
+      </c>
+      <c r="F62" s="49" t="inlineStr">
+        <is>
+          <t>ППК26009</t>
+        </is>
+      </c>
+      <c r="G62" s="49" t="inlineStr">
+        <is>
           <t>21.01.2026</t>
         </is>
       </c>
-      <c r="H61" s="49" t="inlineStr">
+      <c r="H62" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I61" s="49" t="inlineStr">
+      <c r="I62" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="50" t="n">
-        <v>39</v>
-      </c>
-      <c r="B62" s="51" t="inlineStr">
-        <is>
-          <t>GP082501-2</t>
-        </is>
-      </c>
-      <c r="C62" s="52" t="inlineStr">
-        <is>
-          <t>P050322</t>
-        </is>
-      </c>
-      <c r="D62" s="52" t="inlineStr">
-        <is>
-          <t>14.83%</t>
-        </is>
-      </c>
-      <c r="E62" s="52" t="inlineStr">
-        <is>
-          <t>13.3 – 16.3 %</t>
-        </is>
-      </c>
-      <c r="F62" s="52" t="inlineStr">
-        <is>
-          <t>PP CoA #021 / ППК25381</t>
-        </is>
-      </c>
-      <c r="G62" s="52" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H62" s="52" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="47" t="n">
+        <v>41</v>
+      </c>
+      <c r="B63" s="48" t="inlineStr">
+        <is>
+          <t>P160012</t>
+        </is>
+      </c>
+      <c r="C63" s="49" t="inlineStr">
+        <is>
+          <t>P160012</t>
+        </is>
+      </c>
+      <c r="D63" s="49" t="inlineStr">
+        <is>
+          <t>26.32%</t>
+        </is>
+      </c>
+      <c r="E63" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F63" s="49" t="inlineStr">
+        <is>
+          <t>ППК26117</t>
+        </is>
+      </c>
+      <c r="G63" s="49" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="H63" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I62" s="52" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="53" t="n"/>
-      <c r="B63" s="53" t="n"/>
-      <c r="C63" s="53" t="n"/>
-      <c r="D63" s="49" t="inlineStr">
-        <is>
-          <t>15.70% w/w (U 0.96% w/w)</t>
-        </is>
-      </c>
-      <c r="E63" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F63" s="49" t="inlineStr">
-        <is>
-          <t>197-12-К/26</t>
-        </is>
-      </c>
-      <c r="G63" s="49" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H63" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
         </is>
       </c>
       <c r="I63" s="49" t="inlineStr">
@@ -37179,36 +37255,36 @@
     </row>
     <row r="64">
       <c r="A64" s="47" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B64" s="48" t="inlineStr">
         <is>
-          <t>GP092501</t>
+          <t>P160022</t>
         </is>
       </c>
       <c r="C64" s="49" t="inlineStr">
         <is>
-          <t>P060092</t>
+          <t>P160022</t>
         </is>
       </c>
       <c r="D64" s="49" t="inlineStr">
         <is>
-          <t>25.73%</t>
+          <t>25.72%</t>
         </is>
       </c>
       <c r="E64" s="49" t="inlineStr">
         <is>
-          <t>23.15 – 28.3 %</t>
+          <t>≥ 5.00 %</t>
         </is>
       </c>
       <c r="F64" s="49" t="inlineStr">
         <is>
-          <t>ППК26009</t>
+          <t>ППК26118</t>
         </is>
       </c>
       <c r="G64" s="49" t="inlineStr">
         <is>
-          <t>21.01.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="H64" s="49" t="inlineStr">
@@ -37224,21 +37300,21 @@
     </row>
     <row r="65">
       <c r="A65" s="47" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B65" s="48" t="inlineStr">
         <is>
-          <t>P160012</t>
+          <t>P160032</t>
         </is>
       </c>
       <c r="C65" s="49" t="inlineStr">
         <is>
-          <t>P160012</t>
+          <t>P160032</t>
         </is>
       </c>
       <c r="D65" s="49" t="inlineStr">
         <is>
-          <t>26.32%</t>
+          <t>24.78%</t>
         </is>
       </c>
       <c r="E65" s="49" t="inlineStr">
@@ -37248,7 +37324,7 @@
       </c>
       <c r="F65" s="49" t="inlineStr">
         <is>
-          <t>ППК26117</t>
+          <t>ППК26119</t>
         </is>
       </c>
       <c r="G65" s="49" t="inlineStr">
@@ -37267,88 +37343,46 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="B66" s="48" t="inlineStr">
-        <is>
-          <t>P160022</t>
-        </is>
-      </c>
-      <c r="C66" s="49" t="inlineStr">
-        <is>
-          <t>P160022</t>
-        </is>
-      </c>
-      <c r="D66" s="49" t="inlineStr">
-        <is>
-          <t>25.72%</t>
-        </is>
-      </c>
-      <c r="E66" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F66" s="49" t="inlineStr">
-        <is>
-          <t>ППК26118</t>
-        </is>
-      </c>
-      <c r="G66" s="49" t="inlineStr">
-        <is>
-          <t>06.07.2026</t>
-        </is>
-      </c>
-      <c r="H66" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I66" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
+    <row r="66" ht="19.5" customHeight="1">
+      <c r="A66" s="46" t="inlineStr">
+        <is>
+          <t>Graps &amp; Creme      1 batch(es)      Total Δ⁹-THC across batches: 11.53 %</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="47" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B67" s="48" t="inlineStr">
         <is>
-          <t>P160032</t>
-        </is>
-      </c>
-      <c r="C67" s="49" t="inlineStr">
-        <is>
-          <t>P160032</t>
-        </is>
-      </c>
+          <t>GRC102501-2</t>
+        </is>
+      </c>
+      <c r="C67" s="49" t="n"/>
       <c r="D67" s="49" t="inlineStr">
         <is>
-          <t>24.78%</t>
+          <t>11.53 %w/w (U ±0.71)</t>
         </is>
       </c>
       <c r="E67" s="49" t="inlineStr">
         <is>
-          <t>≥ 5.00 %</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F67" s="49" t="inlineStr">
         <is>
-          <t>ППК26119</t>
+          <t>051-6-K/26</t>
         </is>
       </c>
       <c r="G67" s="49" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>04.03.2026</t>
         </is>
       </c>
       <c r="H67" s="49" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="I67" s="49" t="inlineStr">
@@ -37360,285 +37394,305 @@
     <row r="68" ht="19.5" customHeight="1">
       <c r="A68" s="46" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme      1 batch(es)      Total Δ⁹-THC across batches: 11.53 %</t>
+          <t>High Pro Amnesia      3 batch(es)      Total Δ⁹-THC across batches: 14.97 – 22.43 %</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="B69" s="48" t="inlineStr">
-        <is>
-          <t>GRC102501-2</t>
-        </is>
-      </c>
-      <c r="C69" s="49" t="n"/>
-      <c r="D69" s="49" t="inlineStr">
-        <is>
-          <t>11.53 %w/w (U ±0.71)</t>
-        </is>
-      </c>
-      <c r="E69" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F69" s="49" t="inlineStr">
-        <is>
-          <t>051-6-K/26</t>
-        </is>
-      </c>
-      <c r="G69" s="49" t="inlineStr">
-        <is>
-          <t>04.03.2026</t>
-        </is>
-      </c>
-      <c r="H69" s="49" t="inlineStr">
+      <c r="A69" s="50" t="n">
+        <v>45</v>
+      </c>
+      <c r="B69" s="51" t="inlineStr">
+        <is>
+          <t>HPA1024_01</t>
+        </is>
+      </c>
+      <c r="C69" s="52" t="inlineStr">
+        <is>
+          <t>P050052</t>
+        </is>
+      </c>
+      <c r="D69" s="52" t="inlineStr">
+        <is>
+          <t>22.43%</t>
+        </is>
+      </c>
+      <c r="E69" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F69" s="52" t="inlineStr">
+        <is>
+          <t>НИК22155 (likely OCR misread of ППК25xxx)</t>
+        </is>
+      </c>
+      <c r="G69" s="52" t="inlineStr">
+        <is>
+          <t>24.06.2025</t>
+        </is>
+      </c>
+      <c r="H69" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I69" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="53" t="n"/>
+      <c r="B70" s="53" t="n"/>
+      <c r="C70" s="53" t="n"/>
+      <c r="D70" s="49" t="inlineStr">
+        <is>
+          <t>21.61 %w/w (U 1.33)</t>
+        </is>
+      </c>
+      <c r="E70" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F70" s="49" t="inlineStr">
+        <is>
+          <t>197-14-К/26</t>
+        </is>
+      </c>
+      <c r="G70" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H70" s="49" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I69" s="49" t="inlineStr">
+      <c r="I70" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="19.5" customHeight="1">
-      <c r="A70" s="46" t="inlineStr">
-        <is>
-          <t>High Pro Amnesia      3 batch(es)      Total Δ⁹-THC across batches: 14.97 – 22.43 %</t>
-        </is>
-      </c>
-    </row>
     <row r="71">
-      <c r="A71" s="50" t="n">
-        <v>45</v>
-      </c>
-      <c r="B71" s="51" t="inlineStr">
-        <is>
-          <t>HPA1024_01</t>
-        </is>
-      </c>
-      <c r="C71" s="52" t="inlineStr">
-        <is>
-          <t>P050052</t>
-        </is>
-      </c>
-      <c r="D71" s="52" t="inlineStr">
-        <is>
-          <t>22.43%</t>
-        </is>
-      </c>
-      <c r="E71" s="52" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F71" s="52" t="inlineStr">
-        <is>
-          <t>НИК22155 (likely OCR misread of ППК25xxx)</t>
-        </is>
-      </c>
-      <c r="G71" s="52" t="inlineStr">
-        <is>
-          <t>24.06.2025</t>
-        </is>
-      </c>
-      <c r="H71" s="52" t="inlineStr">
+      <c r="A71" s="47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B71" s="48" t="inlineStr">
+        <is>
+          <t>HPA052501</t>
+        </is>
+      </c>
+      <c r="C71" s="49" t="inlineStr">
+        <is>
+          <t>P050182</t>
+        </is>
+      </c>
+      <c r="D71" s="49" t="inlineStr">
+        <is>
+          <t>20.39%</t>
+        </is>
+      </c>
+      <c r="E71" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F71" s="49" t="inlineStr">
+        <is>
+          <t>ППК25278</t>
+        </is>
+      </c>
+      <c r="G71" s="49" t="inlineStr">
+        <is>
+          <t>19.09.2025</t>
+        </is>
+      </c>
+      <c r="H71" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I71" s="52" t="inlineStr">
+      <c r="I71" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="53" t="n"/>
-      <c r="B72" s="53" t="n"/>
-      <c r="C72" s="53" t="n"/>
-      <c r="D72" s="49" t="inlineStr">
-        <is>
-          <t>21.61 %w/w (U 1.33)</t>
-        </is>
-      </c>
-      <c r="E72" s="49" t="inlineStr">
+      <c r="A72" s="50" t="n">
+        <v>47</v>
+      </c>
+      <c r="B72" s="51" t="inlineStr">
+        <is>
+          <t>HPA1024</t>
+        </is>
+      </c>
+      <c r="C72" s="52" t="n"/>
+      <c r="D72" s="52" t="inlineStr">
+        <is>
+          <t>14.97%</t>
+        </is>
+      </c>
+      <c r="E72" s="52" t="inlineStr">
+        <is>
+          <t>12.6 – 15.4 %</t>
+        </is>
+      </c>
+      <c r="F72" s="52" t="inlineStr">
+        <is>
+          <t>n/a — Purely Plant in-house CoA (Batch HPA1024, no certificate/report number printed)</t>
+        </is>
+      </c>
+      <c r="G72" s="52" t="inlineStr">
+        <is>
+          <t>23.01.2025</t>
+        </is>
+      </c>
+      <c r="H72" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I72" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="53" t="n"/>
+      <c r="B73" s="53" t="n"/>
+      <c r="C73" s="53" t="n"/>
+      <c r="D73" s="49" t="inlineStr">
+        <is>
+          <t>17.31 %w/w (U 1.06 %w/w, k=2)</t>
+        </is>
+      </c>
+      <c r="E73" s="49" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F72" s="49" t="inlineStr">
-        <is>
-          <t>197-14-К/26</t>
-        </is>
-      </c>
-      <c r="G72" s="49" t="inlineStr">
+      <c r="F73" s="49" t="inlineStr">
+        <is>
+          <t>197-13-К/26</t>
+        </is>
+      </c>
+      <c r="G73" s="49" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H72" s="49" t="inlineStr">
+      <c r="H73" s="49" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I72" s="49" t="inlineStr">
+      <c r="I73" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B73" s="48" t="inlineStr">
-        <is>
-          <t>HPA052501</t>
-        </is>
-      </c>
-      <c r="C73" s="49" t="inlineStr">
-        <is>
-          <t>P050182</t>
-        </is>
-      </c>
-      <c r="D73" s="49" t="inlineStr">
-        <is>
-          <t>20.39%</t>
-        </is>
-      </c>
-      <c r="E73" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F73" s="49" t="inlineStr">
-        <is>
-          <t>ППК25278</t>
-        </is>
-      </c>
-      <c r="G73" s="49" t="inlineStr">
-        <is>
-          <t>19.09.2025</t>
-        </is>
-      </c>
-      <c r="H73" s="49" t="inlineStr">
+    <row r="74" ht="19.5" customHeight="1">
+      <c r="A74" s="46" t="inlineStr">
+        <is>
+          <t>Jelly Donutz      6 batch(es)      Total Δ⁹-THC across batches: 13.93 – 20.54 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="47" t="n">
+        <v>48</v>
+      </c>
+      <c r="B75" s="48" t="inlineStr">
+        <is>
+          <t>JD012601</t>
+        </is>
+      </c>
+      <c r="C75" s="49" t="n"/>
+      <c r="D75" s="49" t="inlineStr">
+        <is>
+          <t>18.16%</t>
+        </is>
+      </c>
+      <c r="E75" s="49" t="n"/>
+      <c r="F75" s="49" t="inlineStr">
+        <is>
+          <t>ППК26064</t>
+        </is>
+      </c>
+      <c r="G75" s="49" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H75" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I73" s="49" t="inlineStr">
+      <c r="I75" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B74" s="51" t="inlineStr">
-        <is>
-          <t>HPA1024</t>
-        </is>
-      </c>
-      <c r="C74" s="52" t="n"/>
-      <c r="D74" s="52" t="inlineStr">
-        <is>
-          <t>14.97%</t>
-        </is>
-      </c>
-      <c r="E74" s="52" t="inlineStr">
-        <is>
-          <t>12.6 – 15.4 %</t>
-        </is>
-      </c>
-      <c r="F74" s="52" t="inlineStr">
-        <is>
-          <t>n/a — Purely Plant in-house CoA (Batch HPA1024, no certificate/report number printed)</t>
-        </is>
-      </c>
-      <c r="G74" s="52" t="inlineStr">
-        <is>
-          <t>23.01.2025</t>
-        </is>
-      </c>
-      <c r="H74" s="52" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B76" s="51" t="inlineStr">
+        <is>
+          <t>JD112501</t>
+        </is>
+      </c>
+      <c r="C76" s="52" t="n"/>
+      <c r="D76" s="52" t="inlineStr">
+        <is>
+          <t>19.64%</t>
+        </is>
+      </c>
+      <c r="E76" s="52" t="n"/>
+      <c r="F76" s="52" t="inlineStr">
+        <is>
+          <t>ППК26063</t>
+        </is>
+      </c>
+      <c r="G76" s="52" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H76" s="52" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I74" s="52" t="inlineStr">
+      <c r="I76" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="53" t="n"/>
-      <c r="B75" s="53" t="n"/>
-      <c r="C75" s="53" t="n"/>
-      <c r="D75" s="49" t="inlineStr">
-        <is>
-          <t>17.31 %w/w (U 1.06 %w/w, k=2)</t>
-        </is>
-      </c>
-      <c r="E75" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F75" s="49" t="inlineStr">
-        <is>
-          <t>197-13-К/26</t>
-        </is>
-      </c>
-      <c r="G75" s="49" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H75" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I75" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="19.5" customHeight="1">
-      <c r="A76" s="46" t="inlineStr">
-        <is>
-          <t>Jelly Donutz      6 batch(es)      Total Δ⁹-THC across batches: 13.93 – 20.54 %</t>
-        </is>
-      </c>
-    </row>
     <row r="77">
-      <c r="A77" s="47" t="n">
-        <v>48</v>
-      </c>
-      <c r="B77" s="48" t="inlineStr">
-        <is>
-          <t>JD012601</t>
-        </is>
-      </c>
-      <c r="C77" s="49" t="n"/>
+      <c r="A77" s="53" t="n"/>
+      <c r="B77" s="53" t="n"/>
+      <c r="C77" s="53" t="n"/>
       <c r="D77" s="49" t="inlineStr">
         <is>
-          <t>18.16%</t>
+          <t>13.93%</t>
         </is>
       </c>
       <c r="E77" s="49" t="n"/>
       <c r="F77" s="49" t="inlineStr">
         <is>
-          <t>ППК26064</t>
+          <t>ППК26065</t>
         </is>
       </c>
       <c r="G77" s="49" t="inlineStr">
@@ -37658,60 +37712,74 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B78" s="51" t="inlineStr">
-        <is>
-          <t>JD112501</t>
-        </is>
-      </c>
-      <c r="C78" s="52" t="n"/>
-      <c r="D78" s="52" t="inlineStr">
-        <is>
-          <t>19.64%</t>
-        </is>
-      </c>
-      <c r="E78" s="52" t="n"/>
-      <c r="F78" s="52" t="inlineStr">
-        <is>
-          <t>ППК26063</t>
-        </is>
-      </c>
-      <c r="G78" s="52" t="inlineStr">
-        <is>
-          <t>11.05.2026</t>
-        </is>
-      </c>
-      <c r="H78" s="52" t="inlineStr">
+      <c r="A78" s="47" t="n">
+        <v>50</v>
+      </c>
+      <c r="B78" s="48" t="inlineStr">
+        <is>
+          <t>JD012603-02</t>
+        </is>
+      </c>
+      <c r="C78" s="49" t="n"/>
+      <c r="D78" s="49" t="inlineStr">
+        <is>
+          <t>20.54%</t>
+        </is>
+      </c>
+      <c r="E78" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F78" s="49" t="inlineStr">
+        <is>
+          <t>ППК26113</t>
+        </is>
+      </c>
+      <c r="G78" s="49" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="H78" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I78" s="52" t="inlineStr">
+      <c r="I78" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="53" t="n"/>
-      <c r="B79" s="53" t="n"/>
-      <c r="C79" s="53" t="n"/>
+      <c r="A79" s="47" t="n">
+        <v>51</v>
+      </c>
+      <c r="B79" s="48" t="inlineStr">
+        <is>
+          <t>JD012603-02V</t>
+        </is>
+      </c>
+      <c r="C79" s="49" t="n"/>
       <c r="D79" s="49" t="inlineStr">
         <is>
-          <t>13.93%</t>
-        </is>
-      </c>
-      <c r="E79" s="49" t="n"/>
+          <t>15.16%</t>
+        </is>
+      </c>
+      <c r="E79" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
       <c r="F79" s="49" t="inlineStr">
         <is>
-          <t>ППК26065</t>
+          <t>ППК26111</t>
         </is>
       </c>
       <c r="G79" s="49" t="inlineStr">
         <is>
-          <t>11.05.2026</t>
+          <t>30.06.2026</t>
         </is>
       </c>
       <c r="H79" s="49" t="inlineStr">
@@ -37727,17 +37795,17 @@
     </row>
     <row r="80">
       <c r="A80" s="47" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B80" s="48" t="inlineStr">
         <is>
-          <t>JD012603-02</t>
+          <t>JD022601</t>
         </is>
       </c>
       <c r="C80" s="49" t="n"/>
       <c r="D80" s="49" t="inlineStr">
         <is>
-          <t>20.54%</t>
+          <t>18.58%</t>
         </is>
       </c>
       <c r="E80" s="49" t="inlineStr">
@@ -37747,7 +37815,7 @@
       </c>
       <c r="F80" s="49" t="inlineStr">
         <is>
-          <t>ППК26113</t>
+          <t>ППК26115</t>
         </is>
       </c>
       <c r="G80" s="49" t="inlineStr">
@@ -37768,17 +37836,21 @@
     </row>
     <row r="81">
       <c r="A81" s="47" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B81" s="48" t="inlineStr">
         <is>
-          <t>JD012603-02V</t>
-        </is>
-      </c>
-      <c r="C81" s="49" t="n"/>
+          <t>P060212</t>
+        </is>
+      </c>
+      <c r="C81" s="49" t="inlineStr">
+        <is>
+          <t>P060212</t>
+        </is>
+      </c>
       <c r="D81" s="49" t="inlineStr">
         <is>
-          <t>15.16%</t>
+          <t>20.32 %w/w (U 1.25 %w/w, k=2)</t>
         </is>
       </c>
       <c r="E81" s="49" t="inlineStr">
@@ -37788,17 +37860,17 @@
       </c>
       <c r="F81" s="49" t="inlineStr">
         <is>
-          <t>ППК26111</t>
+          <t>197-15-К/26</t>
         </is>
       </c>
       <c r="G81" s="49" t="inlineStr">
         <is>
-          <t>30.06.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="H81" s="49" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="I81" s="49" t="inlineStr">
@@ -37807,79 +37879,41 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="B82" s="48" t="inlineStr">
-        <is>
-          <t>JD022601</t>
-        </is>
-      </c>
-      <c r="C82" s="49" t="n"/>
-      <c r="D82" s="49" t="inlineStr">
-        <is>
-          <t>18.58%</t>
-        </is>
-      </c>
-      <c r="E82" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F82" s="49" t="inlineStr">
-        <is>
-          <t>ППК26115</t>
-        </is>
-      </c>
-      <c r="G82" s="49" t="inlineStr">
-        <is>
-          <t>30.06.2026</t>
-        </is>
-      </c>
-      <c r="H82" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I82" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
+    <row r="82" ht="19.5" customHeight="1">
+      <c r="A82" s="46" t="inlineStr">
+        <is>
+          <t>Jokerz 31      4 batch(es)      Total Δ⁹-THC across batches: 17.32 – 25.27 %</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="47" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B83" s="48" t="inlineStr">
         <is>
-          <t>P060212</t>
-        </is>
-      </c>
-      <c r="C83" s="49" t="inlineStr">
-        <is>
-          <t>P060212</t>
-        </is>
-      </c>
+          <t>J31102501</t>
+        </is>
+      </c>
+      <c r="C83" s="49" t="n"/>
       <c r="D83" s="49" t="inlineStr">
         <is>
-          <t>20.32 %w/w (U 1.25 %w/w, k=2)</t>
+          <t>19.14 %w/w (U ±1.18)</t>
         </is>
       </c>
       <c r="E83" s="49" t="inlineStr">
         <is>
-          <t>≥ 5.00 %</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F83" s="49" t="inlineStr">
         <is>
-          <t>197-15-К/26</t>
+          <t>051-1-K/26</t>
         </is>
       </c>
       <c r="G83" s="49" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>04.03.2026</t>
         </is>
       </c>
       <c r="H83" s="49" t="inlineStr">
@@ -37893,26 +37927,54 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="19.5" customHeight="1">
-      <c r="A84" s="46" t="inlineStr">
-        <is>
-          <t>Jokerz 31      4 batch(es)      Total Δ⁹-THC across batches: 17.32 – 25.27 %</t>
+    <row r="84">
+      <c r="A84" s="50" t="n">
+        <v>55</v>
+      </c>
+      <c r="B84" s="51" t="inlineStr">
+        <is>
+          <t>J31112501</t>
+        </is>
+      </c>
+      <c r="C84" s="52" t="n"/>
+      <c r="D84" s="52" t="inlineStr">
+        <is>
+          <t>25.27 %w/w (U ±1.55)</t>
+        </is>
+      </c>
+      <c r="E84" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F84" s="52" t="inlineStr">
+        <is>
+          <t>051-5-K/26</t>
+        </is>
+      </c>
+      <c r="G84" s="52" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="H84" s="52" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I84" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="47" t="n">
-        <v>54</v>
-      </c>
-      <c r="B85" s="48" t="inlineStr">
-        <is>
-          <t>J31102501</t>
-        </is>
-      </c>
-      <c r="C85" s="49" t="n"/>
+      <c r="A85" s="53" t="n"/>
+      <c r="B85" s="53" t="n"/>
+      <c r="C85" s="53" t="n"/>
       <c r="D85" s="49" t="inlineStr">
         <is>
-          <t>19.14 %w/w (U ±1.18)</t>
+          <t>20.21 %w/w (U ±1.24)</t>
         </is>
       </c>
       <c r="E85" s="49" t="inlineStr">
@@ -37922,12 +37984,12 @@
       </c>
       <c r="F85" s="49" t="inlineStr">
         <is>
-          <t>051-1-K/26</t>
+          <t>100-1-K/26</t>
         </is>
       </c>
       <c r="G85" s="49" t="inlineStr">
         <is>
-          <t>04.03.2026</t>
+          <t>09.04.2026</t>
         </is>
       </c>
       <c r="H85" s="49" t="inlineStr">
@@ -37943,17 +38005,17 @@
     </row>
     <row r="86">
       <c r="A86" s="50" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B86" s="51" t="inlineStr">
         <is>
-          <t>J31112501</t>
+          <t>J31122501</t>
         </is>
       </c>
       <c r="C86" s="52" t="n"/>
       <c r="D86" s="52" t="inlineStr">
         <is>
-          <t>25.27 %w/w (U ±1.55)</t>
+          <t>19.84 %w/w (U ±1.22)</t>
         </is>
       </c>
       <c r="E86" s="52" t="inlineStr">
@@ -37963,12 +38025,12 @@
       </c>
       <c r="F86" s="52" t="inlineStr">
         <is>
-          <t>051-5-K/26</t>
+          <t>100-2-К/26</t>
         </is>
       </c>
       <c r="G86" s="52" t="inlineStr">
         <is>
-          <t>04.03.2026</t>
+          <t>09.04.2026</t>
         </is>
       </c>
       <c r="H86" s="52" t="inlineStr">
@@ -37988,7 +38050,7 @@
       <c r="C87" s="53" t="n"/>
       <c r="D87" s="49" t="inlineStr">
         <is>
-          <t>20.21 %w/w (U ±1.24)</t>
+          <t>21.84 %w/w (U ±1.34)</t>
         </is>
       </c>
       <c r="E87" s="49" t="inlineStr">
@@ -37998,7 +38060,7 @@
       </c>
       <c r="F87" s="49" t="inlineStr">
         <is>
-          <t>100-1-K/26</t>
+          <t>100-3-К/26</t>
         </is>
       </c>
       <c r="G87" s="49" t="inlineStr">
@@ -38018,113 +38080,85 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="50" t="n">
-        <v>56</v>
-      </c>
-      <c r="B88" s="51" t="inlineStr">
-        <is>
-          <t>J31122501</t>
-        </is>
-      </c>
-      <c r="C88" s="52" t="n"/>
-      <c r="D88" s="52" t="inlineStr">
-        <is>
-          <t>19.84 %w/w (U ±1.22)</t>
-        </is>
-      </c>
-      <c r="E88" s="52" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F88" s="52" t="inlineStr">
-        <is>
-          <t>100-2-К/26</t>
-        </is>
-      </c>
-      <c r="G88" s="52" t="inlineStr">
-        <is>
-          <t>09.04.2026</t>
-        </is>
-      </c>
-      <c r="H88" s="52" t="inlineStr">
+      <c r="A88" s="47" t="n">
+        <v>57</v>
+      </c>
+      <c r="B88" s="48" t="inlineStr">
+        <is>
+          <t>P060152</t>
+        </is>
+      </c>
+      <c r="C88" s="49" t="inlineStr">
+        <is>
+          <t>P060152</t>
+        </is>
+      </c>
+      <c r="D88" s="49" t="inlineStr">
+        <is>
+          <t>17.32 %w/w (U 1.06 %w/w, k=2)</t>
+        </is>
+      </c>
+      <c r="E88" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F88" s="49" t="inlineStr">
+        <is>
+          <t>197-16-К/26</t>
+        </is>
+      </c>
+      <c r="G88" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H88" s="49" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I88" s="52" t="inlineStr">
+      <c r="I88" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="53" t="n"/>
-      <c r="B89" s="53" t="n"/>
-      <c r="C89" s="53" t="n"/>
-      <c r="D89" s="49" t="inlineStr">
-        <is>
-          <t>21.84 %w/w (U ±1.34)</t>
-        </is>
-      </c>
-      <c r="E89" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F89" s="49" t="inlineStr">
-        <is>
-          <t>100-3-К/26</t>
-        </is>
-      </c>
-      <c r="G89" s="49" t="inlineStr">
-        <is>
-          <t>09.04.2026</t>
-        </is>
-      </c>
-      <c r="H89" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I89" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
+    <row r="89" ht="19.5" customHeight="1">
+      <c r="A89" s="46" t="inlineStr">
+        <is>
+          <t>Kush Crasher      1 batch(es)      Total Δ⁹-THC across batches: 17.04 %</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="47" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B90" s="48" t="inlineStr">
         <is>
-          <t>P060152</t>
-        </is>
-      </c>
-      <c r="C90" s="49" t="inlineStr">
-        <is>
-          <t>P060152</t>
-        </is>
-      </c>
+          <t>KC102501</t>
+        </is>
+      </c>
+      <c r="C90" s="49" t="n"/>
       <c r="D90" s="49" t="inlineStr">
         <is>
-          <t>17.32 %w/w (U 1.06 %w/w, k=2)</t>
+          <t>17.04 %w/w (U ±1.05)</t>
         </is>
       </c>
       <c r="E90" s="49" t="inlineStr">
         <is>
-          <t>≥ 5.00 %</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F90" s="49" t="inlineStr">
         <is>
-          <t>197-16-К/26</t>
+          <t>051-4-K/26</t>
         </is>
       </c>
       <c r="G90" s="49" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>04.03.2026</t>
         </is>
       </c>
       <c r="H90" s="49" t="inlineStr">
@@ -38141,23 +38175,27 @@
     <row r="91" ht="19.5" customHeight="1">
       <c r="A91" s="46" t="inlineStr">
         <is>
-          <t>Kush Crasher      1 batch(es)      Total Δ⁹-THC across batches: 17.04 %</t>
+          <t>Motor Breath      2 batch(es)      Total Δ⁹-THC across batches: 16.82 – 18.67 %</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="47" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B92" s="48" t="inlineStr">
         <is>
-          <t>KC102501</t>
-        </is>
-      </c>
-      <c r="C92" s="49" t="n"/>
+          <t>MB0824_04</t>
+        </is>
+      </c>
+      <c r="C92" s="49" t="inlineStr">
+        <is>
+          <t>P050032</t>
+        </is>
+      </c>
       <c r="D92" s="49" t="inlineStr">
         <is>
-          <t>17.04 %w/w (U ±1.05)</t>
+          <t>18.67%</t>
         </is>
       </c>
       <c r="E92" s="49" t="inlineStr">
@@ -38167,17 +38205,17 @@
       </c>
       <c r="F92" s="49" t="inlineStr">
         <is>
-          <t>051-4-K/26</t>
+          <t>ППК25118</t>
         </is>
       </c>
       <c r="G92" s="49" t="inlineStr">
         <is>
-          <t>04.03.2026</t>
+          <t>06.05.2025</t>
         </is>
       </c>
       <c r="H92" s="49" t="inlineStr">
         <is>
-          <t>Farmahem</t>
+          <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
       <c r="I92" s="49" t="inlineStr">
@@ -38186,75 +38224,75 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="19.5" customHeight="1">
-      <c r="A93" s="46" t="inlineStr">
-        <is>
-          <t>Motor Breath      2 batch(es)      Total Δ⁹-THC across batches: 16.82 – 18.67 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="B94" s="48" t="inlineStr">
-        <is>
-          <t>MB0824_04</t>
-        </is>
-      </c>
-      <c r="C94" s="49" t="inlineStr">
-        <is>
-          <t>P050032</t>
-        </is>
-      </c>
-      <c r="D94" s="49" t="inlineStr">
-        <is>
-          <t>18.67%</t>
-        </is>
-      </c>
-      <c r="E94" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F94" s="49" t="inlineStr">
-        <is>
-          <t>ППК25118</t>
-        </is>
-      </c>
-      <c r="G94" s="49" t="inlineStr">
-        <is>
-          <t>06.05.2025</t>
-        </is>
-      </c>
-      <c r="H94" s="49" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="47" t="n">
+        <v>60</v>
+      </c>
+      <c r="B93" s="48" t="inlineStr">
+        <is>
+          <t>MB0824_05</t>
+        </is>
+      </c>
+      <c r="C93" s="49" t="inlineStr">
+        <is>
+          <t>P050112</t>
+        </is>
+      </c>
+      <c r="D93" s="49" t="inlineStr">
+        <is>
+          <t>16.82%</t>
+        </is>
+      </c>
+      <c r="E93" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F93" s="49" t="inlineStr">
+        <is>
+          <t>ППК25211</t>
+        </is>
+      </c>
+      <c r="G93" s="49" t="inlineStr">
+        <is>
+          <t>28.07.2025</t>
+        </is>
+      </c>
+      <c r="H93" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I94" s="49" t="inlineStr">
+      <c r="I93" s="49" t="inlineStr">
         <is>
           <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="19.5" customHeight="1">
+      <c r="A94" s="46" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa      9 batch(es)      Total Δ⁹-THC across batches: 7.91 – 20.03 %</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="47" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B95" s="48" t="inlineStr">
         <is>
-          <t>MB0824_05</t>
+          <t>OPM1024_01</t>
         </is>
       </c>
       <c r="C95" s="49" t="inlineStr">
         <is>
-          <t>P050112</t>
+          <t>P050042</t>
         </is>
       </c>
       <c r="D95" s="49" t="inlineStr">
         <is>
-          <t>16.82%</t>
+          <t>15.38%</t>
         </is>
       </c>
       <c r="E95" s="49" t="inlineStr">
@@ -38264,149 +38302,187 @@
       </c>
       <c r="F95" s="49" t="inlineStr">
         <is>
-          <t>ППК25211</t>
+          <t>ППК25117</t>
         </is>
       </c>
       <c r="G95" s="49" t="inlineStr">
         <is>
+          <t>06.05.2025</t>
+        </is>
+      </c>
+      <c r="H95" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I95" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="50" t="n">
+        <v>62</v>
+      </c>
+      <c r="B96" s="51" t="inlineStr">
+        <is>
+          <t>OPM1024_02</t>
+        </is>
+      </c>
+      <c r="C96" s="52" t="inlineStr">
+        <is>
+          <t>P050062</t>
+        </is>
+      </c>
+      <c r="D96" s="52" t="inlineStr">
+        <is>
+          <t>18.27%</t>
+        </is>
+      </c>
+      <c r="E96" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F96" s="52" t="inlineStr">
+        <is>
+          <t>ППК25154</t>
+        </is>
+      </c>
+      <c r="G96" s="52" t="inlineStr">
+        <is>
+          <t>24.06.2025</t>
+        </is>
+      </c>
+      <c r="H96" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I96" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="53" t="n"/>
+      <c r="B97" s="53" t="n"/>
+      <c r="C97" s="53" t="n"/>
+      <c r="D97" s="49" t="inlineStr">
+        <is>
+          <t>18.04 %w/w (U 1.11)</t>
+        </is>
+      </c>
+      <c r="E97" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F97" s="49" t="inlineStr">
+        <is>
+          <t>197-18-К/26</t>
+        </is>
+      </c>
+      <c r="G97" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H97" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I97" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="47" t="n">
+        <v>63</v>
+      </c>
+      <c r="B98" s="48" t="inlineStr">
+        <is>
+          <t>OPM1024_03</t>
+        </is>
+      </c>
+      <c r="C98" s="49" t="inlineStr">
+        <is>
+          <t>P050082</t>
+        </is>
+      </c>
+      <c r="D98" s="49" t="inlineStr">
+        <is>
+          <t>16.55%</t>
+        </is>
+      </c>
+      <c r="E98" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F98" s="49" t="inlineStr">
+        <is>
+          <t>ППК25210</t>
+        </is>
+      </c>
+      <c r="G98" s="49" t="inlineStr">
+        <is>
           <t>28.07.2025</t>
         </is>
       </c>
-      <c r="H95" s="49" t="inlineStr">
+      <c r="H98" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I95" s="49" t="inlineStr">
+      <c r="I98" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="19.5" customHeight="1">
-      <c r="A96" s="46" t="inlineStr">
-        <is>
-          <t>Orange Punch Mimosa      9 batch(es)      Total Δ⁹-THC across batches: 7.91 – 20.03 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="B97" s="48" t="inlineStr">
-        <is>
-          <t>OPM1024_01</t>
-        </is>
-      </c>
-      <c r="C97" s="49" t="inlineStr">
-        <is>
-          <t>P050042</t>
-        </is>
-      </c>
-      <c r="D97" s="49" t="inlineStr">
-        <is>
-          <t>15.38%</t>
-        </is>
-      </c>
-      <c r="E97" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F97" s="49" t="inlineStr">
-        <is>
-          <t>ППК25117</t>
-        </is>
-      </c>
-      <c r="G97" s="49" t="inlineStr">
-        <is>
-          <t>06.05.2025</t>
-        </is>
-      </c>
-      <c r="H97" s="49" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="47" t="n">
+        <v>64</v>
+      </c>
+      <c r="B99" s="48" t="inlineStr">
+        <is>
+          <t>OPM052501</t>
+        </is>
+      </c>
+      <c r="C99" s="49" t="inlineStr">
+        <is>
+          <t>P050132</t>
+        </is>
+      </c>
+      <c r="D99" s="49" t="inlineStr">
+        <is>
+          <t>14.16%</t>
+        </is>
+      </c>
+      <c r="E99" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F99" s="49" t="inlineStr">
+        <is>
+          <t>ППК25257</t>
+        </is>
+      </c>
+      <c r="G99" s="49" t="inlineStr">
+        <is>
+          <t>05.09.2025</t>
+        </is>
+      </c>
+      <c r="H99" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I97" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="50" t="n">
-        <v>62</v>
-      </c>
-      <c r="B98" s="51" t="inlineStr">
-        <is>
-          <t>OPM1024_02</t>
-        </is>
-      </c>
-      <c r="C98" s="52" t="inlineStr">
-        <is>
-          <t>P050062</t>
-        </is>
-      </c>
-      <c r="D98" s="52" t="inlineStr">
-        <is>
-          <t>18.27%</t>
-        </is>
-      </c>
-      <c r="E98" s="52" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F98" s="52" t="inlineStr">
-        <is>
-          <t>ППК25154</t>
-        </is>
-      </c>
-      <c r="G98" s="52" t="inlineStr">
-        <is>
-          <t>24.06.2025</t>
-        </is>
-      </c>
-      <c r="H98" s="52" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I98" s="52" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="53" t="n"/>
-      <c r="B99" s="53" t="n"/>
-      <c r="C99" s="53" t="n"/>
-      <c r="D99" s="49" t="inlineStr">
-        <is>
-          <t>18.04 %w/w (U 1.11)</t>
-        </is>
-      </c>
-      <c r="E99" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F99" s="49" t="inlineStr">
-        <is>
-          <t>197-18-К/26</t>
-        </is>
-      </c>
-      <c r="G99" s="49" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H99" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
         </is>
       </c>
       <c r="I99" s="49" t="inlineStr">
@@ -38417,36 +38493,36 @@
     </row>
     <row r="100">
       <c r="A100" s="47" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B100" s="48" t="inlineStr">
         <is>
-          <t>OPM1024_03</t>
+          <t>OPM092501</t>
         </is>
       </c>
       <c r="C100" s="49" t="inlineStr">
         <is>
-          <t>P050082</t>
+          <t>P060042</t>
         </is>
       </c>
       <c r="D100" s="49" t="inlineStr">
         <is>
-          <t>16.55%</t>
+          <t>9.43%</t>
         </is>
       </c>
       <c r="E100" s="49" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>8.48 – 10.37 %</t>
         </is>
       </c>
       <c r="F100" s="49" t="inlineStr">
         <is>
-          <t>ППК25210</t>
+          <t>ППК26008</t>
         </is>
       </c>
       <c r="G100" s="49" t="inlineStr">
         <is>
-          <t>28.07.2025</t>
+          <t>21.01.2026</t>
         </is>
       </c>
       <c r="H100" s="49" t="inlineStr">
@@ -38462,21 +38538,17 @@
     </row>
     <row r="101">
       <c r="A101" s="47" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B101" s="48" t="inlineStr">
         <is>
-          <t>OPM052501</t>
-        </is>
-      </c>
-      <c r="C101" s="49" t="inlineStr">
-        <is>
-          <t>P050132</t>
-        </is>
-      </c>
+          <t>OPM112501</t>
+        </is>
+      </c>
+      <c r="C101" s="49" t="n"/>
       <c r="D101" s="49" t="inlineStr">
         <is>
-          <t>14.16%</t>
+          <t>8.00%</t>
         </is>
       </c>
       <c r="E101" s="49" t="inlineStr">
@@ -38486,12 +38558,12 @@
       </c>
       <c r="F101" s="49" t="inlineStr">
         <is>
-          <t>ППК25257</t>
+          <t>ППК26031</t>
         </is>
       </c>
       <c r="G101" s="49" t="inlineStr">
         <is>
-          <t>05.09.2025</t>
+          <t>05.03.2026</t>
         </is>
       </c>
       <c r="H101" s="49" t="inlineStr">
@@ -38507,41 +38579,37 @@
     </row>
     <row r="102">
       <c r="A102" s="47" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B102" s="48" t="inlineStr">
         <is>
-          <t>OPM092501</t>
-        </is>
-      </c>
-      <c r="C102" s="49" t="inlineStr">
-        <is>
-          <t>P060042</t>
-        </is>
-      </c>
+          <t>OPM122501</t>
+        </is>
+      </c>
+      <c r="C102" s="49" t="n"/>
       <c r="D102" s="49" t="inlineStr">
         <is>
-          <t>9.43%</t>
+          <t>8.09 %w/w (U ±0.50)</t>
         </is>
       </c>
       <c r="E102" s="49" t="inlineStr">
         <is>
-          <t>8.48 – 10.37 %</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F102" s="49" t="inlineStr">
         <is>
-          <t>ППК26008</t>
+          <t>100-4-К/26</t>
         </is>
       </c>
       <c r="G102" s="49" t="inlineStr">
         <is>
-          <t>21.01.2026</t>
+          <t>09.04.2026</t>
         </is>
       </c>
       <c r="H102" s="49" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="I102" s="49" t="inlineStr">
@@ -38552,367 +38620,329 @@
     </row>
     <row r="103">
       <c r="A103" s="47" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B103" s="48" t="inlineStr">
         <is>
-          <t>OPM112501</t>
-        </is>
-      </c>
-      <c r="C103" s="49" t="n"/>
+          <t>P060242</t>
+        </is>
+      </c>
+      <c r="C103" s="49" t="inlineStr">
+        <is>
+          <t>P060242</t>
+        </is>
+      </c>
       <c r="D103" s="49" t="inlineStr">
         <is>
-          <t>8.00%</t>
+          <t>7.91 %w/w (U 0.49 %w/w, k=2)</t>
         </is>
       </c>
       <c r="E103" s="49" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>≥ 5.00 %</t>
         </is>
       </c>
       <c r="F103" s="49" t="inlineStr">
         <is>
-          <t>ППК26031</t>
+          <t>197-19-К/26</t>
         </is>
       </c>
       <c r="G103" s="49" t="inlineStr">
         <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H103" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I103" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="50" t="n">
+        <v>69</v>
+      </c>
+      <c r="B104" s="51" t="inlineStr">
+        <is>
+          <t>OPM1024</t>
+        </is>
+      </c>
+      <c r="C104" s="52" t="n"/>
+      <c r="D104" s="52" t="inlineStr">
+        <is>
+          <t>19.96%</t>
+        </is>
+      </c>
+      <c r="E104" s="52" t="inlineStr">
+        <is>
+          <t>18.0 – 22.0 %</t>
+        </is>
+      </c>
+      <c r="F104" s="52" t="inlineStr">
+        <is>
+          <t>n/a — Purely Plant in-house CoA (Batch OPM1024, no certificate/report number printed)</t>
+        </is>
+      </c>
+      <c r="G104" s="52" t="inlineStr">
+        <is>
+          <t>23.04.2025</t>
+        </is>
+      </c>
+      <c r="H104" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I104" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="53" t="n"/>
+      <c r="B105" s="53" t="n"/>
+      <c r="C105" s="53" t="n"/>
+      <c r="D105" s="49" t="inlineStr">
+        <is>
+          <t>20.03 %w/w (U 1.23 %w/w, k=2)</t>
+        </is>
+      </c>
+      <c r="E105" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F105" s="49" t="inlineStr">
+        <is>
+          <t>197-17-К/26</t>
+        </is>
+      </c>
+      <c r="G105" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H105" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I105" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="19.5" customHeight="1">
+      <c r="A106" s="46" t="inlineStr">
+        <is>
+          <t>Permanent Market      3 batch(es)      Total Δ⁹-THC across batches: 10.01 – 14.06 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="47" t="n">
+        <v>70</v>
+      </c>
+      <c r="B107" s="48" t="inlineStr">
+        <is>
+          <t>PM072501</t>
+        </is>
+      </c>
+      <c r="C107" s="49" t="inlineStr">
+        <is>
+          <t>P050272</t>
+        </is>
+      </c>
+      <c r="D107" s="49" t="inlineStr">
+        <is>
+          <t>10.01%</t>
+        </is>
+      </c>
+      <c r="E107" s="49" t="inlineStr">
+        <is>
+          <t>9 – 11.01 %</t>
+        </is>
+      </c>
+      <c r="F107" s="49" t="inlineStr">
+        <is>
+          <t>ППК25368</t>
+        </is>
+      </c>
+      <c r="G107" s="49" t="inlineStr">
+        <is>
+          <t>28.11.2025</t>
+        </is>
+      </c>
+      <c r="H107" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I107" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="50" t="n">
+        <v>71</v>
+      </c>
+      <c r="B108" s="51" t="inlineStr">
+        <is>
+          <t>PM092501</t>
+        </is>
+      </c>
+      <c r="C108" s="52" t="inlineStr">
+        <is>
+          <t>P060062</t>
+        </is>
+      </c>
+      <c r="D108" s="52" t="inlineStr">
+        <is>
+          <t>14.06%</t>
+        </is>
+      </c>
+      <c r="E108" s="52" t="inlineStr">
+        <is>
+          <t>12.65 – 15.46 %</t>
+        </is>
+      </c>
+      <c r="F108" s="52" t="inlineStr">
+        <is>
+          <t>ППК26004</t>
+        </is>
+      </c>
+      <c r="G108" s="52" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H108" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I108" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="53" t="n"/>
+      <c r="B109" s="53" t="n"/>
+      <c r="C109" s="53" t="n"/>
+      <c r="D109" s="49" t="inlineStr">
+        <is>
+          <t>12.25% w/w (U 0.75% w/w)</t>
+        </is>
+      </c>
+      <c r="E109" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F109" s="49" t="inlineStr">
+        <is>
+          <t>197-20-К/26</t>
+        </is>
+      </c>
+      <c r="G109" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H109" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I109" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="47" t="n">
+        <v>72</v>
+      </c>
+      <c r="B110" s="48" t="inlineStr">
+        <is>
+          <t>PM112501</t>
+        </is>
+      </c>
+      <c r="C110" s="49" t="n"/>
+      <c r="D110" s="49" t="inlineStr">
+        <is>
+          <t>13.33%</t>
+        </is>
+      </c>
+      <c r="E110" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F110" s="49" t="inlineStr">
+        <is>
+          <t>ППК26030</t>
+        </is>
+      </c>
+      <c r="G110" s="49" t="inlineStr">
+        <is>
           <t>05.03.2026</t>
         </is>
       </c>
-      <c r="H103" s="49" t="inlineStr">
+      <c r="H110" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I103" s="49" t="inlineStr">
+      <c r="I110" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="47" t="n">
-        <v>67</v>
-      </c>
-      <c r="B104" s="48" t="inlineStr">
-        <is>
-          <t>OPM122501</t>
-        </is>
-      </c>
-      <c r="C104" s="49" t="n"/>
-      <c r="D104" s="49" t="inlineStr">
-        <is>
-          <t>8.09 %w/w (U ±0.50)</t>
-        </is>
-      </c>
-      <c r="E104" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F104" s="49" t="inlineStr">
-        <is>
-          <t>100-4-К/26</t>
-        </is>
-      </c>
-      <c r="G104" s="49" t="inlineStr">
-        <is>
-          <t>09.04.2026</t>
-        </is>
-      </c>
-      <c r="H104" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I104" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="47" t="n">
-        <v>68</v>
-      </c>
-      <c r="B105" s="48" t="inlineStr">
-        <is>
-          <t>P060242</t>
-        </is>
-      </c>
-      <c r="C105" s="49" t="inlineStr">
-        <is>
-          <t>P060242</t>
-        </is>
-      </c>
-      <c r="D105" s="49" t="inlineStr">
-        <is>
-          <t>7.91 %w/w (U 0.49 %w/w, k=2)</t>
-        </is>
-      </c>
-      <c r="E105" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F105" s="49" t="inlineStr">
-        <is>
-          <t>197-19-К/26</t>
-        </is>
-      </c>
-      <c r="G105" s="49" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H105" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I105" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="50" t="n">
-        <v>69</v>
-      </c>
-      <c r="B106" s="51" t="inlineStr">
-        <is>
-          <t>OPM1024</t>
-        </is>
-      </c>
-      <c r="C106" s="52" t="n"/>
-      <c r="D106" s="52" t="inlineStr">
-        <is>
-          <t>19.96%</t>
-        </is>
-      </c>
-      <c r="E106" s="52" t="inlineStr">
-        <is>
-          <t>18.0 – 22.0 %</t>
-        </is>
-      </c>
-      <c r="F106" s="52" t="inlineStr">
-        <is>
-          <t>n/a — Purely Plant in-house CoA (Batch OPM1024, no certificate/report number printed)</t>
-        </is>
-      </c>
-      <c r="G106" s="52" t="inlineStr">
-        <is>
-          <t>23.04.2025</t>
-        </is>
-      </c>
-      <c r="H106" s="52" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I106" s="52" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="53" t="n"/>
-      <c r="B107" s="53" t="n"/>
-      <c r="C107" s="53" t="n"/>
-      <c r="D107" s="49" t="inlineStr">
-        <is>
-          <t>20.03 %w/w (U 1.23 %w/w, k=2)</t>
-        </is>
-      </c>
-      <c r="E107" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F107" s="49" t="inlineStr">
-        <is>
-          <t>197-17-К/26</t>
-        </is>
-      </c>
-      <c r="G107" s="49" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H107" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I107" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="19.5" customHeight="1">
-      <c r="A108" s="46" t="inlineStr">
-        <is>
-          <t>Permanent Market      3 batch(es)      Total Δ⁹-THC across batches: 10.01 – 14.06 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="47" t="n">
-        <v>70</v>
-      </c>
-      <c r="B109" s="48" t="inlineStr">
-        <is>
-          <t>PM072501</t>
-        </is>
-      </c>
-      <c r="C109" s="49" t="inlineStr">
-        <is>
-          <t>P050272</t>
-        </is>
-      </c>
-      <c r="D109" s="49" t="inlineStr">
-        <is>
-          <t>10.01%</t>
-        </is>
-      </c>
-      <c r="E109" s="49" t="inlineStr">
-        <is>
-          <t>9 – 11.01 %</t>
-        </is>
-      </c>
-      <c r="F109" s="49" t="inlineStr">
-        <is>
-          <t>ППК25368</t>
-        </is>
-      </c>
-      <c r="G109" s="49" t="inlineStr">
-        <is>
-          <t>28.11.2025</t>
-        </is>
-      </c>
-      <c r="H109" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I109" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="50" t="n">
-        <v>71</v>
-      </c>
-      <c r="B110" s="51" t="inlineStr">
-        <is>
-          <t>PM092501</t>
-        </is>
-      </c>
-      <c r="C110" s="52" t="inlineStr">
-        <is>
-          <t>P060062</t>
-        </is>
-      </c>
-      <c r="D110" s="52" t="inlineStr">
-        <is>
-          <t>14.06%</t>
-        </is>
-      </c>
-      <c r="E110" s="52" t="inlineStr">
-        <is>
-          <t>12.65 – 15.46 %</t>
-        </is>
-      </c>
-      <c r="F110" s="52" t="inlineStr">
-        <is>
-          <t>ППК26004</t>
-        </is>
-      </c>
-      <c r="G110" s="52" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H110" s="52" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I110" s="52" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="53" t="n"/>
-      <c r="B111" s="53" t="n"/>
-      <c r="C111" s="53" t="n"/>
-      <c r="D111" s="49" t="inlineStr">
-        <is>
-          <t>12.25% w/w (U 0.75% w/w)</t>
-        </is>
-      </c>
-      <c r="E111" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F111" s="49" t="inlineStr">
-        <is>
-          <t>197-20-К/26</t>
-        </is>
-      </c>
-      <c r="G111" s="49" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H111" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I111" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
+    <row r="111" ht="19.5" customHeight="1">
+      <c r="A111" s="46" t="inlineStr">
+        <is>
+          <t>Scrambler      3 batch(es)      Total Δ⁹-THC across batches: 17.13 – 21.92 %</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="47" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B112" s="48" t="inlineStr">
         <is>
-          <t>PM112501</t>
+          <t>SCR112501</t>
         </is>
       </c>
       <c r="C112" s="49" t="n"/>
       <c r="D112" s="49" t="inlineStr">
         <is>
-          <t>13.33%</t>
-        </is>
-      </c>
-      <c r="E112" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>17.13%</t>
+        </is>
+      </c>
+      <c r="E112" s="49" t="n"/>
       <c r="F112" s="49" t="inlineStr">
         <is>
-          <t>ППК26030</t>
+          <t>ППК26069</t>
         </is>
       </c>
       <c r="G112" s="49" t="inlineStr">
         <is>
-          <t>05.03.2026</t>
+          <t>11.05.2026</t>
         </is>
       </c>
       <c r="H112" s="49" t="inlineStr">
@@ -38926,42 +38956,84 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="19.5" customHeight="1">
-      <c r="A113" s="46" t="inlineStr">
-        <is>
-          <t>Scrambler      3 batch(es)      Total Δ⁹-THC across batches: 17.13 – 21.92 %</t>
+    <row r="113">
+      <c r="A113" s="47" t="n">
+        <v>74</v>
+      </c>
+      <c r="B113" s="48" t="inlineStr">
+        <is>
+          <t>SCR022601</t>
+        </is>
+      </c>
+      <c r="C113" s="49" t="n"/>
+      <c r="D113" s="49" t="inlineStr">
+        <is>
+          <t>21.92%</t>
+        </is>
+      </c>
+      <c r="E113" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F113" s="49" t="inlineStr">
+        <is>
+          <t>ППК26116</t>
+        </is>
+      </c>
+      <c r="G113" s="49" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="H113" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I113" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="47" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B114" s="48" t="inlineStr">
         <is>
-          <t>SCR112501</t>
-        </is>
-      </c>
-      <c r="C114" s="49" t="n"/>
+          <t>P060382</t>
+        </is>
+      </c>
+      <c r="C114" s="49" t="inlineStr">
+        <is>
+          <t>P060382</t>
+        </is>
+      </c>
       <c r="D114" s="49" t="inlineStr">
         <is>
-          <t>17.13%</t>
-        </is>
-      </c>
-      <c r="E114" s="49" t="n"/>
+          <t>17.84 %w/w (U 1.10 %w/w, k=2)</t>
+        </is>
+      </c>
+      <c r="E114" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
       <c r="F114" s="49" t="inlineStr">
         <is>
-          <t>ППК26069</t>
+          <t>197-21-К/26</t>
         </is>
       </c>
       <c r="G114" s="49" t="inlineStr">
         <is>
-          <t>11.05.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="H114" s="49" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="I114" s="49" t="inlineStr">
@@ -38970,136 +39042,132 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="47" t="n">
-        <v>74</v>
-      </c>
-      <c r="B115" s="48" t="inlineStr">
-        <is>
-          <t>SCR022601</t>
-        </is>
-      </c>
-      <c r="C115" s="49" t="n"/>
-      <c r="D115" s="49" t="inlineStr">
-        <is>
-          <t>21.92%</t>
-        </is>
-      </c>
-      <c r="E115" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F115" s="49" t="inlineStr">
-        <is>
-          <t>ППК26116</t>
-        </is>
-      </c>
-      <c r="G115" s="49" t="inlineStr">
-        <is>
-          <t>06.07.2026</t>
-        </is>
-      </c>
-      <c r="H115" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I115" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
+    <row r="115" ht="19.5" customHeight="1">
+      <c r="A115" s="46" t="inlineStr">
+        <is>
+          <t>Sleepy Joy      3 batch(es)      Total Δ⁹-THC across batches: 9.20 – 11.20 %</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="47" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B116" s="48" t="inlineStr">
         <is>
-          <t>P060382</t>
+          <t>SJ092501</t>
         </is>
       </c>
       <c r="C116" s="49" t="inlineStr">
         <is>
-          <t>P060382</t>
+          <t>P060082</t>
         </is>
       </c>
       <c r="D116" s="49" t="inlineStr">
         <is>
-          <t>17.84 %w/w (U 1.10 %w/w, k=2)</t>
+          <t>10.96%</t>
         </is>
       </c>
       <c r="E116" s="49" t="inlineStr">
         <is>
-          <t>≥ 5.00 %</t>
+          <t>9.86 – 12.05 %</t>
         </is>
       </c>
       <c r="F116" s="49" t="inlineStr">
         <is>
-          <t>197-21-К/26</t>
+          <t>ППК26006</t>
         </is>
       </c>
       <c r="G116" s="49" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>21.01.2026</t>
         </is>
       </c>
       <c r="H116" s="49" t="inlineStr">
         <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I116" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="47" t="n">
+        <v>77</v>
+      </c>
+      <c r="B117" s="48" t="inlineStr">
+        <is>
+          <t>SJ102501</t>
+        </is>
+      </c>
+      <c r="C117" s="49" t="n"/>
+      <c r="D117" s="49" t="inlineStr">
+        <is>
+          <t>11.20 %w/w (U ±0.69)</t>
+        </is>
+      </c>
+      <c r="E117" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F117" s="49" t="inlineStr">
+        <is>
+          <t>051-3-K/26</t>
+        </is>
+      </c>
+      <c r="G117" s="49" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="H117" s="49" t="inlineStr">
+        <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I116" s="49" t="inlineStr">
+      <c r="I117" s="49" t="inlineStr">
         <is>
           <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="19.5" customHeight="1">
-      <c r="A117" s="46" t="inlineStr">
-        <is>
-          <t>Sleepy Joy      3 batch(es)      Total Δ⁹-THC across batches: 9.20 – 11.20 %</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="47" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B118" s="48" t="inlineStr">
         <is>
-          <t>SJ092501</t>
-        </is>
-      </c>
-      <c r="C118" s="49" t="inlineStr">
-        <is>
-          <t>P060082</t>
-        </is>
-      </c>
+          <t>SJ112501</t>
+        </is>
+      </c>
+      <c r="C118" s="49" t="n"/>
       <c r="D118" s="49" t="inlineStr">
         <is>
-          <t>10.96%</t>
+          <t>9.20 %w/w (U ±0.57)</t>
         </is>
       </c>
       <c r="E118" s="49" t="inlineStr">
         <is>
-          <t>9.86 – 12.05 %</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F118" s="49" t="inlineStr">
         <is>
-          <t>ППК26006</t>
+          <t>051-2-K/26</t>
         </is>
       </c>
       <c r="G118" s="49" t="inlineStr">
         <is>
-          <t>21.01.2026</t>
+          <t>04.03.2026</t>
         </is>
       </c>
       <c r="H118" s="49" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="I118" s="49" t="inlineStr">
@@ -39108,80 +39176,50 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="47" t="n">
-        <v>77</v>
-      </c>
-      <c r="B119" s="48" t="inlineStr">
-        <is>
-          <t>SJ102501</t>
-        </is>
-      </c>
-      <c r="C119" s="49" t="n"/>
-      <c r="D119" s="49" t="inlineStr">
-        <is>
-          <t>11.20 %w/w (U ±0.69)</t>
-        </is>
-      </c>
-      <c r="E119" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F119" s="49" t="inlineStr">
-        <is>
-          <t>051-3-K/26</t>
-        </is>
-      </c>
-      <c r="G119" s="49" t="inlineStr">
-        <is>
-          <t>04.03.2026</t>
-        </is>
-      </c>
-      <c r="H119" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I119" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
+    <row r="119" ht="19.5" customHeight="1">
+      <c r="A119" s="46" t="inlineStr">
+        <is>
+          <t>Wedding Crasher      2 batch(es)      Total Δ⁹-THC across batches: 21.67 – 22.11 %</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="47" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B120" s="48" t="inlineStr">
         <is>
-          <t>SJ112501</t>
-        </is>
-      </c>
-      <c r="C120" s="49" t="n"/>
+          <t>WC072501</t>
+        </is>
+      </c>
+      <c r="C120" s="49" t="inlineStr">
+        <is>
+          <t>P050262</t>
+        </is>
+      </c>
       <c r="D120" s="49" t="inlineStr">
         <is>
-          <t>9.20 %w/w (U ±0.57)</t>
+          <t>22.11%</t>
         </is>
       </c>
       <c r="E120" s="49" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>n/a (informational)</t>
         </is>
       </c>
       <c r="F120" s="49" t="inlineStr">
         <is>
-          <t>051-2-K/26</t>
+          <t>ППК25369</t>
         </is>
       </c>
       <c r="G120" s="49" t="inlineStr">
         <is>
-          <t>04.03.2026</t>
+          <t>28.11.2025</t>
         </is>
       </c>
       <c r="H120" s="49" t="inlineStr">
         <is>
-          <t>Farmahem</t>
+          <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
       <c r="I120" s="49" t="inlineStr">
@@ -39190,180 +39228,126 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="19.5" customHeight="1">
-      <c r="A121" s="46" t="inlineStr">
-        <is>
-          <t>Wedding Crasher      2 batch(es)      Total Δ⁹-THC across batches: 21.67 – 22.11 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="47" t="n">
-        <v>79</v>
-      </c>
-      <c r="B122" s="48" t="inlineStr">
-        <is>
-          <t>WC072501</t>
-        </is>
-      </c>
-      <c r="C122" s="49" t="inlineStr">
-        <is>
-          <t>P050262</t>
-        </is>
-      </c>
-      <c r="D122" s="49" t="inlineStr">
-        <is>
-          <t>22.11%</t>
-        </is>
-      </c>
-      <c r="E122" s="49" t="inlineStr">
-        <is>
-          <t>n/a (informational)</t>
-        </is>
-      </c>
-      <c r="F122" s="49" t="inlineStr">
-        <is>
-          <t>ППК25369</t>
-        </is>
-      </c>
-      <c r="G122" s="49" t="inlineStr">
-        <is>
-          <t>28.11.2025</t>
-        </is>
-      </c>
-      <c r="H122" s="49" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="47" t="n">
+        <v>80</v>
+      </c>
+      <c r="B121" s="48" t="inlineStr">
+        <is>
+          <t>WC082501</t>
+        </is>
+      </c>
+      <c r="C121" s="49" t="inlineStr">
+        <is>
+          <t>P060012</t>
+        </is>
+      </c>
+      <c r="D121" s="49" t="inlineStr">
+        <is>
+          <t>21.67%</t>
+        </is>
+      </c>
+      <c r="E121" s="49" t="inlineStr">
+        <is>
+          <t>19.5 – 23.83 %</t>
+        </is>
+      </c>
+      <c r="F121" s="49" t="inlineStr">
+        <is>
+          <t>ППК26001</t>
+        </is>
+      </c>
+      <c r="G121" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H121" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I122" s="49" t="inlineStr">
+      <c r="I121" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="B123" s="48" t="inlineStr">
-        <is>
-          <t>WC082501</t>
-        </is>
-      </c>
-      <c r="C123" s="49" t="inlineStr">
-        <is>
-          <t>P060012</t>
-        </is>
-      </c>
-      <c r="D123" s="49" t="inlineStr">
-        <is>
-          <t>21.67%</t>
-        </is>
-      </c>
-      <c r="E123" s="49" t="inlineStr">
-        <is>
-          <t>19.5 – 23.83 %</t>
-        </is>
-      </c>
-      <c r="F123" s="49" t="inlineStr">
-        <is>
-          <t>ППК26001</t>
-        </is>
-      </c>
-      <c r="G123" s="49" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H123" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I123" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="75">
+  <mergeCells count="73">
     <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A84:I84"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A108:I108"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A66:I66"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A69:A70"/>
     <mergeCell ref="B86:B87"/>
+    <mergeCell ref="A89:I89"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="A113:I113"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C104:C105"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A33:I33"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="A76:I76"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C41:C42"/>
     <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="A106:I106"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="A91:I91"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A96:I96"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="C110:C111"/>
-    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="B84:B85"/>
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A19:I19"/>
     <mergeCell ref="A68:I68"/>
+    <mergeCell ref="C51:C52"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A117:I117"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="A93:I93"/>
-    <mergeCell ref="A121:I121"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A111:I111"/>
+    <mergeCell ref="A115:I115"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B76:B77"/>
     <mergeCell ref="A15:I15"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="A51:I51"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A82:I82"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B104:B105"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="A70:I70"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A94:I94"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="A119:I119"/>
+    <mergeCell ref="B72:B73"/>
     <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="A30:A31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/qc-corrections/PP_Batch_Release_QC_Register_CORRECTED.xlsx
+++ b/qc-corrections/PP_Batch_Release_QC_Register_CORRECTED.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch Release QC" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="THC by Strain" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stability Testing Programme" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Batch Release QC'!$A$4:$Z$289</definedName>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -119,8 +120,13 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF5A6E75"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -167,6 +173,16 @@
         <fgColor rgb="FFF4F6F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAEDD4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -190,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -319,6 +335,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -685,7 +713,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Z297"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -35028,7 +35056,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I121"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8.300000000000001" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -39351,4 +39379,897 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="46" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="43" t="inlineStr">
+        <is>
+          <t>Purely Plant GmbH — Stability testing programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>ICH long-term (25 °C / 60 % RH) and accelerated (40 °C / 75 % RH) timepoint analyses, grouped by batch. These are stability-study results only — they are NOT batch-release results and must not be used as release or CoA-register values. Initial (t=0) release values are in the 'Batch Release QC' sheet. Values transcribed verbatim from the UKIM certificates held in RAGflow dataset STABILITY_PROGRAMME.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="45" t="inlineStr">
+        <is>
+          <t>Seq</t>
+        </is>
+      </c>
+      <c r="B4" s="45" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="C4" s="45" t="inlineStr">
+        <is>
+          <t>Variety</t>
+        </is>
+      </c>
+      <c r="D4" s="45" t="inlineStr">
+        <is>
+          <t>Timepoint</t>
+        </is>
+      </c>
+      <c r="E4" s="45" t="inlineStr">
+        <is>
+          <t>Storage condition</t>
+        </is>
+      </c>
+      <c r="F4" s="45" t="inlineStr">
+        <is>
+          <t>Report No.</t>
+        </is>
+      </c>
+      <c r="G4" s="45" t="inlineStr">
+        <is>
+          <t>Date of issue</t>
+        </is>
+      </c>
+      <c r="H4" s="45" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
+      <c r="I4" s="45" t="inlineStr">
+        <is>
+          <t>Loss on drying</t>
+        </is>
+      </c>
+      <c r="J4" s="45" t="inlineStr">
+        <is>
+          <t>CBDA</t>
+        </is>
+      </c>
+      <c r="K4" s="45" t="inlineStr">
+        <is>
+          <t>CBD</t>
+        </is>
+      </c>
+      <c r="L4" s="45" t="inlineStr">
+        <is>
+          <t>CBN</t>
+        </is>
+      </c>
+      <c r="M4" s="45" t="inlineStr">
+        <is>
+          <t>Δ⁹-THC</t>
+        </is>
+      </c>
+      <c r="N4" s="45" t="inlineStr">
+        <is>
+          <t>Δ⁹-THCA</t>
+        </is>
+      </c>
+      <c r="O4" s="45" t="inlineStr">
+        <is>
+          <t>Total CBD</t>
+        </is>
+      </c>
+      <c r="P4" s="45" t="inlineStr">
+        <is>
+          <t>Total Δ⁹-THC</t>
+        </is>
+      </c>
+      <c r="Q4" s="45" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="54" t="n"/>
+      <c r="B5" s="54" t="n"/>
+      <c r="C5" s="54" t="n"/>
+      <c r="D5" s="54" t="n"/>
+      <c r="E5" s="54" t="n"/>
+      <c r="F5" s="54" t="n"/>
+      <c r="G5" s="54" t="n"/>
+      <c r="H5" s="54" t="inlineStr">
+        <is>
+          <t>Specification</t>
+        </is>
+      </c>
+      <c r="I5" s="54" t="inlineStr">
+        <is>
+          <t>≤ 10.00 %</t>
+        </is>
+      </c>
+      <c r="J5" s="54" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="K5" s="54" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="L5" s="54" t="inlineStr">
+        <is>
+          <t>≤ 1.00 %</t>
+        </is>
+      </c>
+      <c r="M5" s="54" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="N5" s="54" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="O5" s="54" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="P5" s="54" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="Q5" s="54" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="46" t="inlineStr">
+        <is>
+          <t>P050022      Grape Pie      3 analyses      timepoints: 6 mo, 9 mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="49" t="inlineStr">
+        <is>
+          <t>P050022</t>
+        </is>
+      </c>
+      <c r="C7" s="49" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D7" s="49" t="inlineStr">
+        <is>
+          <t>6 months</t>
+        </is>
+      </c>
+      <c r="E7" s="49" t="inlineStr">
+        <is>
+          <t>25°C / 60% RH</t>
+        </is>
+      </c>
+      <c r="F7" s="49" t="inlineStr">
+        <is>
+          <t>ППК26032</t>
+        </is>
+      </c>
+      <c r="G7" s="49" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="H7" s="49" t="inlineStr">
+        <is>
+          <t>Универзитет „Св. Кирил и Методиј“, Скопје, Фармацевтски факултет, Центар за природни производи</t>
+        </is>
+      </c>
+      <c r="I7" s="55" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="J7" s="55" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K7" s="49" t="inlineStr">
+        <is>
+          <t>BLQ</t>
+        </is>
+      </c>
+      <c r="L7" s="55" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M7" s="55" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="N7" s="55" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="O7" s="55" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P7" s="55" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="Q7" s="49" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="49" t="inlineStr">
+        <is>
+          <t>P050022</t>
+        </is>
+      </c>
+      <c r="C8" s="49" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D8" s="49" t="inlineStr">
+        <is>
+          <t>6 months</t>
+        </is>
+      </c>
+      <c r="E8" s="49" t="inlineStr">
+        <is>
+          <t>40°C / 75% RH</t>
+        </is>
+      </c>
+      <c r="F8" s="49" t="inlineStr">
+        <is>
+          <t>ППК26033</t>
+        </is>
+      </c>
+      <c r="G8" s="49" t="inlineStr">
+        <is>
+          <t>25.03.2026</t>
+        </is>
+      </c>
+      <c r="H8" s="49" t="inlineStr">
+        <is>
+          <t>Ss. Cyril and Methodius University, Skopje, Faculty of Pharmacy, Center for natural products</t>
+        </is>
+      </c>
+      <c r="I8" s="55" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="J8" s="55" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K8" s="55" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L8" s="56" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M8" s="55" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="N8" s="55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O8" s="55" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P8" s="55" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="Q8" s="57" t="inlineStr">
+        <is>
+          <t>CBN 2.35 % exceeds the ≤ 1.00 % limit stated on the certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="49" t="inlineStr">
+        <is>
+          <t>P050022</t>
+        </is>
+      </c>
+      <c r="C9" s="49" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D9" s="49" t="inlineStr">
+        <is>
+          <t>9 months</t>
+        </is>
+      </c>
+      <c r="E9" s="49" t="inlineStr">
+        <is>
+          <t>25°C / 60% RH</t>
+        </is>
+      </c>
+      <c r="F9" s="49" t="inlineStr">
+        <is>
+          <t>ППК26059</t>
+        </is>
+      </c>
+      <c r="G9" s="49" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H9" s="49" t="inlineStr">
+        <is>
+          <t>Универзитет „Св. Кирил и Методиј“, Скопје, Фармацевтски факултет, Центар за природни производи</t>
+        </is>
+      </c>
+      <c r="I9" s="55" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="J9" s="55" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K9" s="55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L9" s="55" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M9" s="55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N9" s="55" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="O9" s="55" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P9" s="55" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="Q9" s="49" t="inlineStr"/>
+    </row>
+    <row r="10" ht="19.5" customHeight="1">
+      <c r="A10" s="46" t="inlineStr">
+        <is>
+          <t>P050072      Grape Pie      3 analyses      timepoints: 6 mo, 9 mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="49" t="inlineStr">
+        <is>
+          <t>P050072</t>
+        </is>
+      </c>
+      <c r="C11" s="49" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D11" s="49" t="inlineStr">
+        <is>
+          <t>6 months</t>
+        </is>
+      </c>
+      <c r="E11" s="49" t="inlineStr">
+        <is>
+          <t>25°C / 60% RH</t>
+        </is>
+      </c>
+      <c r="F11" s="49" t="inlineStr">
+        <is>
+          <t>ППК26034</t>
+        </is>
+      </c>
+      <c r="G11" s="49" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="H11" s="49" t="inlineStr">
+        <is>
+          <t>Ss. Cyril and Methodius University, Skopje, Faculty of Pharmacy, Center for natural products</t>
+        </is>
+      </c>
+      <c r="I11" s="55" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="J11" s="55" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K11" s="49" t="inlineStr">
+        <is>
+          <t>BLQ</t>
+        </is>
+      </c>
+      <c r="L11" s="55" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M11" s="55" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="N11" s="55" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="O11" s="55" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P11" s="55" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="Q11" s="49" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="49" t="inlineStr">
+        <is>
+          <t>P050072</t>
+        </is>
+      </c>
+      <c r="C12" s="49" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D12" s="49" t="inlineStr">
+        <is>
+          <t>6 months</t>
+        </is>
+      </c>
+      <c r="E12" s="49" t="inlineStr">
+        <is>
+          <t>40°C / 75% RH</t>
+        </is>
+      </c>
+      <c r="F12" s="49" t="inlineStr">
+        <is>
+          <t>ППК26035</t>
+        </is>
+      </c>
+      <c r="G12" s="49" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="H12" s="49" t="inlineStr">
+        <is>
+          <t>Универзитет „Св. Кирил и Методиј“, Скопје, Фармацевтски факултет, Центар за природни производи</t>
+        </is>
+      </c>
+      <c r="I12" s="55" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="J12" s="55" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K12" s="49" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="L12" s="56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M12" s="55" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="N12" s="49" t="inlineStr">
+        <is>
+          <t>BLQ</t>
+        </is>
+      </c>
+      <c r="O12" s="55" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P12" s="55" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="Q12" s="57" t="inlineStr">
+        <is>
+          <t>CBN 2.15 % exceeds the ≤ 1.00 % limit stated on the certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="49" t="inlineStr">
+        <is>
+          <t>P050072</t>
+        </is>
+      </c>
+      <c r="C13" s="49" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D13" s="49" t="inlineStr">
+        <is>
+          <t>9 months</t>
+        </is>
+      </c>
+      <c r="E13" s="49" t="inlineStr">
+        <is>
+          <t>25°C / 60% RH</t>
+        </is>
+      </c>
+      <c r="F13" s="49" t="inlineStr">
+        <is>
+          <t>ППК26060</t>
+        </is>
+      </c>
+      <c r="G13" s="49" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H13" s="49" t="inlineStr">
+        <is>
+          <t>Ss. Cyril and Methodius University, Skopje, Faculty of Pharmacy, Center for natural products</t>
+        </is>
+      </c>
+      <c r="I13" s="55" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="J13" s="55" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K13" s="55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L13" s="55" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M13" s="55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N13" s="55" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="O13" s="55" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P13" s="55" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="Q13" s="49" t="inlineStr"/>
+    </row>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="46" t="inlineStr">
+        <is>
+          <t>P050202      Grape Pie      4 analyses      timepoints: 3 mo, 6 mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" s="49" t="inlineStr">
+        <is>
+          <t>P050202</t>
+        </is>
+      </c>
+      <c r="C15" s="49" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D15" s="49" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="E15" s="49" t="inlineStr">
+        <is>
+          <t>25°C / 60% RH</t>
+        </is>
+      </c>
+      <c r="F15" s="49" t="inlineStr">
+        <is>
+          <t>ППК26036</t>
+        </is>
+      </c>
+      <c r="G15" s="49" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="H15" s="49" t="inlineStr">
+        <is>
+          <t>Универзитет ,,Св. Кирил и Методиј“, Скопје, Фармацевтски факултет, Центар за природни производи</t>
+        </is>
+      </c>
+      <c r="I15" s="55" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="J15" s="55" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K15" s="49" t="inlineStr">
+        <is>
+          <t>BLQ</t>
+        </is>
+      </c>
+      <c r="L15" s="55" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M15" s="55" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="N15" s="55" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="O15" s="55" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P15" s="55" t="n">
+        <v>22.83</v>
+      </c>
+      <c r="Q15" s="49" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" s="49" t="inlineStr">
+        <is>
+          <t>P050202</t>
+        </is>
+      </c>
+      <c r="C16" s="49" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D16" s="49" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="E16" s="49" t="inlineStr">
+        <is>
+          <t>40°C / 75% RH</t>
+        </is>
+      </c>
+      <c r="F16" s="49" t="inlineStr">
+        <is>
+          <t>ППК26037</t>
+        </is>
+      </c>
+      <c r="G16" s="49" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="H16" s="49" t="inlineStr">
+        <is>
+          <t>Универзитет „Св. Кирил и Методиј“, Скопје, Фармацевтски факултет, Центар за природни производи</t>
+        </is>
+      </c>
+      <c r="I16" s="55" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="J16" s="55" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K16" s="55" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L16" s="55" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M16" s="55" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="N16" s="55" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="O16" s="55" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P16" s="55" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="Q16" s="49" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" s="49" t="inlineStr">
+        <is>
+          <t>P050202</t>
+        </is>
+      </c>
+      <c r="C17" s="49" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D17" s="49" t="inlineStr">
+        <is>
+          <t>6 months</t>
+        </is>
+      </c>
+      <c r="E17" s="49" t="inlineStr">
+        <is>
+          <t>25°C / 60% RH</t>
+        </is>
+      </c>
+      <c r="F17" s="49" t="inlineStr">
+        <is>
+          <t>ППК26057</t>
+        </is>
+      </c>
+      <c r="G17" s="49" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H17" s="49" t="inlineStr">
+        <is>
+          <t>Sts. Cyril and Methodius University, Skopje, Faculty of Pharmacy, Center for natural products</t>
+        </is>
+      </c>
+      <c r="I17" s="55" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="J17" s="55" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K17" s="55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L17" s="55" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M17" s="55" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="N17" s="55" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="O17" s="55" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P17" s="55" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="Q17" s="49" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="49" t="inlineStr">
+        <is>
+          <t>P050202</t>
+        </is>
+      </c>
+      <c r="C18" s="49" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D18" s="49" t="inlineStr">
+        <is>
+          <t>6 months</t>
+        </is>
+      </c>
+      <c r="E18" s="49" t="inlineStr">
+        <is>
+          <t>40°C / 75% RH</t>
+        </is>
+      </c>
+      <c r="F18" s="49" t="inlineStr">
+        <is>
+          <t>ППК26058</t>
+        </is>
+      </c>
+      <c r="G18" s="49" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H18" s="49" t="inlineStr">
+        <is>
+          <t>Универзитет „Св. Кирил и Методиј“, Скопје, Фармацевтски факултет, Центар за природни производи</t>
+        </is>
+      </c>
+      <c r="I18" s="55" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J18" s="55" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K18" s="55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L18" s="56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M18" s="55" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N18" s="55" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="O18" s="55" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P18" s="55" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Q18" s="57" t="inlineStr">
+        <is>
+          <t>CBN 2.05 % exceeds the ≤ 1.00 % limit stated on the certificate</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A14:Q14"/>
+    <mergeCell ref="A6:Q6"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A10:Q10"/>
+    <mergeCell ref="A1:Q1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/qc-corrections/PP_Batch_Release_QC_Register_CORRECTED.xlsx
+++ b/qc-corrections/PP_Batch_Release_QC_Register_CORRECTED.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,6 +122,10 @@
     </font>
     <font>
       <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
       <color rgb="FF5A6E75"/>
       <sz val="9"/>
     </font>
@@ -175,12 +179,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFFAEDD4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAEDD4"/>
+        <fgColor rgb="FFEEF3F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -206,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -336,15 +340,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="17" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="17" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="17" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -35055,14 +35065,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:I131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8.300000000000001" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
@@ -35076,10 +35086,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
+    <row r="2" ht="40" customHeight="1">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Every production batch grouped by strain, with every Total Δ⁹-THC result on file, referenced to its certificate. BLQ / &lt;LOQ values are shown but excluded from the numeric range. Strain names canonicalised; CoA codes resolved against source certificates.</t>
+          <t>Every production batch grouped by strain, with every Total Δ⁹-THC result on file, referenced to its certificate. BLQ / &lt;LOQ values are shown but excluded from the numeric range. Stability-study results are included for completeness, shaded and marked 'STABILITY', and are excluded from the release range — a stability value is never a release value.</t>
         </is>
       </c>
     </row>
@@ -35133,7 +35143,7 @@
     <row r="5" ht="19.5" customHeight="1">
       <c r="A5" s="46" t="inlineStr">
         <is>
-          <t>Apple and Banana      1 batch(es)      Total Δ⁹-THC across batches: 16.93 %</t>
+          <t>Apple and Banana      1 batch(es)      Total Δ⁹-THC across batches (release): 16.93 %</t>
         </is>
       </c>
     </row>
@@ -35185,7 +35195,7 @@
     <row r="7" ht="19.5" customHeight="1">
       <c r="A7" s="46" t="inlineStr">
         <is>
-          <t>Blue Gelato      1 batch(es)      Total Δ⁹-THC across batches: 21.80 – 26.14 %</t>
+          <t>Blue Gelato      1 batch(es)      Total Δ⁹-THC across batches (release): 21.80 – 26.14 %</t>
         </is>
       </c>
     </row>
@@ -35268,7 +35278,7 @@
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="46" t="inlineStr">
         <is>
-          <t>Blue Sunset Sherbet      3 batch(es)      Total Δ⁹-THC across batches: 20.39 – 25.01 %</t>
+          <t>Blue Sunset Sherbet      3 batch(es)      Total Δ⁹-THC across batches (release): 20.39 – 25.01 %</t>
         </is>
       </c>
     </row>
@@ -35441,7 +35451,7 @@
     <row r="15" ht="19.5" customHeight="1">
       <c r="A15" s="46" t="inlineStr">
         <is>
-          <t>Cash Cow      2 batch(es)      Total Δ⁹-THC across batches: 13.35 – 17.67 %</t>
+          <t>Cash Cow      2 batch(es)      Total Δ⁹-THC across batches (release): 13.35 – 17.67 %</t>
         </is>
       </c>
     </row>
@@ -35530,7 +35540,7 @@
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="46" t="inlineStr">
         <is>
-          <t>Clemosa a bud      1 batch(es)      Total Δ⁹-THC across batches: 8.02 %</t>
+          <t>Clemosa a bud      1 batch(es)      Total Δ⁹-THC across batches (release): 8.02 %</t>
         </is>
       </c>
     </row>
@@ -35582,7 +35592,7 @@
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" s="46" t="inlineStr">
         <is>
-          <t>Cup Junky      9 batch(es)      Total Δ⁹-THC across batches: 14.93 – 24.96 %</t>
+          <t>Cup Junky      9 batch(es)      Total Δ⁹-THC across batches (release): 14.93 – 24.96 %</t>
         </is>
       </c>
     </row>
@@ -36095,7 +36105,7 @@
     <row r="33" ht="19.5" customHeight="1">
       <c r="A33" s="46" t="inlineStr">
         <is>
-          <t>Fat Bastard      6 batch(es)      Total Δ⁹-THC across batches: 12.39 – 20.83 %</t>
+          <t>Fat Bastard      6 batch(es)      Total Δ⁹-THC across batches (release): 12.39 – 20.83 %</t>
         </is>
       </c>
     </row>
@@ -36344,7 +36354,7 @@
     <row r="40" ht="19.5" customHeight="1">
       <c r="A40" s="46" t="inlineStr">
         <is>
-          <t>Gorilla Glue      7 batch(es)      Total Δ⁹-THC across batches: 15.35 – 18.98 %</t>
+          <t>Gorilla Glue      7 batch(es)      Total Δ⁹-THC across batches (release): 15.35 – 18.98 %</t>
         </is>
       </c>
     </row>
@@ -36677,7 +36687,7 @@
     <row r="49" ht="19.5" customHeight="1">
       <c r="A49" s="46" t="inlineStr">
         <is>
-          <t>Grape Pie      13 batch(es)      Total Δ⁹-THC across batches: 14.83 – 26.32 %</t>
+          <t>Grape Pie      13 batch(es)      Total Δ⁹-THC across batches (release): 14.83 – 26.32 %</t>
         </is>
       </c>
     </row>
@@ -36772,125 +36782,96 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="53" t="n"/>
-      <c r="B52" s="53" t="n"/>
-      <c r="C52" s="53" t="n"/>
-      <c r="D52" s="49" t="inlineStr">
+      <c r="D52" s="52" t="inlineStr">
         <is>
           <t>22.61 %w/w (U 1.39)</t>
         </is>
       </c>
-      <c r="E52" s="49" t="inlineStr">
+      <c r="E52" s="52" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F52" s="49" t="inlineStr">
+      <c r="F52" s="52" t="inlineStr">
         <is>
           <t>197-11-К/26</t>
         </is>
       </c>
-      <c r="G52" s="49" t="inlineStr">
+      <c r="G52" s="52" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H52" s="49" t="inlineStr">
+      <c r="H52" s="52" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I52" s="49" t="inlineStr">
+      <c r="I52" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="47" t="n">
-        <v>33</v>
-      </c>
-      <c r="B53" s="48" t="inlineStr">
-        <is>
-          <t>GP0824_03</t>
-        </is>
-      </c>
-      <c r="C53" s="49" t="inlineStr">
-        <is>
-          <t>P050072</t>
-        </is>
-      </c>
-      <c r="D53" s="49" t="inlineStr">
-        <is>
-          <t>25.45%</t>
-        </is>
-      </c>
-      <c r="E53" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F53" s="49" t="inlineStr">
-        <is>
-          <t>ППК25175</t>
-        </is>
-      </c>
-      <c r="G53" s="49" t="inlineStr">
-        <is>
-          <t>10.07.2025</t>
-        </is>
-      </c>
-      <c r="H53" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I53" s="49" t="inlineStr">
+      <c r="D53" s="54" t="inlineStr">
+        <is>
+          <t>21.31% (stability 6 mo, 25°C / 60% RH)</t>
+        </is>
+      </c>
+      <c r="E53" s="54" t="inlineStr">
+        <is>
+          <t>STABILITY — not a release value</t>
+        </is>
+      </c>
+      <c r="F53" s="54" t="inlineStr">
+        <is>
+          <t>ППК26032</t>
+        </is>
+      </c>
+      <c r="G53" s="54" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="H53" s="54" t="inlineStr">
+        <is>
+          <t>Универзитет „Св. Кирил и Методиј“, Скопје, Фармацевтски факултет, Центар за природни производи</t>
+        </is>
+      </c>
+      <c r="I53" s="54" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="50" t="n">
-        <v>34</v>
-      </c>
-      <c r="B54" s="51" t="inlineStr">
-        <is>
-          <t>GP052501</t>
-        </is>
-      </c>
-      <c r="C54" s="52" t="inlineStr">
-        <is>
-          <t>P050152</t>
-        </is>
-      </c>
-      <c r="D54" s="52" t="inlineStr">
-        <is>
-          <t>18.98%</t>
-        </is>
-      </c>
-      <c r="E54" s="52" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F54" s="52" t="inlineStr">
-        <is>
-          <t>ППК25279</t>
-        </is>
-      </c>
-      <c r="G54" s="52" t="inlineStr">
-        <is>
-          <t>19.09.2025</t>
-        </is>
-      </c>
-      <c r="H54" s="52" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I54" s="52" t="inlineStr">
+      <c r="D54" s="54" t="inlineStr">
+        <is>
+          <t>13.16% (stability 6 mo, 40°C / 75% RH)</t>
+        </is>
+      </c>
+      <c r="E54" s="54" t="inlineStr">
+        <is>
+          <t>STABILITY — not a release value</t>
+        </is>
+      </c>
+      <c r="F54" s="54" t="inlineStr">
+        <is>
+          <t>ППК26033</t>
+        </is>
+      </c>
+      <c r="G54" s="54" t="inlineStr">
+        <is>
+          <t>25.03.2026</t>
+        </is>
+      </c>
+      <c r="H54" s="54" t="inlineStr">
+        <is>
+          <t>Ss. Cyril and Methodius University, Skopje, Faculty of Pharmacy, Center for natural products</t>
+        </is>
+      </c>
+      <c r="I54" s="54" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -36900,212 +36881,176 @@
       <c r="A55" s="53" t="n"/>
       <c r="B55" s="53" t="n"/>
       <c r="C55" s="53" t="n"/>
-      <c r="D55" s="49" t="inlineStr">
-        <is>
-          <t>18.52 %w/w (U 1.14)</t>
-        </is>
-      </c>
-      <c r="E55" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F55" s="49" t="inlineStr">
-        <is>
-          <t>197-10-К/26</t>
-        </is>
-      </c>
-      <c r="G55" s="49" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H55" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I55" s="49" t="inlineStr">
+      <c r="D55" s="55" t="inlineStr">
+        <is>
+          <t>23.08% (stability 9 mo, 25°C / 60% RH)</t>
+        </is>
+      </c>
+      <c r="E55" s="55" t="inlineStr">
+        <is>
+          <t>STABILITY — not a release value</t>
+        </is>
+      </c>
+      <c r="F55" s="55" t="inlineStr">
+        <is>
+          <t>ППК26059</t>
+        </is>
+      </c>
+      <c r="G55" s="55" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H55" s="55" t="inlineStr">
+        <is>
+          <t>Универзитет „Св. Кирил и Методиј“, Скопје, Фармацевтски факултет, Центар за природни производи</t>
+        </is>
+      </c>
+      <c r="I55" s="55" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="47" t="n">
-        <v>35</v>
-      </c>
-      <c r="B56" s="48" t="inlineStr">
-        <is>
-          <t>GP062501</t>
-        </is>
-      </c>
-      <c r="C56" s="49" t="inlineStr">
-        <is>
-          <t>P050202</t>
-        </is>
-      </c>
-      <c r="D56" s="49" t="inlineStr">
-        <is>
-          <t>24.89%</t>
-        </is>
-      </c>
-      <c r="E56" s="49" t="inlineStr">
-        <is>
-          <t>19.8 – 24.2 %</t>
-        </is>
-      </c>
-      <c r="F56" s="49" t="inlineStr">
-        <is>
-          <t>In-house HPLC cross-check NPCCC/SCP-02, NGP/QCG/SOP-024</t>
-        </is>
-      </c>
-      <c r="G56" s="49" t="inlineStr">
-        <is>
-          <t>28.11.2025</t>
-        </is>
-      </c>
-      <c r="H56" s="49" t="inlineStr">
-        <is>
-          <t>Purely Plant (in-house)</t>
-        </is>
-      </c>
-      <c r="I56" s="49" t="inlineStr">
+      <c r="A56" s="50" t="n">
+        <v>33</v>
+      </c>
+      <c r="B56" s="51" t="inlineStr">
+        <is>
+          <t>GP0824_03</t>
+        </is>
+      </c>
+      <c r="C56" s="52" t="inlineStr">
+        <is>
+          <t>P050072</t>
+        </is>
+      </c>
+      <c r="D56" s="52" t="inlineStr">
+        <is>
+          <t>25.45%</t>
+        </is>
+      </c>
+      <c r="E56" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F56" s="52" t="inlineStr">
+        <is>
+          <t>ППК25175</t>
+        </is>
+      </c>
+      <c r="G56" s="52" t="inlineStr">
+        <is>
+          <t>10.07.2025</t>
+        </is>
+      </c>
+      <c r="H56" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I56" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="B57" s="48" t="inlineStr">
-        <is>
-          <t>GP072501-1</t>
-        </is>
-      </c>
-      <c r="C57" s="49" t="inlineStr">
-        <is>
-          <t>P050292</t>
-        </is>
-      </c>
-      <c r="D57" s="49" t="inlineStr">
-        <is>
-          <t>21.36%</t>
-        </is>
-      </c>
-      <c r="E57" s="49" t="inlineStr">
-        <is>
-          <t>19.2 – 23.4 %</t>
-        </is>
-      </c>
-      <c r="F57" s="49" t="inlineStr">
-        <is>
-          <t>PP CoA #018 / ППК25378</t>
-        </is>
-      </c>
-      <c r="G57" s="49" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H57" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I57" s="49" t="inlineStr">
+      <c r="D57" s="54" t="inlineStr">
+        <is>
+          <t>24.62% (stability 6 mo, 25°C / 60% RH)</t>
+        </is>
+      </c>
+      <c r="E57" s="54" t="inlineStr">
+        <is>
+          <t>STABILITY — not a release value</t>
+        </is>
+      </c>
+      <c r="F57" s="54" t="inlineStr">
+        <is>
+          <t>ППК26034</t>
+        </is>
+      </c>
+      <c r="G57" s="54" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="H57" s="54" t="inlineStr">
+        <is>
+          <t>Ss. Cyril and Methodius University, Skopje, Faculty of Pharmacy, Center for natural products</t>
+        </is>
+      </c>
+      <c r="I57" s="54" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="47" t="n">
-        <v>37</v>
-      </c>
-      <c r="B58" s="48" t="inlineStr">
-        <is>
-          <t>GP072501-2</t>
-        </is>
-      </c>
-      <c r="C58" s="49" t="inlineStr">
-        <is>
-          <t>P050302</t>
-        </is>
-      </c>
-      <c r="D58" s="49" t="inlineStr">
-        <is>
-          <t>19.81%</t>
-        </is>
-      </c>
-      <c r="E58" s="49" t="inlineStr">
-        <is>
-          <t>17.8 – 21.7 %</t>
-        </is>
-      </c>
-      <c r="F58" s="49" t="inlineStr">
-        <is>
-          <t>PP CoA #019 / ППК25379</t>
-        </is>
-      </c>
-      <c r="G58" s="49" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H58" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I58" s="49" t="inlineStr">
+      <c r="D58" s="54" t="inlineStr">
+        <is>
+          <t>14.99% (stability 6 mo, 40°C / 75% RH)</t>
+        </is>
+      </c>
+      <c r="E58" s="54" t="inlineStr">
+        <is>
+          <t>STABILITY — not a release value</t>
+        </is>
+      </c>
+      <c r="F58" s="54" t="inlineStr">
+        <is>
+          <t>ППК26035</t>
+        </is>
+      </c>
+      <c r="G58" s="54" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="H58" s="54" t="inlineStr">
+        <is>
+          <t>Универзитет „Св. Кирил и Методиј“, Скопје, Фармацевтски факултет, Центар за природни производи</t>
+        </is>
+      </c>
+      <c r="I58" s="54" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="47" t="n">
-        <v>38</v>
-      </c>
-      <c r="B59" s="48" t="inlineStr">
-        <is>
-          <t>GP082501-1</t>
-        </is>
-      </c>
-      <c r="C59" s="49" t="inlineStr">
-        <is>
-          <t>P050312</t>
-        </is>
-      </c>
-      <c r="D59" s="49" t="inlineStr">
-        <is>
-          <t>21.29%</t>
-        </is>
-      </c>
-      <c r="E59" s="49" t="inlineStr">
-        <is>
-          <t>19.1 – 23.4 %</t>
-        </is>
-      </c>
-      <c r="F59" s="49" t="inlineStr">
-        <is>
-          <t>PP CoA #020 / ППК25380</t>
-        </is>
-      </c>
-      <c r="G59" s="49" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H59" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I59" s="49" t="inlineStr">
+      <c r="A59" s="53" t="n"/>
+      <c r="B59" s="53" t="n"/>
+      <c r="C59" s="53" t="n"/>
+      <c r="D59" s="55" t="inlineStr">
+        <is>
+          <t>25.98% (stability 9 mo, 25°C / 60% RH)</t>
+        </is>
+      </c>
+      <c r="E59" s="55" t="inlineStr">
+        <is>
+          <t>STABILITY — not a release value</t>
+        </is>
+      </c>
+      <c r="F59" s="55" t="inlineStr">
+        <is>
+          <t>ППК26060</t>
+        </is>
+      </c>
+      <c r="G59" s="55" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H59" s="55" t="inlineStr">
+        <is>
+          <t>Ss. Cyril and Methodius University, Skopje, Faculty of Pharmacy, Center for natural products</t>
+        </is>
+      </c>
+      <c r="I59" s="55" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -37113,36 +37058,36 @@
     </row>
     <row r="60">
       <c r="A60" s="50" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B60" s="51" t="inlineStr">
         <is>
-          <t>GP082501-2</t>
+          <t>GP052501</t>
         </is>
       </c>
       <c r="C60" s="52" t="inlineStr">
         <is>
-          <t>P050322</t>
+          <t>P050152</t>
         </is>
       </c>
       <c r="D60" s="52" t="inlineStr">
         <is>
-          <t>14.83%</t>
+          <t>18.98%</t>
         </is>
       </c>
       <c r="E60" s="52" t="inlineStr">
         <is>
-          <t>13.3 – 16.3 %</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F60" s="52" t="inlineStr">
         <is>
-          <t>PP CoA #021 / ППК25381</t>
+          <t>ППК25279</t>
         </is>
       </c>
       <c r="G60" s="52" t="inlineStr">
         <is>
-          <t>21.01.2026</t>
+          <t>19.09.2025</t>
         </is>
       </c>
       <c r="H60" s="52" t="inlineStr">
@@ -37162,7 +37107,7 @@
       <c r="C61" s="53" t="n"/>
       <c r="D61" s="49" t="inlineStr">
         <is>
-          <t>15.70% w/w (U 0.96% w/w)</t>
+          <t>18.52 %w/w (U 1.14)</t>
         </is>
       </c>
       <c r="E61" s="49" t="inlineStr">
@@ -37172,7 +37117,7 @@
       </c>
       <c r="F61" s="49" t="inlineStr">
         <is>
-          <t>197-12-К/26</t>
+          <t>197-10-К/26</t>
         </is>
       </c>
       <c r="G61" s="49" t="inlineStr">
@@ -37192,472 +37137,563 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="47" t="n">
-        <v>40</v>
-      </c>
-      <c r="B62" s="48" t="inlineStr">
-        <is>
-          <t>GP092501</t>
-        </is>
-      </c>
-      <c r="C62" s="49" t="inlineStr">
-        <is>
-          <t>P060092</t>
-        </is>
-      </c>
-      <c r="D62" s="49" t="inlineStr">
-        <is>
-          <t>25.73%</t>
-        </is>
-      </c>
-      <c r="E62" s="49" t="inlineStr">
-        <is>
-          <t>23.15 – 28.3 %</t>
-        </is>
-      </c>
-      <c r="F62" s="49" t="inlineStr">
-        <is>
-          <t>ППК26009</t>
-        </is>
-      </c>
-      <c r="G62" s="49" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H62" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I62" s="49" t="inlineStr">
+      <c r="A62" s="50" t="n">
+        <v>35</v>
+      </c>
+      <c r="B62" s="51" t="inlineStr">
+        <is>
+          <t>GP062501</t>
+        </is>
+      </c>
+      <c r="C62" s="52" t="inlineStr">
+        <is>
+          <t>P050202</t>
+        </is>
+      </c>
+      <c r="D62" s="52" t="inlineStr">
+        <is>
+          <t>24.89%</t>
+        </is>
+      </c>
+      <c r="E62" s="52" t="inlineStr">
+        <is>
+          <t>19.8 – 24.2 %</t>
+        </is>
+      </c>
+      <c r="F62" s="52" t="inlineStr">
+        <is>
+          <t>In-house HPLC cross-check NPCCC/SCP-02, NGP/QCG/SOP-024</t>
+        </is>
+      </c>
+      <c r="G62" s="52" t="inlineStr">
+        <is>
+          <t>28.11.2025</t>
+        </is>
+      </c>
+      <c r="H62" s="52" t="inlineStr">
+        <is>
+          <t>Purely Plant (in-house)</t>
+        </is>
+      </c>
+      <c r="I62" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="47" t="n">
-        <v>41</v>
-      </c>
-      <c r="B63" s="48" t="inlineStr">
-        <is>
-          <t>P160012</t>
-        </is>
-      </c>
-      <c r="C63" s="49" t="inlineStr">
-        <is>
-          <t>P160012</t>
-        </is>
-      </c>
-      <c r="D63" s="49" t="inlineStr">
-        <is>
-          <t>26.32%</t>
-        </is>
-      </c>
-      <c r="E63" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F63" s="49" t="inlineStr">
-        <is>
-          <t>ППК26117</t>
-        </is>
-      </c>
-      <c r="G63" s="49" t="inlineStr">
-        <is>
-          <t>06.07.2026</t>
-        </is>
-      </c>
-      <c r="H63" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I63" s="49" t="inlineStr">
+      <c r="D63" s="54" t="inlineStr">
+        <is>
+          <t>22.83% (stability 3 mo, 25°C / 60% RH)</t>
+        </is>
+      </c>
+      <c r="E63" s="54" t="inlineStr">
+        <is>
+          <t>STABILITY — not a release value</t>
+        </is>
+      </c>
+      <c r="F63" s="54" t="inlineStr">
+        <is>
+          <t>ППК26036</t>
+        </is>
+      </c>
+      <c r="G63" s="54" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="H63" s="54" t="inlineStr">
+        <is>
+          <t>Универзитет ,,Св. Кирил и Методиј“, Скопје, Фармацевтски факултет, Центар за природни производи</t>
+        </is>
+      </c>
+      <c r="I63" s="54" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="B64" s="48" t="inlineStr">
-        <is>
-          <t>P160022</t>
-        </is>
-      </c>
-      <c r="C64" s="49" t="inlineStr">
-        <is>
-          <t>P160022</t>
-        </is>
-      </c>
-      <c r="D64" s="49" t="inlineStr">
-        <is>
-          <t>25.72%</t>
-        </is>
-      </c>
-      <c r="E64" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F64" s="49" t="inlineStr">
-        <is>
-          <t>ППК26118</t>
-        </is>
-      </c>
-      <c r="G64" s="49" t="inlineStr">
-        <is>
-          <t>06.07.2026</t>
-        </is>
-      </c>
-      <c r="H64" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I64" s="49" t="inlineStr">
+      <c r="D64" s="54" t="inlineStr">
+        <is>
+          <t>18.62% (stability 3 mo, 40°C / 75% RH)</t>
+        </is>
+      </c>
+      <c r="E64" s="54" t="inlineStr">
+        <is>
+          <t>STABILITY — not a release value</t>
+        </is>
+      </c>
+      <c r="F64" s="54" t="inlineStr">
+        <is>
+          <t>ППК26037</t>
+        </is>
+      </c>
+      <c r="G64" s="54" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="H64" s="54" t="inlineStr">
+        <is>
+          <t>Универзитет „Св. Кирил и Методиј“, Скопје, Фармацевтски факултет, Центар за природни производи</t>
+        </is>
+      </c>
+      <c r="I64" s="54" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="47" t="n">
-        <v>43</v>
-      </c>
-      <c r="B65" s="48" t="inlineStr">
-        <is>
-          <t>P160032</t>
-        </is>
-      </c>
-      <c r="C65" s="49" t="inlineStr">
-        <is>
-          <t>P160032</t>
-        </is>
-      </c>
-      <c r="D65" s="49" t="inlineStr">
-        <is>
-          <t>24.78%</t>
-        </is>
-      </c>
-      <c r="E65" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F65" s="49" t="inlineStr">
-        <is>
-          <t>ППК26119</t>
-        </is>
-      </c>
-      <c r="G65" s="49" t="inlineStr">
-        <is>
-          <t>06.07.2026</t>
-        </is>
-      </c>
-      <c r="H65" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I65" s="49" t="inlineStr">
+      <c r="D65" s="54" t="inlineStr">
+        <is>
+          <t>24.51% (stability 6 mo, 25°C / 60% RH)</t>
+        </is>
+      </c>
+      <c r="E65" s="54" t="inlineStr">
+        <is>
+          <t>STABILITY — not a release value</t>
+        </is>
+      </c>
+      <c r="F65" s="54" t="inlineStr">
+        <is>
+          <t>ППК26057</t>
+        </is>
+      </c>
+      <c r="G65" s="54" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H65" s="54" t="inlineStr">
+        <is>
+          <t>Sts. Cyril and Methodius University, Skopje, Faculty of Pharmacy, Center for natural products</t>
+        </is>
+      </c>
+      <c r="I65" s="54" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="19.5" customHeight="1">
-      <c r="A66" s="46" t="inlineStr">
-        <is>
-          <t>Graps &amp; Creme      1 batch(es)      Total Δ⁹-THC across batches: 11.53 %</t>
+    <row r="66">
+      <c r="A66" s="53" t="n"/>
+      <c r="B66" s="53" t="n"/>
+      <c r="C66" s="53" t="n"/>
+      <c r="D66" s="55" t="inlineStr">
+        <is>
+          <t>1.17% (stability 6 mo, 40°C / 75% RH)</t>
+        </is>
+      </c>
+      <c r="E66" s="55" t="inlineStr">
+        <is>
+          <t>STABILITY — not a release value</t>
+        </is>
+      </c>
+      <c r="F66" s="55" t="inlineStr">
+        <is>
+          <t>ППК26058</t>
+        </is>
+      </c>
+      <c r="G66" s="55" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H66" s="55" t="inlineStr">
+        <is>
+          <t>Универзитет „Св. Кирил и Методиј“, Скопје, Фармацевтски факултет, Центар за природни производи</t>
+        </is>
+      </c>
+      <c r="I66" s="55" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="47" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B67" s="48" t="inlineStr">
         <is>
-          <t>GRC102501-2</t>
-        </is>
-      </c>
-      <c r="C67" s="49" t="n"/>
+          <t>GP072501-1</t>
+        </is>
+      </c>
+      <c r="C67" s="49" t="inlineStr">
+        <is>
+          <t>P050292</t>
+        </is>
+      </c>
       <c r="D67" s="49" t="inlineStr">
         <is>
-          <t>11.53 %w/w (U ±0.71)</t>
+          <t>21.36%</t>
         </is>
       </c>
       <c r="E67" s="49" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>19.2 – 23.4 %</t>
         </is>
       </c>
       <c r="F67" s="49" t="inlineStr">
         <is>
-          <t>051-6-K/26</t>
+          <t>PP CoA #018 / ППК25378</t>
         </is>
       </c>
       <c r="G67" s="49" t="inlineStr">
         <is>
-          <t>04.03.2026</t>
+          <t>21.01.2026</t>
         </is>
       </c>
       <c r="H67" s="49" t="inlineStr">
         <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I67" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="47" t="n">
+        <v>37</v>
+      </c>
+      <c r="B68" s="48" t="inlineStr">
+        <is>
+          <t>GP072501-2</t>
+        </is>
+      </c>
+      <c r="C68" s="49" t="inlineStr">
+        <is>
+          <t>P050302</t>
+        </is>
+      </c>
+      <c r="D68" s="49" t="inlineStr">
+        <is>
+          <t>19.81%</t>
+        </is>
+      </c>
+      <c r="E68" s="49" t="inlineStr">
+        <is>
+          <t>17.8 – 21.7 %</t>
+        </is>
+      </c>
+      <c r="F68" s="49" t="inlineStr">
+        <is>
+          <t>PP CoA #019 / ППК25379</t>
+        </is>
+      </c>
+      <c r="G68" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H68" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I68" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="47" t="n">
+        <v>38</v>
+      </c>
+      <c r="B69" s="48" t="inlineStr">
+        <is>
+          <t>GP082501-1</t>
+        </is>
+      </c>
+      <c r="C69" s="49" t="inlineStr">
+        <is>
+          <t>P050312</t>
+        </is>
+      </c>
+      <c r="D69" s="49" t="inlineStr">
+        <is>
+          <t>21.29%</t>
+        </is>
+      </c>
+      <c r="E69" s="49" t="inlineStr">
+        <is>
+          <t>19.1 – 23.4 %</t>
+        </is>
+      </c>
+      <c r="F69" s="49" t="inlineStr">
+        <is>
+          <t>PP CoA #020 / ППК25380</t>
+        </is>
+      </c>
+      <c r="G69" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H69" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I69" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="50" t="n">
+        <v>39</v>
+      </c>
+      <c r="B70" s="51" t="inlineStr">
+        <is>
+          <t>GP082501-2</t>
+        </is>
+      </c>
+      <c r="C70" s="52" t="inlineStr">
+        <is>
+          <t>P050322</t>
+        </is>
+      </c>
+      <c r="D70" s="52" t="inlineStr">
+        <is>
+          <t>14.83%</t>
+        </is>
+      </c>
+      <c r="E70" s="52" t="inlineStr">
+        <is>
+          <t>13.3 – 16.3 %</t>
+        </is>
+      </c>
+      <c r="F70" s="52" t="inlineStr">
+        <is>
+          <t>PP CoA #021 / ППК25381</t>
+        </is>
+      </c>
+      <c r="G70" s="52" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H70" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I70" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="53" t="n"/>
+      <c r="B71" s="53" t="n"/>
+      <c r="C71" s="53" t="n"/>
+      <c r="D71" s="49" t="inlineStr">
+        <is>
+          <t>15.70% w/w (U 0.96% w/w)</t>
+        </is>
+      </c>
+      <c r="E71" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F71" s="49" t="inlineStr">
+        <is>
+          <t>197-12-К/26</t>
+        </is>
+      </c>
+      <c r="G71" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H71" s="49" t="inlineStr">
+        <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I67" s="49" t="inlineStr">
+      <c r="I71" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="19.5" customHeight="1">
-      <c r="A68" s="46" t="inlineStr">
-        <is>
-          <t>High Pro Amnesia      3 batch(es)      Total Δ⁹-THC across batches: 14.97 – 22.43 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="50" t="n">
-        <v>45</v>
-      </c>
-      <c r="B69" s="51" t="inlineStr">
-        <is>
-          <t>HPA1024_01</t>
-        </is>
-      </c>
-      <c r="C69" s="52" t="inlineStr">
-        <is>
-          <t>P050052</t>
-        </is>
-      </c>
-      <c r="D69" s="52" t="inlineStr">
-        <is>
-          <t>22.43%</t>
-        </is>
-      </c>
-      <c r="E69" s="52" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F69" s="52" t="inlineStr">
-        <is>
-          <t>НИК22155 (likely OCR misread of ППК25xxx)</t>
-        </is>
-      </c>
-      <c r="G69" s="52" t="inlineStr">
-        <is>
-          <t>24.06.2025</t>
-        </is>
-      </c>
-      <c r="H69" s="52" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="47" t="n">
+        <v>40</v>
+      </c>
+      <c r="B72" s="48" t="inlineStr">
+        <is>
+          <t>GP092501</t>
+        </is>
+      </c>
+      <c r="C72" s="49" t="inlineStr">
+        <is>
+          <t>P060092</t>
+        </is>
+      </c>
+      <c r="D72" s="49" t="inlineStr">
+        <is>
+          <t>25.73%</t>
+        </is>
+      </c>
+      <c r="E72" s="49" t="inlineStr">
+        <is>
+          <t>23.15 – 28.3 %</t>
+        </is>
+      </c>
+      <c r="F72" s="49" t="inlineStr">
+        <is>
+          <t>ППК26009</t>
+        </is>
+      </c>
+      <c r="G72" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H72" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I69" s="52" t="inlineStr">
+      <c r="I72" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="53" t="n"/>
-      <c r="B70" s="53" t="n"/>
-      <c r="C70" s="53" t="n"/>
-      <c r="D70" s="49" t="inlineStr">
-        <is>
-          <t>21.61 %w/w (U 1.33)</t>
-        </is>
-      </c>
-      <c r="E70" s="49" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="47" t="n">
+        <v>41</v>
+      </c>
+      <c r="B73" s="48" t="inlineStr">
+        <is>
+          <t>P160012</t>
+        </is>
+      </c>
+      <c r="C73" s="49" t="inlineStr">
+        <is>
+          <t>P160012</t>
+        </is>
+      </c>
+      <c r="D73" s="49" t="inlineStr">
+        <is>
+          <t>26.32%</t>
+        </is>
+      </c>
+      <c r="E73" s="49" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F70" s="49" t="inlineStr">
-        <is>
-          <t>197-14-К/26</t>
-        </is>
-      </c>
-      <c r="G70" s="49" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H70" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I70" s="49" t="inlineStr">
+      <c r="F73" s="49" t="inlineStr">
+        <is>
+          <t>ППК26117</t>
+        </is>
+      </c>
+      <c r="G73" s="49" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="H73" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I73" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B71" s="48" t="inlineStr">
-        <is>
-          <t>HPA052501</t>
-        </is>
-      </c>
-      <c r="C71" s="49" t="inlineStr">
-        <is>
-          <t>P050182</t>
-        </is>
-      </c>
-      <c r="D71" s="49" t="inlineStr">
-        <is>
-          <t>20.39%</t>
-        </is>
-      </c>
-      <c r="E71" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F71" s="49" t="inlineStr">
-        <is>
-          <t>ППК25278</t>
-        </is>
-      </c>
-      <c r="G71" s="49" t="inlineStr">
-        <is>
-          <t>19.09.2025</t>
-        </is>
-      </c>
-      <c r="H71" s="49" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="47" t="n">
+        <v>42</v>
+      </c>
+      <c r="B74" s="48" t="inlineStr">
+        <is>
+          <t>P160022</t>
+        </is>
+      </c>
+      <c r="C74" s="49" t="inlineStr">
+        <is>
+          <t>P160022</t>
+        </is>
+      </c>
+      <c r="D74" s="49" t="inlineStr">
+        <is>
+          <t>25.72%</t>
+        </is>
+      </c>
+      <c r="E74" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F74" s="49" t="inlineStr">
+        <is>
+          <t>ППК26118</t>
+        </is>
+      </c>
+      <c r="G74" s="49" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="H74" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I71" s="49" t="inlineStr">
+      <c r="I74" s="49" t="inlineStr">
         <is>
           <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B72" s="51" t="inlineStr">
-        <is>
-          <t>HPA1024</t>
-        </is>
-      </c>
-      <c r="C72" s="52" t="n"/>
-      <c r="D72" s="52" t="inlineStr">
-        <is>
-          <t>14.97%</t>
-        </is>
-      </c>
-      <c r="E72" s="52" t="inlineStr">
-        <is>
-          <t>12.6 – 15.4 %</t>
-        </is>
-      </c>
-      <c r="F72" s="52" t="inlineStr">
-        <is>
-          <t>n/a — Purely Plant in-house CoA (Batch HPA1024, no certificate/report number printed)</t>
-        </is>
-      </c>
-      <c r="G72" s="52" t="inlineStr">
-        <is>
-          <t>23.01.2025</t>
-        </is>
-      </c>
-      <c r="H72" s="52" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I72" s="52" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="53" t="n"/>
-      <c r="B73" s="53" t="n"/>
-      <c r="C73" s="53" t="n"/>
-      <c r="D73" s="49" t="inlineStr">
-        <is>
-          <t>17.31 %w/w (U 1.06 %w/w, k=2)</t>
-        </is>
-      </c>
-      <c r="E73" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F73" s="49" t="inlineStr">
-        <is>
-          <t>197-13-К/26</t>
-        </is>
-      </c>
-      <c r="G73" s="49" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H73" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I73" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="19.5" customHeight="1">
-      <c r="A74" s="46" t="inlineStr">
-        <is>
-          <t>Jelly Donutz      6 batch(es)      Total Δ⁹-THC across batches: 13.93 – 20.54 %</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="47" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B75" s="48" t="inlineStr">
         <is>
-          <t>JD012601</t>
-        </is>
-      </c>
-      <c r="C75" s="49" t="n"/>
+          <t>P160032</t>
+        </is>
+      </c>
+      <c r="C75" s="49" t="inlineStr">
+        <is>
+          <t>P160032</t>
+        </is>
+      </c>
       <c r="D75" s="49" t="inlineStr">
         <is>
-          <t>18.16%</t>
-        </is>
-      </c>
-      <c r="E75" s="49" t="n"/>
+          <t>24.78%</t>
+        </is>
+      </c>
+      <c r="E75" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
       <c r="F75" s="49" t="inlineStr">
         <is>
-          <t>ППК26064</t>
+          <t>ППК26119</t>
         </is>
       </c>
       <c r="G75" s="49" t="inlineStr">
         <is>
-          <t>11.05.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="H75" s="49" t="inlineStr">
@@ -37671,189 +37707,133 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B76" s="51" t="inlineStr">
-        <is>
-          <t>JD112501</t>
-        </is>
-      </c>
-      <c r="C76" s="52" t="n"/>
-      <c r="D76" s="52" t="inlineStr">
-        <is>
-          <t>19.64%</t>
-        </is>
-      </c>
-      <c r="E76" s="52" t="n"/>
-      <c r="F76" s="52" t="inlineStr">
-        <is>
-          <t>ППК26063</t>
-        </is>
-      </c>
-      <c r="G76" s="52" t="inlineStr">
-        <is>
-          <t>11.05.2026</t>
-        </is>
-      </c>
-      <c r="H76" s="52" t="inlineStr">
+    <row r="76" ht="19.5" customHeight="1">
+      <c r="A76" s="46" t="inlineStr">
+        <is>
+          <t>Graps &amp; Creme      1 batch(es)      Total Δ⁹-THC across batches (release): 11.53 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="47" t="n">
+        <v>44</v>
+      </c>
+      <c r="B77" s="48" t="inlineStr">
+        <is>
+          <t>GRC102501-2</t>
+        </is>
+      </c>
+      <c r="C77" s="49" t="n"/>
+      <c r="D77" s="49" t="inlineStr">
+        <is>
+          <t>11.53 %w/w (U ±0.71)</t>
+        </is>
+      </c>
+      <c r="E77" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F77" s="49" t="inlineStr">
+        <is>
+          <t>051-6-K/26</t>
+        </is>
+      </c>
+      <c r="G77" s="49" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="H77" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I77" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="19.5" customHeight="1">
+      <c r="A78" s="46" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia      3 batch(es)      Total Δ⁹-THC across batches (release): 14.97 – 22.43 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="50" t="n">
+        <v>45</v>
+      </c>
+      <c r="B79" s="51" t="inlineStr">
+        <is>
+          <t>HPA1024_01</t>
+        </is>
+      </c>
+      <c r="C79" s="52" t="inlineStr">
+        <is>
+          <t>P050052</t>
+        </is>
+      </c>
+      <c r="D79" s="52" t="inlineStr">
+        <is>
+          <t>22.43%</t>
+        </is>
+      </c>
+      <c r="E79" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F79" s="52" t="inlineStr">
+        <is>
+          <t>НИК22155 (likely OCR misread of ППК25xxx)</t>
+        </is>
+      </c>
+      <c r="G79" s="52" t="inlineStr">
+        <is>
+          <t>24.06.2025</t>
+        </is>
+      </c>
+      <c r="H79" s="52" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I76" s="52" t="inlineStr">
+      <c r="I79" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="53" t="n"/>
-      <c r="B77" s="53" t="n"/>
-      <c r="C77" s="53" t="n"/>
-      <c r="D77" s="49" t="inlineStr">
-        <is>
-          <t>13.93%</t>
-        </is>
-      </c>
-      <c r="E77" s="49" t="n"/>
-      <c r="F77" s="49" t="inlineStr">
-        <is>
-          <t>ППК26065</t>
-        </is>
-      </c>
-      <c r="G77" s="49" t="inlineStr">
-        <is>
-          <t>11.05.2026</t>
-        </is>
-      </c>
-      <c r="H77" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I77" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="47" t="n">
-        <v>50</v>
-      </c>
-      <c r="B78" s="48" t="inlineStr">
-        <is>
-          <t>JD012603-02</t>
-        </is>
-      </c>
-      <c r="C78" s="49" t="n"/>
-      <c r="D78" s="49" t="inlineStr">
-        <is>
-          <t>20.54%</t>
-        </is>
-      </c>
-      <c r="E78" s="49" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="53" t="n"/>
+      <c r="B80" s="53" t="n"/>
+      <c r="C80" s="53" t="n"/>
+      <c r="D80" s="49" t="inlineStr">
+        <is>
+          <t>21.61 %w/w (U 1.33)</t>
+        </is>
+      </c>
+      <c r="E80" s="49" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F78" s="49" t="inlineStr">
-        <is>
-          <t>ППК26113</t>
-        </is>
-      </c>
-      <c r="G78" s="49" t="inlineStr">
-        <is>
-          <t>30.06.2026</t>
-        </is>
-      </c>
-      <c r="H78" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I78" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="B79" s="48" t="inlineStr">
-        <is>
-          <t>JD012603-02V</t>
-        </is>
-      </c>
-      <c r="C79" s="49" t="n"/>
-      <c r="D79" s="49" t="inlineStr">
-        <is>
-          <t>15.16%</t>
-        </is>
-      </c>
-      <c r="E79" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F79" s="49" t="inlineStr">
-        <is>
-          <t>ППК26111</t>
-        </is>
-      </c>
-      <c r="G79" s="49" t="inlineStr">
-        <is>
-          <t>30.06.2026</t>
-        </is>
-      </c>
-      <c r="H79" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I79" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="B80" s="48" t="inlineStr">
-        <is>
-          <t>JD022601</t>
-        </is>
-      </c>
-      <c r="C80" s="49" t="n"/>
-      <c r="D80" s="49" t="inlineStr">
-        <is>
-          <t>18.58%</t>
-        </is>
-      </c>
-      <c r="E80" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
       <c r="F80" s="49" t="inlineStr">
         <is>
-          <t>ППК26115</t>
+          <t>197-14-К/26</t>
         </is>
       </c>
       <c r="G80" s="49" t="inlineStr">
         <is>
-          <t>30.06.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="H80" s="49" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="I80" s="49" t="inlineStr">
@@ -37864,165 +37844,161 @@
     </row>
     <row r="81">
       <c r="A81" s="47" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B81" s="48" t="inlineStr">
         <is>
-          <t>P060212</t>
+          <t>HPA052501</t>
         </is>
       </c>
       <c r="C81" s="49" t="inlineStr">
         <is>
-          <t>P060212</t>
+          <t>P050182</t>
         </is>
       </c>
       <c r="D81" s="49" t="inlineStr">
         <is>
-          <t>20.32 %w/w (U 1.25 %w/w, k=2)</t>
+          <t>20.39%</t>
         </is>
       </c>
       <c r="E81" s="49" t="inlineStr">
         <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F81" s="49" t="inlineStr">
+        <is>
+          <t>ППК25278</t>
+        </is>
+      </c>
+      <c r="G81" s="49" t="inlineStr">
+        <is>
+          <t>19.09.2025</t>
+        </is>
+      </c>
+      <c r="H81" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I81" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="50" t="n">
+        <v>47</v>
+      </c>
+      <c r="B82" s="51" t="inlineStr">
+        <is>
+          <t>HPA1024</t>
+        </is>
+      </c>
+      <c r="C82" s="52" t="n"/>
+      <c r="D82" s="52" t="inlineStr">
+        <is>
+          <t>14.97%</t>
+        </is>
+      </c>
+      <c r="E82" s="52" t="inlineStr">
+        <is>
+          <t>12.6 – 15.4 %</t>
+        </is>
+      </c>
+      <c r="F82" s="52" t="inlineStr">
+        <is>
+          <t>n/a — Purely Plant in-house CoA (Batch HPA1024, no certificate/report number printed)</t>
+        </is>
+      </c>
+      <c r="G82" s="52" t="inlineStr">
+        <is>
+          <t>23.01.2025</t>
+        </is>
+      </c>
+      <c r="H82" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I82" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="53" t="n"/>
+      <c r="B83" s="53" t="n"/>
+      <c r="C83" s="53" t="n"/>
+      <c r="D83" s="49" t="inlineStr">
+        <is>
+          <t>17.31 %w/w (U 1.06 %w/w, k=2)</t>
+        </is>
+      </c>
+      <c r="E83" s="49" t="inlineStr">
+        <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F81" s="49" t="inlineStr">
-        <is>
-          <t>197-15-К/26</t>
-        </is>
-      </c>
-      <c r="G81" s="49" t="inlineStr">
+      <c r="F83" s="49" t="inlineStr">
+        <is>
+          <t>197-13-К/26</t>
+        </is>
+      </c>
+      <c r="G83" s="49" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H81" s="49" t="inlineStr">
+      <c r="H83" s="49" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I81" s="49" t="inlineStr">
+      <c r="I83" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="19.5" customHeight="1">
-      <c r="A82" s="46" t="inlineStr">
-        <is>
-          <t>Jokerz 31      4 batch(es)      Total Δ⁹-THC across batches: 17.32 – 25.27 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="47" t="n">
-        <v>54</v>
-      </c>
-      <c r="B83" s="48" t="inlineStr">
-        <is>
-          <t>J31102501</t>
-        </is>
-      </c>
-      <c r="C83" s="49" t="n"/>
-      <c r="D83" s="49" t="inlineStr">
-        <is>
-          <t>19.14 %w/w (U ±1.18)</t>
-        </is>
-      </c>
-      <c r="E83" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F83" s="49" t="inlineStr">
-        <is>
-          <t>051-1-K/26</t>
-        </is>
-      </c>
-      <c r="G83" s="49" t="inlineStr">
-        <is>
-          <t>04.03.2026</t>
-        </is>
-      </c>
-      <c r="H83" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I83" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="50" t="n">
-        <v>55</v>
-      </c>
-      <c r="B84" s="51" t="inlineStr">
-        <is>
-          <t>J31112501</t>
-        </is>
-      </c>
-      <c r="C84" s="52" t="n"/>
-      <c r="D84" s="52" t="inlineStr">
-        <is>
-          <t>25.27 %w/w (U ±1.55)</t>
-        </is>
-      </c>
-      <c r="E84" s="52" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F84" s="52" t="inlineStr">
-        <is>
-          <t>051-5-K/26</t>
-        </is>
-      </c>
-      <c r="G84" s="52" t="inlineStr">
-        <is>
-          <t>04.03.2026</t>
-        </is>
-      </c>
-      <c r="H84" s="52" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I84" s="52" t="inlineStr">
-        <is>
-          <t>Open</t>
+    <row r="84" ht="19.5" customHeight="1">
+      <c r="A84" s="46" t="inlineStr">
+        <is>
+          <t>Jelly Donutz      6 batch(es)      Total Δ⁹-THC across batches (release): 13.93 – 20.54 %</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="53" t="n"/>
-      <c r="B85" s="53" t="n"/>
-      <c r="C85" s="53" t="n"/>
+      <c r="A85" s="47" t="n">
+        <v>48</v>
+      </c>
+      <c r="B85" s="48" t="inlineStr">
+        <is>
+          <t>JD012601</t>
+        </is>
+      </c>
+      <c r="C85" s="49" t="n"/>
       <c r="D85" s="49" t="inlineStr">
         <is>
-          <t>20.21 %w/w (U ±1.24)</t>
-        </is>
-      </c>
-      <c r="E85" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>18.16%</t>
+        </is>
+      </c>
+      <c r="E85" s="49" t="n"/>
       <c r="F85" s="49" t="inlineStr">
         <is>
-          <t>100-1-K/26</t>
+          <t>ППК26064</t>
         </is>
       </c>
       <c r="G85" s="49" t="inlineStr">
         <is>
-          <t>09.04.2026</t>
+          <t>11.05.2026</t>
         </is>
       </c>
       <c r="H85" s="49" t="inlineStr">
         <is>
-          <t>Farmahem</t>
+          <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
       <c r="I85" s="49" t="inlineStr">
@@ -38033,37 +38009,33 @@
     </row>
     <row r="86">
       <c r="A86" s="50" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B86" s="51" t="inlineStr">
         <is>
-          <t>J31122501</t>
+          <t>JD112501</t>
         </is>
       </c>
       <c r="C86" s="52" t="n"/>
       <c r="D86" s="52" t="inlineStr">
         <is>
-          <t>19.84 %w/w (U ±1.22)</t>
-        </is>
-      </c>
-      <c r="E86" s="52" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>19.64%</t>
+        </is>
+      </c>
+      <c r="E86" s="52" t="n"/>
       <c r="F86" s="52" t="inlineStr">
         <is>
-          <t>100-2-К/26</t>
+          <t>ППК26063</t>
         </is>
       </c>
       <c r="G86" s="52" t="inlineStr">
         <is>
-          <t>09.04.2026</t>
+          <t>11.05.2026</t>
         </is>
       </c>
       <c r="H86" s="52" t="inlineStr">
         <is>
-          <t>Farmahem</t>
+          <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
       <c r="I86" s="52" t="inlineStr">
@@ -38078,27 +38050,23 @@
       <c r="C87" s="53" t="n"/>
       <c r="D87" s="49" t="inlineStr">
         <is>
-          <t>21.84 %w/w (U ±1.34)</t>
-        </is>
-      </c>
-      <c r="E87" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>13.93%</t>
+        </is>
+      </c>
+      <c r="E87" s="49" t="n"/>
       <c r="F87" s="49" t="inlineStr">
         <is>
-          <t>100-3-К/26</t>
+          <t>ППК26065</t>
         </is>
       </c>
       <c r="G87" s="49" t="inlineStr">
         <is>
-          <t>09.04.2026</t>
+          <t>11.05.2026</t>
         </is>
       </c>
       <c r="H87" s="49" t="inlineStr">
         <is>
-          <t>Farmahem</t>
+          <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
       <c r="I87" s="49" t="inlineStr">
@@ -38109,21 +38077,17 @@
     </row>
     <row r="88">
       <c r="A88" s="47" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B88" s="48" t="inlineStr">
         <is>
-          <t>P060152</t>
-        </is>
-      </c>
-      <c r="C88" s="49" t="inlineStr">
-        <is>
-          <t>P060152</t>
-        </is>
-      </c>
+          <t>JD012603-02</t>
+        </is>
+      </c>
+      <c r="C88" s="49" t="n"/>
       <c r="D88" s="49" t="inlineStr">
         <is>
-          <t>17.32 %w/w (U 1.06 %w/w, k=2)</t>
+          <t>20.54%</t>
         </is>
       </c>
       <c r="E88" s="49" t="inlineStr">
@@ -38133,17 +38097,17 @@
       </c>
       <c r="F88" s="49" t="inlineStr">
         <is>
-          <t>197-16-К/26</t>
+          <t>ППК26113</t>
         </is>
       </c>
       <c r="G88" s="49" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>30.06.2026</t>
         </is>
       </c>
       <c r="H88" s="49" t="inlineStr">
         <is>
-          <t>Farmahem</t>
+          <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
       <c r="I88" s="49" t="inlineStr">
@@ -38152,123 +38116,153 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="19.5" customHeight="1">
-      <c r="A89" s="46" t="inlineStr">
-        <is>
-          <t>Kush Crasher      1 batch(es)      Total Δ⁹-THC across batches: 17.04 %</t>
+    <row r="89">
+      <c r="A89" s="47" t="n">
+        <v>51</v>
+      </c>
+      <c r="B89" s="48" t="inlineStr">
+        <is>
+          <t>JD012603-02V</t>
+        </is>
+      </c>
+      <c r="C89" s="49" t="n"/>
+      <c r="D89" s="49" t="inlineStr">
+        <is>
+          <t>15.16%</t>
+        </is>
+      </c>
+      <c r="E89" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F89" s="49" t="inlineStr">
+        <is>
+          <t>ППК26111</t>
+        </is>
+      </c>
+      <c r="G89" s="49" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="H89" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I89" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="47" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B90" s="48" t="inlineStr">
         <is>
-          <t>KC102501</t>
+          <t>JD022601</t>
         </is>
       </c>
       <c r="C90" s="49" t="n"/>
       <c r="D90" s="49" t="inlineStr">
         <is>
-          <t>17.04 %w/w (U ±1.05)</t>
+          <t>18.58%</t>
         </is>
       </c>
       <c r="E90" s="49" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>≥ 5.00 %</t>
         </is>
       </c>
       <c r="F90" s="49" t="inlineStr">
         <is>
-          <t>051-4-K/26</t>
+          <t>ППК26115</t>
         </is>
       </c>
       <c r="G90" s="49" t="inlineStr">
         <is>
-          <t>04.03.2026</t>
+          <t>30.06.2026</t>
         </is>
       </c>
       <c r="H90" s="49" t="inlineStr">
         <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I90" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="47" t="n">
+        <v>53</v>
+      </c>
+      <c r="B91" s="48" t="inlineStr">
+        <is>
+          <t>P060212</t>
+        </is>
+      </c>
+      <c r="C91" s="49" t="inlineStr">
+        <is>
+          <t>P060212</t>
+        </is>
+      </c>
+      <c r="D91" s="49" t="inlineStr">
+        <is>
+          <t>20.32 %w/w (U 1.25 %w/w, k=2)</t>
+        </is>
+      </c>
+      <c r="E91" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F91" s="49" t="inlineStr">
+        <is>
+          <t>197-15-К/26</t>
+        </is>
+      </c>
+      <c r="G91" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H91" s="49" t="inlineStr">
+        <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I90" s="49" t="inlineStr">
+      <c r="I91" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="19.5" customHeight="1">
-      <c r="A91" s="46" t="inlineStr">
-        <is>
-          <t>Motor Breath      2 batch(es)      Total Δ⁹-THC across batches: 16.82 – 18.67 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="B92" s="48" t="inlineStr">
-        <is>
-          <t>MB0824_04</t>
-        </is>
-      </c>
-      <c r="C92" s="49" t="inlineStr">
-        <is>
-          <t>P050032</t>
-        </is>
-      </c>
-      <c r="D92" s="49" t="inlineStr">
-        <is>
-          <t>18.67%</t>
-        </is>
-      </c>
-      <c r="E92" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F92" s="49" t="inlineStr">
-        <is>
-          <t>ППК25118</t>
-        </is>
-      </c>
-      <c r="G92" s="49" t="inlineStr">
-        <is>
-          <t>06.05.2025</t>
-        </is>
-      </c>
-      <c r="H92" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I92" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
+    <row r="92" ht="19.5" customHeight="1">
+      <c r="A92" s="46" t="inlineStr">
+        <is>
+          <t>Jokerz 31      4 batch(es)      Total Δ⁹-THC across batches (release): 17.32 – 25.27 %</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="47" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B93" s="48" t="inlineStr">
         <is>
-          <t>MB0824_05</t>
-        </is>
-      </c>
-      <c r="C93" s="49" t="inlineStr">
-        <is>
-          <t>P050112</t>
-        </is>
-      </c>
+          <t>J31102501</t>
+        </is>
+      </c>
+      <c r="C93" s="49" t="n"/>
       <c r="D93" s="49" t="inlineStr">
         <is>
-          <t>16.82%</t>
+          <t>19.14 %w/w (U ±1.18)</t>
         </is>
       </c>
       <c r="E93" s="49" t="inlineStr">
@@ -38278,17 +38272,17 @@
       </c>
       <c r="F93" s="49" t="inlineStr">
         <is>
-          <t>ППК25211</t>
+          <t>051-1-K/26</t>
         </is>
       </c>
       <c r="G93" s="49" t="inlineStr">
         <is>
-          <t>28.07.2025</t>
+          <t>04.03.2026</t>
         </is>
       </c>
       <c r="H93" s="49" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="I93" s="49" t="inlineStr">
@@ -38297,30 +38291,54 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="19.5" customHeight="1">
-      <c r="A94" s="46" t="inlineStr">
-        <is>
-          <t>Orange Punch Mimosa      9 batch(es)      Total Δ⁹-THC across batches: 7.91 – 20.03 %</t>
+    <row r="94">
+      <c r="A94" s="50" t="n">
+        <v>55</v>
+      </c>
+      <c r="B94" s="51" t="inlineStr">
+        <is>
+          <t>J31112501</t>
+        </is>
+      </c>
+      <c r="C94" s="52" t="n"/>
+      <c r="D94" s="52" t="inlineStr">
+        <is>
+          <t>25.27 %w/w (U ±1.55)</t>
+        </is>
+      </c>
+      <c r="E94" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F94" s="52" t="inlineStr">
+        <is>
+          <t>051-5-K/26</t>
+        </is>
+      </c>
+      <c r="G94" s="52" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="H94" s="52" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I94" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="B95" s="48" t="inlineStr">
-        <is>
-          <t>OPM1024_01</t>
-        </is>
-      </c>
-      <c r="C95" s="49" t="inlineStr">
-        <is>
-          <t>P050042</t>
-        </is>
-      </c>
+      <c r="A95" s="53" t="n"/>
+      <c r="B95" s="53" t="n"/>
+      <c r="C95" s="53" t="n"/>
       <c r="D95" s="49" t="inlineStr">
         <is>
-          <t>15.38%</t>
+          <t>20.21 %w/w (U ±1.24)</t>
         </is>
       </c>
       <c r="E95" s="49" t="inlineStr">
@@ -38330,17 +38348,17 @@
       </c>
       <c r="F95" s="49" t="inlineStr">
         <is>
-          <t>ППК25117</t>
+          <t>100-1-K/26</t>
         </is>
       </c>
       <c r="G95" s="49" t="inlineStr">
         <is>
-          <t>06.05.2025</t>
+          <t>09.04.2026</t>
         </is>
       </c>
       <c r="H95" s="49" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="I95" s="49" t="inlineStr">
@@ -38351,21 +38369,17 @@
     </row>
     <row r="96">
       <c r="A96" s="50" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B96" s="51" t="inlineStr">
         <is>
-          <t>OPM1024_02</t>
-        </is>
-      </c>
-      <c r="C96" s="52" t="inlineStr">
-        <is>
-          <t>P050062</t>
-        </is>
-      </c>
+          <t>J31122501</t>
+        </is>
+      </c>
+      <c r="C96" s="52" t="n"/>
       <c r="D96" s="52" t="inlineStr">
         <is>
-          <t>18.27%</t>
+          <t>19.84 %w/w (U ±1.22)</t>
         </is>
       </c>
       <c r="E96" s="52" t="inlineStr">
@@ -38375,17 +38389,17 @@
       </c>
       <c r="F96" s="52" t="inlineStr">
         <is>
-          <t>ППК25154</t>
+          <t>100-2-К/26</t>
         </is>
       </c>
       <c r="G96" s="52" t="inlineStr">
         <is>
-          <t>24.06.2025</t>
+          <t>09.04.2026</t>
         </is>
       </c>
       <c r="H96" s="52" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="I96" s="52" t="inlineStr">
@@ -38400,22 +38414,22 @@
       <c r="C97" s="53" t="n"/>
       <c r="D97" s="49" t="inlineStr">
         <is>
-          <t>18.04 %w/w (U 1.11)</t>
+          <t>21.84 %w/w (U ±1.34)</t>
         </is>
       </c>
       <c r="E97" s="49" t="inlineStr">
         <is>
-          <t>≥ 5.00 %</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F97" s="49" t="inlineStr">
         <is>
-          <t>197-18-К/26</t>
+          <t>100-3-К/26</t>
         </is>
       </c>
       <c r="G97" s="49" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>09.04.2026</t>
         </is>
       </c>
       <c r="H97" s="49" t="inlineStr">
@@ -38431,41 +38445,41 @@
     </row>
     <row r="98">
       <c r="A98" s="47" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B98" s="48" t="inlineStr">
         <is>
-          <t>OPM1024_03</t>
+          <t>P060152</t>
         </is>
       </c>
       <c r="C98" s="49" t="inlineStr">
         <is>
-          <t>P050082</t>
+          <t>P060152</t>
         </is>
       </c>
       <c r="D98" s="49" t="inlineStr">
         <is>
-          <t>16.55%</t>
+          <t>17.32 %w/w (U 1.06 %w/w, k=2)</t>
         </is>
       </c>
       <c r="E98" s="49" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>≥ 5.00 %</t>
         </is>
       </c>
       <c r="F98" s="49" t="inlineStr">
         <is>
-          <t>ППК25210</t>
+          <t>197-16-К/26</t>
         </is>
       </c>
       <c r="G98" s="49" t="inlineStr">
         <is>
-          <t>28.07.2025</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="H98" s="49" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="I98" s="49" t="inlineStr">
@@ -38474,88 +38488,46 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="47" t="n">
-        <v>64</v>
-      </c>
-      <c r="B99" s="48" t="inlineStr">
-        <is>
-          <t>OPM052501</t>
-        </is>
-      </c>
-      <c r="C99" s="49" t="inlineStr">
-        <is>
-          <t>P050132</t>
-        </is>
-      </c>
-      <c r="D99" s="49" t="inlineStr">
-        <is>
-          <t>14.16%</t>
-        </is>
-      </c>
-      <c r="E99" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F99" s="49" t="inlineStr">
-        <is>
-          <t>ППК25257</t>
-        </is>
-      </c>
-      <c r="G99" s="49" t="inlineStr">
-        <is>
-          <t>05.09.2025</t>
-        </is>
-      </c>
-      <c r="H99" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I99" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
+    <row r="99" ht="19.5" customHeight="1">
+      <c r="A99" s="46" t="inlineStr">
+        <is>
+          <t>Kush Crasher      1 batch(es)      Total Δ⁹-THC across batches (release): 17.04 %</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="47" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B100" s="48" t="inlineStr">
         <is>
-          <t>OPM092501</t>
-        </is>
-      </c>
-      <c r="C100" s="49" t="inlineStr">
-        <is>
-          <t>P060042</t>
-        </is>
-      </c>
+          <t>KC102501</t>
+        </is>
+      </c>
+      <c r="C100" s="49" t="n"/>
       <c r="D100" s="49" t="inlineStr">
         <is>
-          <t>9.43%</t>
+          <t>17.04 %w/w (U ±1.05)</t>
         </is>
       </c>
       <c r="E100" s="49" t="inlineStr">
         <is>
-          <t>8.48 – 10.37 %</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F100" s="49" t="inlineStr">
         <is>
-          <t>ППК26008</t>
+          <t>051-4-K/26</t>
         </is>
       </c>
       <c r="G100" s="49" t="inlineStr">
         <is>
-          <t>21.01.2026</t>
+          <t>04.03.2026</t>
         </is>
       </c>
       <c r="H100" s="49" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="I100" s="49" t="inlineStr">
@@ -38564,60 +38536,30 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="47" t="n">
-        <v>66</v>
-      </c>
-      <c r="B101" s="48" t="inlineStr">
-        <is>
-          <t>OPM112501</t>
-        </is>
-      </c>
-      <c r="C101" s="49" t="n"/>
-      <c r="D101" s="49" t="inlineStr">
-        <is>
-          <t>8.00%</t>
-        </is>
-      </c>
-      <c r="E101" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F101" s="49" t="inlineStr">
-        <is>
-          <t>ППК26031</t>
-        </is>
-      </c>
-      <c r="G101" s="49" t="inlineStr">
-        <is>
-          <t>05.03.2026</t>
-        </is>
-      </c>
-      <c r="H101" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I101" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
+    <row r="101" ht="19.5" customHeight="1">
+      <c r="A101" s="46" t="inlineStr">
+        <is>
+          <t>Motor Breath      2 batch(es)      Total Δ⁹-THC across batches (release): 16.82 – 18.67 %</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="47" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B102" s="48" t="inlineStr">
         <is>
-          <t>OPM122501</t>
-        </is>
-      </c>
-      <c r="C102" s="49" t="n"/>
+          <t>MB0824_04</t>
+        </is>
+      </c>
+      <c r="C102" s="49" t="inlineStr">
+        <is>
+          <t>P050032</t>
+        </is>
+      </c>
       <c r="D102" s="49" t="inlineStr">
         <is>
-          <t>8.09 %w/w (U ±0.50)</t>
+          <t>18.67%</t>
         </is>
       </c>
       <c r="E102" s="49" t="inlineStr">
@@ -38627,17 +38569,17 @@
       </c>
       <c r="F102" s="49" t="inlineStr">
         <is>
-          <t>100-4-К/26</t>
+          <t>ППК25118</t>
         </is>
       </c>
       <c r="G102" s="49" t="inlineStr">
         <is>
-          <t>09.04.2026</t>
+          <t>06.05.2025</t>
         </is>
       </c>
       <c r="H102" s="49" t="inlineStr">
         <is>
-          <t>Farmahem</t>
+          <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
       <c r="I102" s="49" t="inlineStr">
@@ -38648,249 +38590,263 @@
     </row>
     <row r="103">
       <c r="A103" s="47" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B103" s="48" t="inlineStr">
         <is>
-          <t>P060242</t>
+          <t>MB0824_05</t>
         </is>
       </c>
       <c r="C103" s="49" t="inlineStr">
         <is>
-          <t>P060242</t>
+          <t>P050112</t>
         </is>
       </c>
       <c r="D103" s="49" t="inlineStr">
         <is>
-          <t>7.91 %w/w (U 0.49 %w/w, k=2)</t>
+          <t>16.82%</t>
         </is>
       </c>
       <c r="E103" s="49" t="inlineStr">
         <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F103" s="49" t="inlineStr">
+        <is>
+          <t>ППК25211</t>
+        </is>
+      </c>
+      <c r="G103" s="49" t="inlineStr">
+        <is>
+          <t>28.07.2025</t>
+        </is>
+      </c>
+      <c r="H103" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I103" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="19.5" customHeight="1">
+      <c r="A104" s="46" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa      9 batch(es)      Total Δ⁹-THC across batches (release): 7.91 – 20.03 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="47" t="n">
+        <v>61</v>
+      </c>
+      <c r="B105" s="48" t="inlineStr">
+        <is>
+          <t>OPM1024_01</t>
+        </is>
+      </c>
+      <c r="C105" s="49" t="inlineStr">
+        <is>
+          <t>P050042</t>
+        </is>
+      </c>
+      <c r="D105" s="49" t="inlineStr">
+        <is>
+          <t>15.38%</t>
+        </is>
+      </c>
+      <c r="E105" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F105" s="49" t="inlineStr">
+        <is>
+          <t>ППК25117</t>
+        </is>
+      </c>
+      <c r="G105" s="49" t="inlineStr">
+        <is>
+          <t>06.05.2025</t>
+        </is>
+      </c>
+      <c r="H105" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I105" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="50" t="n">
+        <v>62</v>
+      </c>
+      <c r="B106" s="51" t="inlineStr">
+        <is>
+          <t>OPM1024_02</t>
+        </is>
+      </c>
+      <c r="C106" s="52" t="inlineStr">
+        <is>
+          <t>P050062</t>
+        </is>
+      </c>
+      <c r="D106" s="52" t="inlineStr">
+        <is>
+          <t>18.27%</t>
+        </is>
+      </c>
+      <c r="E106" s="52" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F106" s="52" t="inlineStr">
+        <is>
+          <t>ППК25154</t>
+        </is>
+      </c>
+      <c r="G106" s="52" t="inlineStr">
+        <is>
+          <t>24.06.2025</t>
+        </is>
+      </c>
+      <c r="H106" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I106" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="53" t="n"/>
+      <c r="B107" s="53" t="n"/>
+      <c r="C107" s="53" t="n"/>
+      <c r="D107" s="49" t="inlineStr">
+        <is>
+          <t>18.04 %w/w (U 1.11)</t>
+        </is>
+      </c>
+      <c r="E107" s="49" t="inlineStr">
+        <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F103" s="49" t="inlineStr">
-        <is>
-          <t>197-19-К/26</t>
-        </is>
-      </c>
-      <c r="G103" s="49" t="inlineStr">
+      <c r="F107" s="49" t="inlineStr">
+        <is>
+          <t>197-18-К/26</t>
+        </is>
+      </c>
+      <c r="G107" s="49" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H103" s="49" t="inlineStr">
+      <c r="H107" s="49" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I103" s="49" t="inlineStr">
+      <c r="I107" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="50" t="n">
-        <v>69</v>
-      </c>
-      <c r="B104" s="51" t="inlineStr">
-        <is>
-          <t>OPM1024</t>
-        </is>
-      </c>
-      <c r="C104" s="52" t="n"/>
-      <c r="D104" s="52" t="inlineStr">
-        <is>
-          <t>19.96%</t>
-        </is>
-      </c>
-      <c r="E104" s="52" t="inlineStr">
-        <is>
-          <t>18.0 – 22.0 %</t>
-        </is>
-      </c>
-      <c r="F104" s="52" t="inlineStr">
-        <is>
-          <t>n/a — Purely Plant in-house CoA (Batch OPM1024, no certificate/report number printed)</t>
-        </is>
-      </c>
-      <c r="G104" s="52" t="inlineStr">
-        <is>
-          <t>23.04.2025</t>
-        </is>
-      </c>
-      <c r="H104" s="52" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="47" t="n">
+        <v>63</v>
+      </c>
+      <c r="B108" s="48" t="inlineStr">
+        <is>
+          <t>OPM1024_03</t>
+        </is>
+      </c>
+      <c r="C108" s="49" t="inlineStr">
+        <is>
+          <t>P050082</t>
+        </is>
+      </c>
+      <c r="D108" s="49" t="inlineStr">
+        <is>
+          <t>16.55%</t>
+        </is>
+      </c>
+      <c r="E108" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F108" s="49" t="inlineStr">
+        <is>
+          <t>ППК25210</t>
+        </is>
+      </c>
+      <c r="G108" s="49" t="inlineStr">
+        <is>
+          <t>28.07.2025</t>
+        </is>
+      </c>
+      <c r="H108" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I104" s="52" t="inlineStr">
+      <c r="I108" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="53" t="n"/>
-      <c r="B105" s="53" t="n"/>
-      <c r="C105" s="53" t="n"/>
-      <c r="D105" s="49" t="inlineStr">
-        <is>
-          <t>20.03 %w/w (U 1.23 %w/w, k=2)</t>
-        </is>
-      </c>
-      <c r="E105" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F105" s="49" t="inlineStr">
-        <is>
-          <t>197-17-К/26</t>
-        </is>
-      </c>
-      <c r="G105" s="49" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H105" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I105" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="19.5" customHeight="1">
-      <c r="A106" s="46" t="inlineStr">
-        <is>
-          <t>Permanent Market      3 batch(es)      Total Δ⁹-THC across batches: 10.01 – 14.06 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="47" t="n">
-        <v>70</v>
-      </c>
-      <c r="B107" s="48" t="inlineStr">
-        <is>
-          <t>PM072501</t>
-        </is>
-      </c>
-      <c r="C107" s="49" t="inlineStr">
-        <is>
-          <t>P050272</t>
-        </is>
-      </c>
-      <c r="D107" s="49" t="inlineStr">
-        <is>
-          <t>10.01%</t>
-        </is>
-      </c>
-      <c r="E107" s="49" t="inlineStr">
-        <is>
-          <t>9 – 11.01 %</t>
-        </is>
-      </c>
-      <c r="F107" s="49" t="inlineStr">
-        <is>
-          <t>ППК25368</t>
-        </is>
-      </c>
-      <c r="G107" s="49" t="inlineStr">
-        <is>
-          <t>28.11.2025</t>
-        </is>
-      </c>
-      <c r="H107" s="49" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="47" t="n">
+        <v>64</v>
+      </c>
+      <c r="B109" s="48" t="inlineStr">
+        <is>
+          <t>OPM052501</t>
+        </is>
+      </c>
+      <c r="C109" s="49" t="inlineStr">
+        <is>
+          <t>P050132</t>
+        </is>
+      </c>
+      <c r="D109" s="49" t="inlineStr">
+        <is>
+          <t>14.16%</t>
+        </is>
+      </c>
+      <c r="E109" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F109" s="49" t="inlineStr">
+        <is>
+          <t>ППК25257</t>
+        </is>
+      </c>
+      <c r="G109" s="49" t="inlineStr">
+        <is>
+          <t>05.09.2025</t>
+        </is>
+      </c>
+      <c r="H109" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I107" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="50" t="n">
-        <v>71</v>
-      </c>
-      <c r="B108" s="51" t="inlineStr">
-        <is>
-          <t>PM092501</t>
-        </is>
-      </c>
-      <c r="C108" s="52" t="inlineStr">
-        <is>
-          <t>P060062</t>
-        </is>
-      </c>
-      <c r="D108" s="52" t="inlineStr">
-        <is>
-          <t>14.06%</t>
-        </is>
-      </c>
-      <c r="E108" s="52" t="inlineStr">
-        <is>
-          <t>12.65 – 15.46 %</t>
-        </is>
-      </c>
-      <c r="F108" s="52" t="inlineStr">
-        <is>
-          <t>ППК26004</t>
-        </is>
-      </c>
-      <c r="G108" s="52" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H108" s="52" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I108" s="52" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="53" t="n"/>
-      <c r="B109" s="53" t="n"/>
-      <c r="C109" s="53" t="n"/>
-      <c r="D109" s="49" t="inlineStr">
-        <is>
-          <t>12.25% w/w (U 0.75% w/w)</t>
-        </is>
-      </c>
-      <c r="E109" s="49" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F109" s="49" t="inlineStr">
-        <is>
-          <t>197-20-К/26</t>
-        </is>
-      </c>
-      <c r="G109" s="49" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H109" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
         </is>
       </c>
       <c r="I109" s="49" t="inlineStr">
@@ -38901,81 +38857,123 @@
     </row>
     <row r="110">
       <c r="A110" s="47" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B110" s="48" t="inlineStr">
         <is>
-          <t>PM112501</t>
-        </is>
-      </c>
-      <c r="C110" s="49" t="n"/>
+          <t>OPM092501</t>
+        </is>
+      </c>
+      <c r="C110" s="49" t="inlineStr">
+        <is>
+          <t>P060042</t>
+        </is>
+      </c>
       <c r="D110" s="49" t="inlineStr">
         <is>
-          <t>13.33%</t>
+          <t>9.43%</t>
         </is>
       </c>
       <c r="E110" s="49" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>8.48 – 10.37 %</t>
         </is>
       </c>
       <c r="F110" s="49" t="inlineStr">
         <is>
-          <t>ППК26030</t>
+          <t>ППК26008</t>
         </is>
       </c>
       <c r="G110" s="49" t="inlineStr">
         <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H110" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I110" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="47" t="n">
+        <v>66</v>
+      </c>
+      <c r="B111" s="48" t="inlineStr">
+        <is>
+          <t>OPM112501</t>
+        </is>
+      </c>
+      <c r="C111" s="49" t="n"/>
+      <c r="D111" s="49" t="inlineStr">
+        <is>
+          <t>8.00%</t>
+        </is>
+      </c>
+      <c r="E111" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F111" s="49" t="inlineStr">
+        <is>
+          <t>ППК26031</t>
+        </is>
+      </c>
+      <c r="G111" s="49" t="inlineStr">
+        <is>
           <t>05.03.2026</t>
         </is>
       </c>
-      <c r="H110" s="49" t="inlineStr">
+      <c r="H111" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I110" s="49" t="inlineStr">
+      <c r="I111" s="49" t="inlineStr">
         <is>
           <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="19.5" customHeight="1">
-      <c r="A111" s="46" t="inlineStr">
-        <is>
-          <t>Scrambler      3 batch(es)      Total Δ⁹-THC across batches: 17.13 – 21.92 %</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="47" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B112" s="48" t="inlineStr">
         <is>
-          <t>SCR112501</t>
+          <t>OPM122501</t>
         </is>
       </c>
       <c r="C112" s="49" t="n"/>
       <c r="D112" s="49" t="inlineStr">
         <is>
-          <t>17.13%</t>
-        </is>
-      </c>
-      <c r="E112" s="49" t="n"/>
+          <t>8.09 %w/w (U ±0.50)</t>
+        </is>
+      </c>
+      <c r="E112" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F112" s="49" t="inlineStr">
         <is>
-          <t>ППК26069</t>
+          <t>100-4-К/26</t>
         </is>
       </c>
       <c r="G112" s="49" t="inlineStr">
         <is>
-          <t>11.05.2026</t>
+          <t>09.04.2026</t>
         </is>
       </c>
       <c r="H112" s="49" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="I112" s="49" t="inlineStr">
@@ -38986,17 +38984,21 @@
     </row>
     <row r="113">
       <c r="A113" s="47" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B113" s="48" t="inlineStr">
         <is>
-          <t>SCR022601</t>
-        </is>
-      </c>
-      <c r="C113" s="49" t="n"/>
+          <t>P060242</t>
+        </is>
+      </c>
+      <c r="C113" s="49" t="inlineStr">
+        <is>
+          <t>P060242</t>
+        </is>
+      </c>
       <c r="D113" s="49" t="inlineStr">
         <is>
-          <t>21.92%</t>
+          <t>7.91 %w/w (U 0.49 %w/w, k=2)</t>
         </is>
       </c>
       <c r="E113" s="49" t="inlineStr">
@@ -39006,376 +39008,716 @@
       </c>
       <c r="F113" s="49" t="inlineStr">
         <is>
-          <t>ППК26116</t>
+          <t>197-19-К/26</t>
         </is>
       </c>
       <c r="G113" s="49" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="H113" s="49" t="inlineStr">
         <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I113" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="50" t="n">
+        <v>69</v>
+      </c>
+      <c r="B114" s="51" t="inlineStr">
+        <is>
+          <t>OPM1024</t>
+        </is>
+      </c>
+      <c r="C114" s="52" t="n"/>
+      <c r="D114" s="52" t="inlineStr">
+        <is>
+          <t>19.96%</t>
+        </is>
+      </c>
+      <c r="E114" s="52" t="inlineStr">
+        <is>
+          <t>18.0 – 22.0 %</t>
+        </is>
+      </c>
+      <c r="F114" s="52" t="inlineStr">
+        <is>
+          <t>n/a — Purely Plant in-house CoA (Batch OPM1024, no certificate/report number printed)</t>
+        </is>
+      </c>
+      <c r="G114" s="52" t="inlineStr">
+        <is>
+          <t>23.04.2025</t>
+        </is>
+      </c>
+      <c r="H114" s="52" t="inlineStr">
+        <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I113" s="49" t="inlineStr">
+      <c r="I114" s="52" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="47" t="n">
-        <v>75</v>
-      </c>
-      <c r="B114" s="48" t="inlineStr">
-        <is>
-          <t>P060382</t>
-        </is>
-      </c>
-      <c r="C114" s="49" t="inlineStr">
-        <is>
-          <t>P060382</t>
-        </is>
-      </c>
-      <c r="D114" s="49" t="inlineStr">
-        <is>
-          <t>17.84 %w/w (U 1.10 %w/w, k=2)</t>
-        </is>
-      </c>
-      <c r="E114" s="49" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="53" t="n"/>
+      <c r="B115" s="53" t="n"/>
+      <c r="C115" s="53" t="n"/>
+      <c r="D115" s="49" t="inlineStr">
+        <is>
+          <t>20.03 %w/w (U 1.23 %w/w, k=2)</t>
+        </is>
+      </c>
+      <c r="E115" s="49" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F114" s="49" t="inlineStr">
-        <is>
-          <t>197-21-К/26</t>
-        </is>
-      </c>
-      <c r="G114" s="49" t="inlineStr">
+      <c r="F115" s="49" t="inlineStr">
+        <is>
+          <t>197-17-К/26</t>
+        </is>
+      </c>
+      <c r="G115" s="49" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H114" s="49" t="inlineStr">
+      <c r="H115" s="49" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I114" s="49" t="inlineStr">
+      <c r="I115" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="19.5" customHeight="1">
-      <c r="A115" s="46" t="inlineStr">
-        <is>
-          <t>Sleepy Joy      3 batch(es)      Total Δ⁹-THC across batches: 9.20 – 11.20 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="47" t="n">
-        <v>76</v>
-      </c>
-      <c r="B116" s="48" t="inlineStr">
-        <is>
-          <t>SJ092501</t>
-        </is>
-      </c>
-      <c r="C116" s="49" t="inlineStr">
-        <is>
-          <t>P060082</t>
-        </is>
-      </c>
-      <c r="D116" s="49" t="inlineStr">
-        <is>
-          <t>10.96%</t>
-        </is>
-      </c>
-      <c r="E116" s="49" t="inlineStr">
-        <is>
-          <t>9.86 – 12.05 %</t>
-        </is>
-      </c>
-      <c r="F116" s="49" t="inlineStr">
-        <is>
-          <t>ППК26006</t>
-        </is>
-      </c>
-      <c r="G116" s="49" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H116" s="49" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I116" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
+    <row r="116" ht="19.5" customHeight="1">
+      <c r="A116" s="46" t="inlineStr">
+        <is>
+          <t>Permanent Market      3 batch(es)      Total Δ⁹-THC across batches (release): 10.01 – 14.06 %</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="47" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B117" s="48" t="inlineStr">
         <is>
-          <t>SJ102501</t>
-        </is>
-      </c>
-      <c r="C117" s="49" t="n"/>
+          <t>PM072501</t>
+        </is>
+      </c>
+      <c r="C117" s="49" t="inlineStr">
+        <is>
+          <t>P050272</t>
+        </is>
+      </c>
       <c r="D117" s="49" t="inlineStr">
         <is>
-          <t>11.20 %w/w (U ±0.69)</t>
+          <t>10.01%</t>
         </is>
       </c>
       <c r="E117" s="49" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>9 – 11.01 %</t>
         </is>
       </c>
       <c r="F117" s="49" t="inlineStr">
         <is>
-          <t>051-3-K/26</t>
+          <t>ППК25368</t>
         </is>
       </c>
       <c r="G117" s="49" t="inlineStr">
         <is>
-          <t>04.03.2026</t>
+          <t>28.11.2025</t>
         </is>
       </c>
       <c r="H117" s="49" t="inlineStr">
         <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I117" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="50" t="n">
+        <v>71</v>
+      </c>
+      <c r="B118" s="51" t="inlineStr">
+        <is>
+          <t>PM092501</t>
+        </is>
+      </c>
+      <c r="C118" s="52" t="inlineStr">
+        <is>
+          <t>P060062</t>
+        </is>
+      </c>
+      <c r="D118" s="52" t="inlineStr">
+        <is>
+          <t>14.06%</t>
+        </is>
+      </c>
+      <c r="E118" s="52" t="inlineStr">
+        <is>
+          <t>12.65 – 15.46 %</t>
+        </is>
+      </c>
+      <c r="F118" s="52" t="inlineStr">
+        <is>
+          <t>ППК26004</t>
+        </is>
+      </c>
+      <c r="G118" s="52" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H118" s="52" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I118" s="52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="53" t="n"/>
+      <c r="B119" s="53" t="n"/>
+      <c r="C119" s="53" t="n"/>
+      <c r="D119" s="49" t="inlineStr">
+        <is>
+          <t>12.25% w/w (U 0.75% w/w)</t>
+        </is>
+      </c>
+      <c r="E119" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F119" s="49" t="inlineStr">
+        <is>
+          <t>197-20-К/26</t>
+        </is>
+      </c>
+      <c r="G119" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H119" s="49" t="inlineStr">
+        <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I117" s="49" t="inlineStr">
+      <c r="I119" s="49" t="inlineStr">
         <is>
           <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="B118" s="48" t="inlineStr">
-        <is>
-          <t>SJ112501</t>
-        </is>
-      </c>
-      <c r="C118" s="49" t="n"/>
-      <c r="D118" s="49" t="inlineStr">
-        <is>
-          <t>9.20 %w/w (U ±0.57)</t>
-        </is>
-      </c>
-      <c r="E118" s="49" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F118" s="49" t="inlineStr">
-        <is>
-          <t>051-2-K/26</t>
-        </is>
-      </c>
-      <c r="G118" s="49" t="inlineStr">
-        <is>
-          <t>04.03.2026</t>
-        </is>
-      </c>
-      <c r="H118" s="49" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I118" s="49" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="19.5" customHeight="1">
-      <c r="A119" s="46" t="inlineStr">
-        <is>
-          <t>Wedding Crasher      2 batch(es)      Total Δ⁹-THC across batches: 21.67 – 22.11 %</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="47" t="n">
+        <v>72</v>
+      </c>
+      <c r="B120" s="48" t="inlineStr">
+        <is>
+          <t>PM112501</t>
+        </is>
+      </c>
+      <c r="C120" s="49" t="n"/>
+      <c r="D120" s="49" t="inlineStr">
+        <is>
+          <t>13.33%</t>
+        </is>
+      </c>
+      <c r="E120" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F120" s="49" t="inlineStr">
+        <is>
+          <t>ППК26030</t>
+        </is>
+      </c>
+      <c r="G120" s="49" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="H120" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I120" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="19.5" customHeight="1">
+      <c r="A121" s="46" t="inlineStr">
+        <is>
+          <t>Scrambler      3 batch(es)      Total Δ⁹-THC across batches (release): 17.13 – 21.92 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="47" t="n">
+        <v>73</v>
+      </c>
+      <c r="B122" s="48" t="inlineStr">
+        <is>
+          <t>SCR112501</t>
+        </is>
+      </c>
+      <c r="C122" s="49" t="n"/>
+      <c r="D122" s="49" t="inlineStr">
+        <is>
+          <t>17.13%</t>
+        </is>
+      </c>
+      <c r="E122" s="49" t="n"/>
+      <c r="F122" s="49" t="inlineStr">
+        <is>
+          <t>ППК26069</t>
+        </is>
+      </c>
+      <c r="G122" s="49" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H122" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I122" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="47" t="n">
+        <v>74</v>
+      </c>
+      <c r="B123" s="48" t="inlineStr">
+        <is>
+          <t>SCR022601</t>
+        </is>
+      </c>
+      <c r="C123" s="49" t="n"/>
+      <c r="D123" s="49" t="inlineStr">
+        <is>
+          <t>21.92%</t>
+        </is>
+      </c>
+      <c r="E123" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F123" s="49" t="inlineStr">
+        <is>
+          <t>ППК26116</t>
+        </is>
+      </c>
+      <c r="G123" s="49" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="H123" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I123" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="47" t="n">
+        <v>75</v>
+      </c>
+      <c r="B124" s="48" t="inlineStr">
+        <is>
+          <t>P060382</t>
+        </is>
+      </c>
+      <c r="C124" s="49" t="inlineStr">
+        <is>
+          <t>P060382</t>
+        </is>
+      </c>
+      <c r="D124" s="49" t="inlineStr">
+        <is>
+          <t>17.84 %w/w (U 1.10 %w/w, k=2)</t>
+        </is>
+      </c>
+      <c r="E124" s="49" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F124" s="49" t="inlineStr">
+        <is>
+          <t>197-21-К/26</t>
+        </is>
+      </c>
+      <c r="G124" s="49" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H124" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I124" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="19.5" customHeight="1">
+      <c r="A125" s="46" t="inlineStr">
+        <is>
+          <t>Sleepy Joy      3 batch(es)      Total Δ⁹-THC across batches (release): 9.20 – 11.20 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="47" t="n">
+        <v>76</v>
+      </c>
+      <c r="B126" s="48" t="inlineStr">
+        <is>
+          <t>SJ092501</t>
+        </is>
+      </c>
+      <c r="C126" s="49" t="inlineStr">
+        <is>
+          <t>P060082</t>
+        </is>
+      </c>
+      <c r="D126" s="49" t="inlineStr">
+        <is>
+          <t>10.96%</t>
+        </is>
+      </c>
+      <c r="E126" s="49" t="inlineStr">
+        <is>
+          <t>9.86 – 12.05 %</t>
+        </is>
+      </c>
+      <c r="F126" s="49" t="inlineStr">
+        <is>
+          <t>ППК26006</t>
+        </is>
+      </c>
+      <c r="G126" s="49" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H126" s="49" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I126" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="47" t="n">
+        <v>77</v>
+      </c>
+      <c r="B127" s="48" t="inlineStr">
+        <is>
+          <t>SJ102501</t>
+        </is>
+      </c>
+      <c r="C127" s="49" t="n"/>
+      <c r="D127" s="49" t="inlineStr">
+        <is>
+          <t>11.20 %w/w (U ±0.69)</t>
+        </is>
+      </c>
+      <c r="E127" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F127" s="49" t="inlineStr">
+        <is>
+          <t>051-3-K/26</t>
+        </is>
+      </c>
+      <c r="G127" s="49" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="H127" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I127" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="47" t="n">
+        <v>78</v>
+      </c>
+      <c r="B128" s="48" t="inlineStr">
+        <is>
+          <t>SJ112501</t>
+        </is>
+      </c>
+      <c r="C128" s="49" t="n"/>
+      <c r="D128" s="49" t="inlineStr">
+        <is>
+          <t>9.20 %w/w (U ±0.57)</t>
+        </is>
+      </c>
+      <c r="E128" s="49" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F128" s="49" t="inlineStr">
+        <is>
+          <t>051-2-K/26</t>
+        </is>
+      </c>
+      <c r="G128" s="49" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="H128" s="49" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I128" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="19.5" customHeight="1">
+      <c r="A129" s="46" t="inlineStr">
+        <is>
+          <t>Wedding Crasher      2 batch(es)      Total Δ⁹-THC across batches (release): 21.67 – 22.11 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="47" t="n">
         <v>79</v>
       </c>
-      <c r="B120" s="48" t="inlineStr">
+      <c r="B130" s="48" t="inlineStr">
         <is>
           <t>WC072501</t>
         </is>
       </c>
-      <c r="C120" s="49" t="inlineStr">
+      <c r="C130" s="49" t="inlineStr">
         <is>
           <t>P050262</t>
         </is>
       </c>
-      <c r="D120" s="49" t="inlineStr">
+      <c r="D130" s="49" t="inlineStr">
         <is>
           <t>22.11%</t>
         </is>
       </c>
-      <c r="E120" s="49" t="inlineStr">
+      <c r="E130" s="49" t="inlineStr">
         <is>
           <t>n/a (informational)</t>
         </is>
       </c>
-      <c r="F120" s="49" t="inlineStr">
+      <c r="F130" s="49" t="inlineStr">
         <is>
           <t>ППК25369</t>
         </is>
       </c>
-      <c r="G120" s="49" t="inlineStr">
+      <c r="G130" s="49" t="inlineStr">
         <is>
           <t>28.11.2025</t>
         </is>
       </c>
-      <c r="H120" s="49" t="inlineStr">
+      <c r="H130" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I120" s="49" t="inlineStr">
+      <c r="I130" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="47" t="n">
+    <row r="131">
+      <c r="A131" s="47" t="n">
         <v>80</v>
       </c>
-      <c r="B121" s="48" t="inlineStr">
+      <c r="B131" s="48" t="inlineStr">
         <is>
           <t>WC082501</t>
         </is>
       </c>
-      <c r="C121" s="49" t="inlineStr">
+      <c r="C131" s="49" t="inlineStr">
         <is>
           <t>P060012</t>
         </is>
       </c>
-      <c r="D121" s="49" t="inlineStr">
+      <c r="D131" s="49" t="inlineStr">
         <is>
           <t>21.67%</t>
         </is>
       </c>
-      <c r="E121" s="49" t="inlineStr">
+      <c r="E131" s="49" t="inlineStr">
         <is>
           <t>19.5 – 23.83 %</t>
         </is>
       </c>
-      <c r="F121" s="49" t="inlineStr">
+      <c r="F131" s="49" t="inlineStr">
         <is>
           <t>ППК26001</t>
         </is>
       </c>
-      <c r="G121" s="49" t="inlineStr">
+      <c r="G131" s="49" t="inlineStr">
         <is>
           <t>21.01.2026</t>
         </is>
       </c>
-      <c r="H121" s="49" t="inlineStr">
+      <c r="H131" s="49" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
-      <c r="I121" s="49" t="inlineStr">
+      <c r="I131" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="73">
+  <mergeCells count="79">
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="C30:C31"/>
-    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="A99:I99"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="A101:I101"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="A56:A59"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="C56:C59"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A51:A55"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="B56:B59"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A62:A66"/>
+    <mergeCell ref="A129:I129"/>
+    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="A116:I116"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="A92:I92"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="A78:I78"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="A104:I104"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="C62:C66"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="B22:B23"/>
     <mergeCell ref="B96:B97"/>
     <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A66:I66"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="A89:I89"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="A84:I84"/>
+    <mergeCell ref="C51:C55"/>
     <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A74:I74"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A33:I33"/>
-    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="C118:C119"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="C25:C26"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C41:C42"/>
     <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="A106:I106"/>
     <mergeCell ref="C11:C12"/>
-    <mergeCell ref="A91:I91"/>
-    <mergeCell ref="A76:A77"/>
     <mergeCell ref="A20:I20"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A111:I111"/>
-    <mergeCell ref="A115:I115"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="A40:I40"/>
-    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="A125:I125"/>
+    <mergeCell ref="B62:B66"/>
+    <mergeCell ref="A121:I121"/>
     <mergeCell ref="A96:A97"/>
     <mergeCell ref="C96:C97"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B76:B77"/>
     <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A82:I82"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A94:I94"/>
-    <mergeCell ref="B25:B26"/>
     <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="A119:I119"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A82:A83"/>
     <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A114:A115"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39388,7 +39730,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -39511,59 +39853,59 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="54" t="n"/>
-      <c r="B5" s="54" t="n"/>
-      <c r="C5" s="54" t="n"/>
-      <c r="D5" s="54" t="n"/>
-      <c r="E5" s="54" t="n"/>
-      <c r="F5" s="54" t="n"/>
-      <c r="G5" s="54" t="n"/>
-      <c r="H5" s="54" t="inlineStr">
+      <c r="A5" s="56" t="n"/>
+      <c r="B5" s="56" t="n"/>
+      <c r="C5" s="56" t="n"/>
+      <c r="D5" s="56" t="n"/>
+      <c r="E5" s="56" t="n"/>
+      <c r="F5" s="56" t="n"/>
+      <c r="G5" s="56" t="n"/>
+      <c r="H5" s="56" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="I5" s="54" t="inlineStr">
+      <c r="I5" s="56" t="inlineStr">
         <is>
           <t>≤ 10.00 %</t>
         </is>
       </c>
-      <c r="J5" s="54" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="K5" s="54" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="L5" s="54" t="inlineStr">
+      <c r="J5" s="56" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="K5" s="56" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="L5" s="56" t="inlineStr">
         <is>
           <t>≤ 1.00 %</t>
         </is>
       </c>
-      <c r="M5" s="54" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="N5" s="54" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="O5" s="54" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="P5" s="54" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="Q5" s="54" t="inlineStr">
+      <c r="M5" s="56" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="N5" s="56" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="O5" s="56" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="P5" s="56" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="Q5" s="56" t="inlineStr">
         <is>
           <t>/</t>
         </is>
@@ -39615,30 +39957,26 @@
           <t>Универзитет „Св. Кирил и Методиј“, Скопје, Фармацевтски факултет, Центар за природни производи</t>
         </is>
       </c>
-      <c r="I7" s="55" t="n">
+      <c r="I7" s="57" t="n">
         <v>6.32</v>
       </c>
-      <c r="J7" s="55" t="n">
+      <c r="J7" s="57" t="n">
         <v>0.04</v>
       </c>
-      <c r="K7" s="49" t="inlineStr">
-        <is>
-          <t>BLQ</t>
-        </is>
-      </c>
-      <c r="L7" s="55" t="n">
+      <c r="K7" s="49" t="n"/>
+      <c r="L7" s="57" t="n">
         <v>0.23</v>
       </c>
-      <c r="M7" s="55" t="n">
+      <c r="M7" s="57" t="n">
         <v>12.23</v>
       </c>
-      <c r="N7" s="55" t="n">
+      <c r="N7" s="57" t="n">
         <v>10.34</v>
       </c>
-      <c r="O7" s="55" t="n">
+      <c r="O7" s="57" t="n">
         <v>0.04</v>
       </c>
-      <c r="P7" s="55" t="n">
+      <c r="P7" s="57" t="n">
         <v>21.31</v>
       </c>
       <c r="Q7" s="49" t="inlineStr"/>
@@ -39682,31 +40020,31 @@
           <t>Ss. Cyril and Methodius University, Skopje, Faculty of Pharmacy, Center for natural products</t>
         </is>
       </c>
-      <c r="I8" s="55" t="n">
+      <c r="I8" s="57" t="n">
         <v>5.84</v>
       </c>
-      <c r="J8" s="55" t="n">
+      <c r="J8" s="57" t="n">
         <v>0.03</v>
       </c>
-      <c r="K8" s="55" t="n">
+      <c r="K8" s="57" t="n">
         <v>0.03</v>
       </c>
-      <c r="L8" s="56" t="n">
+      <c r="L8" s="58" t="n">
         <v>2.35</v>
       </c>
-      <c r="M8" s="55" t="n">
+      <c r="M8" s="57" t="n">
         <v>13.16</v>
       </c>
-      <c r="N8" s="55" t="n">
+      <c r="N8" s="57" t="n">
         <v>0.01</v>
       </c>
-      <c r="O8" s="55" t="n">
+      <c r="O8" s="57" t="n">
         <v>0.06</v>
       </c>
-      <c r="P8" s="55" t="n">
+      <c r="P8" s="57" t="n">
         <v>13.16</v>
       </c>
-      <c r="Q8" s="57" t="inlineStr">
+      <c r="Q8" s="59" t="inlineStr">
         <is>
           <t>CBN 2.35 % exceeds the ≤ 1.00 % limit stated on the certificate</t>
         </is>
@@ -39751,28 +40089,28 @@
           <t>Универзитет „Св. Кирил и Методиј“, Скопје, Фармацевтски факултет, Центар за природни производи</t>
         </is>
       </c>
-      <c r="I9" s="55" t="n">
+      <c r="I9" s="57" t="n">
         <v>6.62</v>
       </c>
-      <c r="J9" s="55" t="n">
+      <c r="J9" s="57" t="n">
         <v>0.03</v>
       </c>
-      <c r="K9" s="55" t="n">
+      <c r="K9" s="57" t="n">
         <v>0.01</v>
       </c>
-      <c r="L9" s="55" t="n">
+      <c r="L9" s="57" t="n">
         <v>0.3</v>
       </c>
-      <c r="M9" s="55" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N9" s="55" t="n">
+      <c r="M9" s="57" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="N9" s="57" t="n">
         <v>13.22</v>
       </c>
-      <c r="O9" s="55" t="n">
+      <c r="O9" s="57" t="n">
         <v>0.03</v>
       </c>
-      <c r="P9" s="55" t="n">
+      <c r="P9" s="57" t="n">
         <v>23.08</v>
       </c>
       <c r="Q9" s="49" t="inlineStr"/>
@@ -39823,30 +40161,26 @@
           <t>Ss. Cyril and Methodius University, Skopje, Faculty of Pharmacy, Center for natural products</t>
         </is>
       </c>
-      <c r="I11" s="55" t="n">
+      <c r="I11" s="57" t="n">
         <v>5.92</v>
       </c>
-      <c r="J11" s="55" t="n">
+      <c r="J11" s="57" t="n">
         <v>0.04</v>
       </c>
-      <c r="K11" s="49" t="inlineStr">
-        <is>
-          <t>BLQ</t>
-        </is>
-      </c>
-      <c r="L11" s="55" t="n">
+      <c r="K11" s="49" t="n"/>
+      <c r="L11" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="M11" s="55" t="n">
+      <c r="M11" s="57" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="N11" s="55" t="n">
+      <c r="N11" s="57" t="n">
         <v>16.7</v>
       </c>
-      <c r="O11" s="55" t="n">
+      <c r="O11" s="57" t="n">
         <v>0.04</v>
       </c>
-      <c r="P11" s="55" t="n">
+      <c r="P11" s="57" t="n">
         <v>24.62</v>
       </c>
       <c r="Q11" s="49" t="inlineStr"/>
@@ -39890,10 +40224,10 @@
           <t>Универзитет „Св. Кирил и Методиј“, Скопје, Фармацевтски факултет, Центар за природни производи</t>
         </is>
       </c>
-      <c r="I12" s="55" t="n">
+      <c r="I12" s="57" t="n">
         <v>5.52</v>
       </c>
-      <c r="J12" s="55" t="n">
+      <c r="J12" s="57" t="n">
         <v>0.03</v>
       </c>
       <c r="K12" s="49" t="inlineStr">
@@ -39901,10 +40235,10 @@
           <t>ND</t>
         </is>
       </c>
-      <c r="L12" s="56" t="n">
+      <c r="L12" s="58" t="n">
         <v>2.15</v>
       </c>
-      <c r="M12" s="55" t="n">
+      <c r="M12" s="57" t="n">
         <v>14.98</v>
       </c>
       <c r="N12" s="49" t="inlineStr">
@@ -39912,13 +40246,13 @@
           <t>BLQ</t>
         </is>
       </c>
-      <c r="O12" s="55" t="n">
+      <c r="O12" s="57" t="n">
         <v>0.02</v>
       </c>
-      <c r="P12" s="55" t="n">
+      <c r="P12" s="57" t="n">
         <v>14.99</v>
       </c>
-      <c r="Q12" s="57" t="inlineStr">
+      <c r="Q12" s="59" t="inlineStr">
         <is>
           <t>CBN 2.15 % exceeds the ≤ 1.00 % limit stated on the certificate</t>
         </is>
@@ -39963,28 +40297,28 @@
           <t>Ss. Cyril and Methodius University, Skopje, Faculty of Pharmacy, Center for natural products</t>
         </is>
       </c>
-      <c r="I13" s="55" t="n">
+      <c r="I13" s="57" t="n">
         <v>7.07</v>
       </c>
-      <c r="J13" s="55" t="n">
+      <c r="J13" s="57" t="n">
         <v>0.04</v>
       </c>
-      <c r="K13" s="55" t="n">
+      <c r="K13" s="57" t="n">
         <v>0.01</v>
       </c>
-      <c r="L13" s="55" t="n">
+      <c r="L13" s="57" t="n">
         <v>0.04</v>
       </c>
-      <c r="M13" s="55" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N13" s="55" t="n">
+      <c r="M13" s="57" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="N13" s="57" t="n">
         <v>12.36</v>
       </c>
-      <c r="O13" s="55" t="n">
+      <c r="O13" s="57" t="n">
         <v>0.04</v>
       </c>
-      <c r="P13" s="55" t="n">
+      <c r="P13" s="57" t="n">
         <v>25.98</v>
       </c>
       <c r="Q13" s="49" t="inlineStr"/>
@@ -40035,30 +40369,26 @@
           <t>Универзитет ,,Св. Кирил и Методиј“, Скопје, Фармацевтски факултет, Центар за природни производи</t>
         </is>
       </c>
-      <c r="I15" s="55" t="n">
+      <c r="I15" s="57" t="n">
         <v>5.83</v>
       </c>
-      <c r="J15" s="55" t="n">
+      <c r="J15" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="K15" s="49" t="inlineStr">
-        <is>
-          <t>BLQ</t>
-        </is>
-      </c>
-      <c r="L15" s="55" t="n">
+      <c r="K15" s="49" t="n"/>
+      <c r="L15" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="M15" s="55" t="n">
+      <c r="M15" s="57" t="n">
         <v>7.9</v>
       </c>
-      <c r="N15" s="55" t="n">
+      <c r="N15" s="57" t="n">
         <v>17.03</v>
       </c>
-      <c r="O15" s="55" t="n">
+      <c r="O15" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="P15" s="55" t="n">
+      <c r="P15" s="57" t="n">
         <v>22.83</v>
       </c>
       <c r="Q15" s="49" t="inlineStr"/>
@@ -40102,28 +40432,28 @@
           <t>Универзитет „Св. Кирил и Методиј“, Скопје, Фармацевтски факултет, Центар за природни производи</t>
         </is>
       </c>
-      <c r="I16" s="55" t="n">
+      <c r="I16" s="57" t="n">
         <v>5.38</v>
       </c>
-      <c r="J16" s="55" t="n">
+      <c r="J16" s="57" t="n">
         <v>0.02</v>
       </c>
-      <c r="K16" s="55" t="n">
+      <c r="K16" s="57" t="n">
         <v>0.03</v>
       </c>
-      <c r="L16" s="55" t="n">
+      <c r="L16" s="57" t="n">
         <v>0.19</v>
       </c>
-      <c r="M16" s="55" t="n">
+      <c r="M16" s="57" t="n">
         <v>18.47</v>
       </c>
-      <c r="N16" s="55" t="n">
+      <c r="N16" s="57" t="n">
         <v>0.17</v>
       </c>
-      <c r="O16" s="55" t="n">
+      <c r="O16" s="57" t="n">
         <v>0.06</v>
       </c>
-      <c r="P16" s="55" t="n">
+      <c r="P16" s="57" t="n">
         <v>18.62</v>
       </c>
       <c r="Q16" s="49" t="inlineStr"/>
@@ -40167,28 +40497,28 @@
           <t>Sts. Cyril and Methodius University, Skopje, Faculty of Pharmacy, Center for natural products</t>
         </is>
       </c>
-      <c r="I17" s="55" t="n">
+      <c r="I17" s="57" t="n">
         <v>6.85</v>
       </c>
-      <c r="J17" s="55" t="n">
+      <c r="J17" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="K17" s="55" t="n">
+      <c r="K17" s="57" t="n">
         <v>0.01</v>
       </c>
-      <c r="L17" s="55" t="n">
+      <c r="L17" s="57" t="n">
         <v>0.04</v>
       </c>
-      <c r="M17" s="55" t="n">
+      <c r="M17" s="57" t="n">
         <v>13.49</v>
       </c>
-      <c r="N17" s="55" t="n">
+      <c r="N17" s="57" t="n">
         <v>12.57</v>
       </c>
-      <c r="O17" s="55" t="n">
+      <c r="O17" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="P17" s="55" t="n">
+      <c r="P17" s="57" t="n">
         <v>24.51</v>
       </c>
       <c r="Q17" s="49" t="inlineStr"/>
@@ -40232,31 +40562,31 @@
           <t>Универзитет „Св. Кирил и Методиј“, Скопје, Фармацевтски факултет, Центар за природни производи</t>
         </is>
       </c>
-      <c r="I18" s="55" t="n">
+      <c r="I18" s="57" t="n">
         <v>6.6</v>
       </c>
-      <c r="J18" s="55" t="n">
+      <c r="J18" s="57" t="n">
         <v>0.02</v>
       </c>
-      <c r="K18" s="55" t="n">
+      <c r="K18" s="57" t="n">
         <v>0.01</v>
       </c>
-      <c r="L18" s="56" t="n">
+      <c r="L18" s="58" t="n">
         <v>2.05</v>
       </c>
-      <c r="M18" s="55" t="n">
+      <c r="M18" s="57" t="n">
         <v>0.29</v>
       </c>
-      <c r="N18" s="55" t="n">
+      <c r="N18" s="57" t="n">
         <v>0.97</v>
       </c>
-      <c r="O18" s="55" t="n">
+      <c r="O18" s="57" t="n">
         <v>0.03</v>
       </c>
-      <c r="P18" s="55" t="n">
+      <c r="P18" s="57" t="n">
         <v>1.17</v>
       </c>
-      <c r="Q18" s="57" t="inlineStr">
+      <c r="Q18" s="59" t="inlineStr">
         <is>
           <t>CBN 2.05 % exceeds the ≤ 1.00 % limit stated on the certificate</t>
         </is>
